--- a/아우디_models.xlsx
+++ b/아우디_models.xlsx
@@ -126,7 +126,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -166,6 +166,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1792,7 +1795,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G19" s="6" t="inlineStr">
+      <c r="G19" s="14" t="inlineStr">
         <is>
           <t>ID49(NCF295X)</t>
         </is>
@@ -1815,7 +1818,7 @@
         </is>
       </c>
       <c r="M19" s="11" t="inlineStr"/>
-      <c r="N19" s="6" t="inlineStr">
+      <c r="N19" s="14" t="inlineStr">
         <is>
           <t>MQB-Evo IMMO5</t>
         </is>
@@ -1825,11 +1828,7 @@
           <t>executivecarkeys, programyourremote(2025 A3)</t>
         </is>
       </c>
-      <c r="P19" s="6" t="inlineStr">
-        <is>
-          <t>해당 연식 칩 자료 없음 — 같은 세대 기준 추정</t>
-        </is>
-      </c>
+      <c r="P19" s="14" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="11" t="inlineStr">
@@ -2530,7 +2529,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G30" s="6" t="inlineStr">
+      <c r="G30" s="14" t="inlineStr">
         <is>
           <t>ID49(NCF295X)</t>
         </is>
@@ -2553,7 +2552,7 @@
         </is>
       </c>
       <c r="M30" s="11" t="inlineStr"/>
-      <c r="N30" s="6" t="inlineStr">
+      <c r="N30" s="14" t="inlineStr">
         <is>
           <t>MQB-Evo IMMO5</t>
         </is>
@@ -2563,11 +2562,7 @@
           <t>go-parts</t>
         </is>
       </c>
-      <c r="P30" s="6" t="inlineStr">
-        <is>
-          <t>해당 연식 칩 자료 없음 — 같은 세대 기준 추정</t>
-        </is>
-      </c>
+      <c r="P30" s="14" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="11" t="inlineStr">
@@ -2732,7 +2727,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G33" s="6" t="inlineStr">
+      <c r="G33" s="14" t="inlineStr">
         <is>
           <t>ID49(NCF295X)</t>
         </is>
@@ -2755,7 +2750,7 @@
         </is>
       </c>
       <c r="M33" s="11" t="inlineStr"/>
-      <c r="N33" s="6" t="inlineStr">
+      <c r="N33" s="14" t="inlineStr">
         <is>
           <t>MQB-Evo IMMO5</t>
         </is>
@@ -2765,11 +2760,7 @@
           <t>go-parts, ebay(2023/2024 Audi key)</t>
         </is>
       </c>
-      <c r="P33" s="6" t="inlineStr">
-        <is>
-          <t>해당 연식 칩 자료 없음 — 같은 세대 기준 추정</t>
-        </is>
-      </c>
+      <c r="P33" s="14" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="11" t="inlineStr">
@@ -2802,7 +2793,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G34" s="11" t="inlineStr">
+      <c r="G34" s="14" t="inlineStr">
         <is>
           <t>ID49(NCF295X)</t>
         </is>
@@ -2825,7 +2816,7 @@
         </is>
       </c>
       <c r="M34" s="11" t="inlineStr"/>
-      <c r="N34" s="11" t="inlineStr">
+      <c r="N34" s="14" t="inlineStr">
         <is>
           <t>MQB-Evo IMMO5</t>
         </is>
@@ -2835,7 +2826,7 @@
           <t>parts.audinorthorlando(2025 RS3), keyfirst</t>
         </is>
       </c>
-      <c r="P34" s="11" t="inlineStr"/>
+      <c r="P34" s="14" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="11" t="inlineStr">
@@ -4808,7 +4799,7 @@
       <c r="D69" s="7" t="inlineStr"/>
       <c r="E69" s="7" t="inlineStr"/>
       <c r="F69" s="7" t="inlineStr"/>
-      <c r="G69" s="6" t="inlineStr">
+      <c r="G69" s="14" t="inlineStr">
         <is>
           <t>MLB 전용 칩</t>
         </is>
@@ -4827,7 +4818,7 @@
       <c r="K69" s="11" t="inlineStr"/>
       <c r="L69" s="11" t="inlineStr"/>
       <c r="M69" s="11" t="inlineStr"/>
-      <c r="N69" s="6" t="inlineStr">
+      <c r="N69" s="14" t="inlineStr">
         <is>
           <t>MLB IMMO5</t>
         </is>
@@ -4837,11 +4828,7 @@
           <t>parts.audiusa, 12volt.solutions(2017-2023 S4)</t>
         </is>
       </c>
-      <c r="P69" s="6" t="inlineStr">
-        <is>
-          <t>해당 연식 칩 자료 없음 — 같은 세대 기준 추정</t>
-        </is>
-      </c>
+      <c r="P69" s="14" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="11" t="inlineStr">
@@ -5302,7 +5289,7 @@
       <c r="D78" s="7" t="inlineStr"/>
       <c r="E78" s="7" t="inlineStr"/>
       <c r="F78" s="7" t="inlineStr"/>
-      <c r="G78" s="6" t="inlineStr">
+      <c r="G78" s="14" t="inlineStr">
         <is>
           <t>MLB 전용 칩</t>
         </is>
@@ -5321,7 +5308,7 @@
       <c r="K78" s="11" t="inlineStr"/>
       <c r="L78" s="11" t="inlineStr"/>
       <c r="M78" s="11" t="inlineStr"/>
-      <c r="N78" s="6" t="inlineStr">
+      <c r="N78" s="14" t="inlineStr">
         <is>
           <t>MLB IMMO5</t>
         </is>
@@ -5331,11 +5318,7 @@
           <t>go-parts(2017-2025 B9 key guide)</t>
         </is>
       </c>
-      <c r="P78" s="6" t="inlineStr">
-        <is>
-          <t>해당 연식 칩 자료 없음 — 같은 세대 기준 추정</t>
-        </is>
-      </c>
+      <c r="P78" s="14" t="n"/>
     </row>
     <row r="79">
       <c r="A79" s="11" t="inlineStr">
@@ -5356,7 +5339,7 @@
       <c r="D79" s="7" t="inlineStr"/>
       <c r="E79" s="7" t="inlineStr"/>
       <c r="F79" s="7" t="inlineStr"/>
-      <c r="G79" s="6" t="inlineStr">
+      <c r="G79" s="14" t="inlineStr">
         <is>
           <t>MLB 전용 칩</t>
         </is>
@@ -5375,7 +5358,7 @@
       <c r="K79" s="11" t="inlineStr"/>
       <c r="L79" s="11" t="inlineStr"/>
       <c r="M79" s="11" t="inlineStr"/>
-      <c r="N79" s="6" t="inlineStr">
+      <c r="N79" s="14" t="inlineStr">
         <is>
           <t>MLB IMMO5</t>
         </is>
@@ -5385,11 +5368,7 @@
           <t>go-parts</t>
         </is>
       </c>
-      <c r="P79" s="6" t="inlineStr">
-        <is>
-          <t>해당 연식 칩 자료 없음 — 같은 세대 기준 추정</t>
-        </is>
-      </c>
+      <c r="P79" s="14" t="n"/>
     </row>
     <row r="80">
       <c r="A80" s="11" t="inlineStr">
@@ -5410,7 +5389,7 @@
       <c r="D80" s="7" t="inlineStr"/>
       <c r="E80" s="7" t="inlineStr"/>
       <c r="F80" s="7" t="inlineStr"/>
-      <c r="G80" s="6" t="inlineStr">
+      <c r="G80" s="14" t="inlineStr">
         <is>
           <t>MLB 전용 칩</t>
         </is>
@@ -5429,7 +5408,7 @@
       <c r="K80" s="11" t="inlineStr"/>
       <c r="L80" s="11" t="inlineStr"/>
       <c r="M80" s="11" t="inlineStr"/>
-      <c r="N80" s="6" t="inlineStr">
+      <c r="N80" s="14" t="inlineStr">
         <is>
           <t>MLB IMMO5</t>
         </is>
@@ -5439,11 +5418,7 @@
           <t>go-parts, caredge</t>
         </is>
       </c>
-      <c r="P80" s="6" t="inlineStr">
-        <is>
-          <t>해당 연식 칩 자료 없음 — 같은 세대 기준 추정</t>
-        </is>
-      </c>
+      <c r="P80" s="14" t="n"/>
     </row>
     <row r="81">
       <c r="A81" s="11" t="inlineStr">
@@ -6294,7 +6269,7 @@
       <c r="D96" s="7" t="inlineStr"/>
       <c r="E96" s="7" t="inlineStr"/>
       <c r="F96" s="7" t="inlineStr"/>
-      <c r="G96" s="6" t="inlineStr">
+      <c r="G96" s="14" t="inlineStr">
         <is>
           <t>MLB 전용 칩</t>
         </is>
@@ -6313,7 +6288,7 @@
       <c r="K96" s="11" t="inlineStr"/>
       <c r="L96" s="11" t="inlineStr"/>
       <c r="M96" s="11" t="inlineStr"/>
-      <c r="N96" s="6" t="inlineStr">
+      <c r="N96" s="14" t="inlineStr">
         <is>
           <t>MLB IMMO5</t>
         </is>
@@ -6323,11 +6298,7 @@
           <t>parts.audiusa(2023 A5 CG)</t>
         </is>
       </c>
-      <c r="P96" s="6" t="inlineStr">
-        <is>
-          <t>해당 연식 칩 자료 없음 — 같은 세대 기준 추정</t>
-        </is>
-      </c>
+      <c r="P96" s="14" t="n"/>
     </row>
     <row r="97">
       <c r="A97" s="11" t="inlineStr">
@@ -6954,7 +6925,7 @@
       <c r="D108" s="7" t="inlineStr"/>
       <c r="E108" s="7" t="inlineStr"/>
       <c r="F108" s="7" t="inlineStr"/>
-      <c r="G108" s="6" t="inlineStr">
+      <c r="G108" s="14" t="inlineStr">
         <is>
           <t>MLB 전용 칩</t>
         </is>
@@ -6973,7 +6944,7 @@
       <c r="K108" s="11" t="inlineStr"/>
       <c r="L108" s="11" t="inlineStr"/>
       <c r="M108" s="11" t="inlineStr"/>
-      <c r="N108" s="6" t="inlineStr">
+      <c r="N108" s="14" t="inlineStr">
         <is>
           <t>MLB IMMO5</t>
         </is>
@@ -6983,11 +6954,7 @@
           <t>parts.audiusa(2022 S5)</t>
         </is>
       </c>
-      <c r="P108" s="6" t="inlineStr">
-        <is>
-          <t>해당 연식 칩 자료 없음 — 같은 세대 기준 추정</t>
-        </is>
-      </c>
+      <c r="P108" s="14" t="n"/>
     </row>
     <row r="109">
       <c r="A109" s="11" t="inlineStr">
@@ -7764,7 +7731,7 @@
       <c r="D123" s="7" t="inlineStr"/>
       <c r="E123" s="7" t="inlineStr"/>
       <c r="F123" s="7" t="inlineStr"/>
-      <c r="G123" s="6" t="inlineStr">
+      <c r="G123" s="14" t="inlineStr">
         <is>
           <t>MLB 전용 칩</t>
         </is>
@@ -7783,7 +7750,7 @@
       <c r="K123" s="11" t="inlineStr"/>
       <c r="L123" s="11" t="inlineStr"/>
       <c r="M123" s="11" t="inlineStr"/>
-      <c r="N123" s="6" t="inlineStr">
+      <c r="N123" s="14" t="inlineStr">
         <is>
           <t>MLB IMMO5</t>
         </is>
@@ -7793,11 +7760,7 @@
           <t>parts.audiusa, keylessentryremotefob(RS5)</t>
         </is>
       </c>
-      <c r="P123" s="6" t="inlineStr">
-        <is>
-          <t>해당 연식 칩 자료 없음 — 같은 세대 기준 추정</t>
-        </is>
-      </c>
+      <c r="P123" s="14" t="n"/>
     </row>
     <row r="124">
       <c r="A124" s="11" t="inlineStr">
@@ -7818,7 +7781,7 @@
       <c r="D124" s="7" t="inlineStr"/>
       <c r="E124" s="7" t="inlineStr"/>
       <c r="F124" s="7" t="inlineStr"/>
-      <c r="G124" s="11" t="inlineStr">
+      <c r="G124" s="14" t="inlineStr">
         <is>
           <t>MLB 전용 칩</t>
         </is>
@@ -7837,7 +7800,7 @@
       <c r="K124" s="11" t="inlineStr"/>
       <c r="L124" s="11" t="inlineStr"/>
       <c r="M124" s="11" t="inlineStr"/>
-      <c r="N124" s="11" t="inlineStr">
+      <c r="N124" s="14" t="inlineStr">
         <is>
           <t>MLB IMMO5</t>
         </is>
@@ -7847,7 +7810,7 @@
           <t>parts.audialbany(2024 RS5), carbuzz</t>
         </is>
       </c>
-      <c r="P124" s="11" t="inlineStr"/>
+      <c r="P124" s="14" t="n"/>
     </row>
     <row r="125">
       <c r="A125" s="11" t="inlineStr">
@@ -7868,7 +7831,7 @@
       <c r="D125" s="7" t="inlineStr"/>
       <c r="E125" s="7" t="inlineStr"/>
       <c r="F125" s="7" t="inlineStr"/>
-      <c r="G125" s="6" t="inlineStr">
+      <c r="G125" s="14" t="inlineStr">
         <is>
           <t>MLB 전용 칩</t>
         </is>
@@ -7887,7 +7850,7 @@
       <c r="K125" s="11" t="inlineStr"/>
       <c r="L125" s="11" t="inlineStr"/>
       <c r="M125" s="11" t="inlineStr"/>
-      <c r="N125" s="6" t="inlineStr">
+      <c r="N125" s="14" t="inlineStr">
         <is>
           <t>MLB IMMO5</t>
         </is>
@@ -7897,11 +7860,7 @@
           <t>carbuzz(RS5 coupe generations), audiworld(B9 coupe discontinued 2025)</t>
         </is>
       </c>
-      <c r="P125" s="6" t="inlineStr">
-        <is>
-          <t>해당 연식 칩 자료 없음 — 같은 세대 기준 추정</t>
-        </is>
-      </c>
+      <c r="P125" s="14" t="n"/>
     </row>
     <row r="126">
       <c r="A126" s="11" t="inlineStr">
@@ -9078,7 +9037,7 @@
       <c r="D148" s="7" t="inlineStr"/>
       <c r="E148" s="7" t="inlineStr"/>
       <c r="F148" s="7" t="inlineStr"/>
-      <c r="G148" s="6" t="inlineStr">
+      <c r="G148" s="14" t="inlineStr">
         <is>
           <t>MLB evo 전용 칩</t>
         </is>
@@ -9093,7 +9052,7 @@
       <c r="K148" s="11" t="inlineStr"/>
       <c r="L148" s="11" t="inlineStr"/>
       <c r="M148" s="11" t="inlineStr"/>
-      <c r="N148" s="6" t="inlineStr">
+      <c r="N148" s="14" t="inlineStr">
         <is>
           <t>MLB evo IMMO5</t>
         </is>
@@ -9103,11 +9062,7 @@
           <t>parts.audiusa(2024 A6 allroad), audiworld(A6 2024 key)</t>
         </is>
       </c>
-      <c r="P148" s="6" t="inlineStr">
-        <is>
-          <t>해당 연식 칩 자료 없음 — 같은 세대 기준 추정</t>
-        </is>
-      </c>
+      <c r="P148" s="14" t="n"/>
     </row>
     <row r="149">
       <c r="A149" s="11" t="inlineStr">
@@ -9644,7 +9599,7 @@
       <c r="D159" s="7" t="inlineStr"/>
       <c r="E159" s="7" t="inlineStr"/>
       <c r="F159" s="7" t="inlineStr"/>
-      <c r="G159" s="6" t="inlineStr">
+      <c r="G159" s="14" t="inlineStr">
         <is>
           <t>MLB evo 전용 칩</t>
         </is>
@@ -9659,7 +9614,7 @@
       <c r="K159" s="11" t="inlineStr"/>
       <c r="L159" s="11" t="inlineStr"/>
       <c r="M159" s="11" t="inlineStr"/>
-      <c r="N159" s="6" t="inlineStr">
+      <c r="N159" s="14" t="inlineStr">
         <is>
           <t>MLB evo IMMO5</t>
         </is>
@@ -9669,11 +9624,7 @@
           <t>locksmithkeyless(IYZ-AK2), go-parts</t>
         </is>
       </c>
-      <c r="P159" s="6" t="inlineStr">
-        <is>
-          <t>해당 연식 칩 자료 없음 — 같은 세대 기준 추정</t>
-        </is>
-      </c>
+      <c r="P159" s="14" t="n"/>
     </row>
     <row r="160">
       <c r="A160" s="11" t="inlineStr">
@@ -9694,7 +9645,7 @@
       <c r="D160" s="7" t="inlineStr"/>
       <c r="E160" s="7" t="inlineStr"/>
       <c r="F160" s="7" t="inlineStr"/>
-      <c r="G160" s="6" t="inlineStr">
+      <c r="G160" s="14" t="inlineStr">
         <is>
           <t>MLB evo 전용 칩</t>
         </is>
@@ -9709,7 +9660,7 @@
       <c r="K160" s="11" t="inlineStr"/>
       <c r="L160" s="11" t="inlineStr"/>
       <c r="M160" s="11" t="inlineStr"/>
-      <c r="N160" s="6" t="inlineStr">
+      <c r="N160" s="14" t="inlineStr">
         <is>
           <t>MLB evo IMMO5</t>
         </is>
@@ -9719,11 +9670,7 @@
           <t>carandtruckremotes(2023 A6), keylessentryremotefob(S6)</t>
         </is>
       </c>
-      <c r="P160" s="6" t="inlineStr">
-        <is>
-          <t>해당 연식 칩 자료 없음 — 같은 세대 기준 추정</t>
-        </is>
-      </c>
+      <c r="P160" s="14" t="n"/>
     </row>
     <row r="161">
       <c r="A161" s="11" t="inlineStr">
@@ -9744,7 +9691,7 @@
       <c r="D161" s="7" t="inlineStr"/>
       <c r="E161" s="7" t="inlineStr"/>
       <c r="F161" s="7" t="inlineStr"/>
-      <c r="G161" s="6" t="inlineStr">
+      <c r="G161" s="14" t="inlineStr">
         <is>
           <t>MLB evo 전용 칩</t>
         </is>
@@ -9759,7 +9706,7 @@
       <c r="K161" s="11" t="inlineStr"/>
       <c r="L161" s="11" t="inlineStr"/>
       <c r="M161" s="11" t="inlineStr"/>
-      <c r="N161" s="6" t="inlineStr">
+      <c r="N161" s="14" t="inlineStr">
         <is>
           <t>MLB evo IMMO5</t>
         </is>
@@ -9769,11 +9716,7 @@
           <t>go-parts(2017-2026 key fob guide)</t>
         </is>
       </c>
-      <c r="P161" s="6" t="inlineStr">
-        <is>
-          <t>해당 연식 칩 자료 없음 — 같은 세대 기준 추정</t>
-        </is>
-      </c>
+      <c r="P161" s="14" t="n"/>
     </row>
     <row r="162">
       <c r="A162" s="11" t="inlineStr">
@@ -10996,7 +10939,7 @@
       <c r="D185" s="7" t="inlineStr"/>
       <c r="E185" s="7" t="inlineStr"/>
       <c r="F185" s="7" t="inlineStr"/>
-      <c r="G185" s="6" t="inlineStr">
+      <c r="G185" s="14" t="inlineStr">
         <is>
           <t>MLB evo 전용 칩</t>
         </is>
@@ -11011,7 +10954,7 @@
       <c r="K185" s="11" t="inlineStr"/>
       <c r="L185" s="11" t="inlineStr"/>
       <c r="M185" s="11" t="inlineStr"/>
-      <c r="N185" s="6" t="inlineStr">
+      <c r="N185" s="14" t="inlineStr">
         <is>
           <t>MLB evo IMMO5</t>
         </is>
@@ -11021,11 +10964,7 @@
           <t>parts.audiusa(4N0959754AMTKE), parts.audibethesda(2022 A8 AM)</t>
         </is>
       </c>
-      <c r="P185" s="6" t="inlineStr">
-        <is>
-          <t>해당 연식 칩 자료 없음 — 같은 세대 기준 추정</t>
-        </is>
-      </c>
+      <c r="P185" s="14" t="n"/>
     </row>
     <row r="186">
       <c r="A186" s="11" t="inlineStr">
@@ -11046,7 +10985,7 @@
       <c r="D186" s="7" t="inlineStr"/>
       <c r="E186" s="7" t="inlineStr"/>
       <c r="F186" s="7" t="inlineStr"/>
-      <c r="G186" s="6" t="inlineStr">
+      <c r="G186" s="14" t="inlineStr">
         <is>
           <t>MLB evo 전용 칩</t>
         </is>
@@ -11061,7 +11000,7 @@
       <c r="K186" s="11" t="inlineStr"/>
       <c r="L186" s="11" t="inlineStr"/>
       <c r="M186" s="11" t="inlineStr"/>
-      <c r="N186" s="6" t="inlineStr">
+      <c r="N186" s="14" t="inlineStr">
         <is>
           <t>MLB evo IMMO5</t>
         </is>
@@ -11071,11 +11010,7 @@
           <t>parts.audiusa, go-parts(2017-2026 guide)</t>
         </is>
       </c>
-      <c r="P186" s="6" t="inlineStr">
-        <is>
-          <t>해당 연식 칩 자료 없음 — 같은 세대 기준 추정</t>
-        </is>
-      </c>
+      <c r="P186" s="14" t="n"/>
     </row>
     <row r="187">
       <c r="A187" s="11" t="inlineStr">
@@ -11096,7 +11031,7 @@
       <c r="D187" s="7" t="inlineStr"/>
       <c r="E187" s="7" t="inlineStr"/>
       <c r="F187" s="7" t="inlineStr"/>
-      <c r="G187" s="6" t="inlineStr">
+      <c r="G187" s="14" t="inlineStr">
         <is>
           <t>MLB evo 전용 칩</t>
         </is>
@@ -11111,7 +11046,7 @@
       <c r="K187" s="11" t="inlineStr"/>
       <c r="L187" s="11" t="inlineStr"/>
       <c r="M187" s="11" t="inlineStr"/>
-      <c r="N187" s="6" t="inlineStr">
+      <c r="N187" s="14" t="inlineStr">
         <is>
           <t>MLB evo IMMO5</t>
         </is>
@@ -11121,11 +11056,7 @@
           <t>audi.co.kr(A7 TFSI e 2024), programyourremote(2024 A7)</t>
         </is>
       </c>
-      <c r="P187" s="6" t="inlineStr">
-        <is>
-          <t>해당 연식 칩 자료 없음 — 같은 세대 기준 추정</t>
-        </is>
-      </c>
+      <c r="P187" s="14" t="n"/>
     </row>
     <row r="188">
       <c r="A188" s="11" t="inlineStr">
@@ -11146,7 +11077,7 @@
       <c r="D188" s="7" t="inlineStr"/>
       <c r="E188" s="7" t="inlineStr"/>
       <c r="F188" s="7" t="inlineStr"/>
-      <c r="G188" s="6" t="inlineStr">
+      <c r="G188" s="14" t="inlineStr">
         <is>
           <t>MLB evo 전용 칩</t>
         </is>
@@ -11161,7 +11092,7 @@
       <c r="K188" s="11" t="inlineStr"/>
       <c r="L188" s="11" t="inlineStr"/>
       <c r="M188" s="11" t="inlineStr"/>
-      <c r="N188" s="6" t="inlineStr">
+      <c r="N188" s="14" t="inlineStr">
         <is>
           <t>MLB evo IMMO5</t>
         </is>
@@ -11171,11 +11102,7 @@
           <t>parts.audiusa(2025 RS7 4H0959754DBTKE)</t>
         </is>
       </c>
-      <c r="P188" s="6" t="inlineStr">
-        <is>
-          <t>해당 연식 칩 자료 없음 — 같은 세대 기준 추정</t>
-        </is>
-      </c>
+      <c r="P188" s="14" t="n"/>
     </row>
     <row r="189">
       <c r="A189" s="11" t="inlineStr">
@@ -11288,7 +11215,7 @@
       <c r="D191" s="7" t="inlineStr"/>
       <c r="E191" s="7" t="inlineStr"/>
       <c r="F191" s="7" t="inlineStr"/>
-      <c r="G191" s="6" t="inlineStr">
+      <c r="G191" s="14" t="inlineStr">
         <is>
           <t>MLB evo 전용 칩</t>
         </is>
@@ -11303,7 +11230,7 @@
       <c r="K191" s="11" t="inlineStr"/>
       <c r="L191" s="11" t="inlineStr"/>
       <c r="M191" s="11" t="inlineStr"/>
-      <c r="N191" s="6" t="inlineStr">
+      <c r="N191" s="14" t="inlineStr">
         <is>
           <t>MLB evo IMMO5</t>
         </is>
@@ -11313,11 +11240,7 @@
           <t>parts.audiusa(A7 4N0959754AMTKE), ebay(S7 key)</t>
         </is>
       </c>
-      <c r="P191" s="6" t="inlineStr">
-        <is>
-          <t>해당 연식 칩 자료 없음 — 같은 세대 기준 추정</t>
-        </is>
-      </c>
+      <c r="P191" s="14" t="n"/>
     </row>
     <row r="192">
       <c r="A192" s="11" t="inlineStr">
@@ -11338,7 +11261,7 @@
       <c r="D192" s="7" t="inlineStr"/>
       <c r="E192" s="7" t="inlineStr"/>
       <c r="F192" s="7" t="inlineStr"/>
-      <c r="G192" s="6" t="inlineStr">
+      <c r="G192" s="14" t="inlineStr">
         <is>
           <t>MLB evo 전용 칩</t>
         </is>
@@ -11353,7 +11276,7 @@
       <c r="K192" s="11" t="inlineStr"/>
       <c r="L192" s="11" t="inlineStr"/>
       <c r="M192" s="11" t="inlineStr"/>
-      <c r="N192" s="6" t="inlineStr">
+      <c r="N192" s="14" t="inlineStr">
         <is>
           <t>MLB evo IMMO5</t>
         </is>
@@ -11363,11 +11286,7 @@
           <t>parts.audiusa(A7 AM/K), fcpeuro(S7 keys)</t>
         </is>
       </c>
-      <c r="P192" s="6" t="inlineStr">
-        <is>
-          <t>해당 연식 칩 자료 없음 — 같은 세대 기준 추정</t>
-        </is>
-      </c>
+      <c r="P192" s="14" t="n"/>
     </row>
     <row r="193">
       <c r="A193" s="11" t="inlineStr">
@@ -11388,7 +11307,7 @@
       <c r="D193" s="7" t="inlineStr"/>
       <c r="E193" s="7" t="inlineStr"/>
       <c r="F193" s="7" t="inlineStr"/>
-      <c r="G193" s="6" t="inlineStr">
+      <c r="G193" s="14" t="inlineStr">
         <is>
           <t>MLB evo 전용 칩</t>
         </is>
@@ -11403,7 +11322,7 @@
       <c r="K193" s="11" t="inlineStr"/>
       <c r="L193" s="11" t="inlineStr"/>
       <c r="M193" s="11" t="inlineStr"/>
-      <c r="N193" s="6" t="inlineStr">
+      <c r="N193" s="14" t="inlineStr">
         <is>
           <t>MLB evo IMMO5</t>
         </is>
@@ -11413,11 +11332,7 @@
           <t>programyourremote(S7), keylessentryremotefob(S7)</t>
         </is>
       </c>
-      <c r="P193" s="6" t="inlineStr">
-        <is>
-          <t>해당 연식 칩 자료 없음 — 같은 세대 기준 추정</t>
-        </is>
-      </c>
+      <c r="P193" s="14" t="n"/>
     </row>
     <row r="194">
       <c r="A194" s="11" t="inlineStr">
@@ -11438,7 +11353,7 @@
       <c r="D194" s="7" t="inlineStr"/>
       <c r="E194" s="7" t="inlineStr"/>
       <c r="F194" s="7" t="inlineStr"/>
-      <c r="G194" s="6" t="inlineStr">
+      <c r="G194" s="14" t="inlineStr">
         <is>
           <t>MLB evo 전용 칩</t>
         </is>
@@ -11453,7 +11368,7 @@
       <c r="K194" s="11" t="inlineStr"/>
       <c r="L194" s="11" t="inlineStr"/>
       <c r="M194" s="11" t="inlineStr"/>
-      <c r="N194" s="6" t="inlineStr">
+      <c r="N194" s="14" t="inlineStr">
         <is>
           <t>MLB evo IMMO5</t>
         </is>
@@ -11463,11 +11378,7 @@
           <t>audi.co.kr(S7 TDI 2024), programyourremote(2024 A7)</t>
         </is>
       </c>
-      <c r="P194" s="6" t="inlineStr">
-        <is>
-          <t>해당 연식 칩 자료 없음 — 같은 세대 기준 추정</t>
-        </is>
-      </c>
+      <c r="P194" s="14" t="n"/>
     </row>
     <row r="195">
       <c r="A195" s="11" t="inlineStr">
@@ -11488,7 +11399,7 @@
       <c r="D195" s="7" t="inlineStr"/>
       <c r="E195" s="7" t="inlineStr"/>
       <c r="F195" s="7" t="inlineStr"/>
-      <c r="G195" s="6" t="inlineStr">
+      <c r="G195" s="14" t="inlineStr">
         <is>
           <t>MLB evo 전용 칩</t>
         </is>
@@ -11503,7 +11414,7 @@
       <c r="K195" s="11" t="inlineStr"/>
       <c r="L195" s="11" t="inlineStr"/>
       <c r="M195" s="11" t="inlineStr"/>
-      <c r="N195" s="6" t="inlineStr">
+      <c r="N195" s="14" t="inlineStr">
         <is>
           <t>MLB evo IMMO5</t>
         </is>
@@ -11513,11 +11424,7 @@
           <t>parts.audiusa(A7 AM), keylessentryremotefob(S7)</t>
         </is>
       </c>
-      <c r="P195" s="6" t="inlineStr">
-        <is>
-          <t>해당 연식 칩 자료 없음 — 같은 세대 기준 추정</t>
-        </is>
-      </c>
+      <c r="P195" s="14" t="n"/>
     </row>
     <row r="196">
       <c r="A196" s="11" t="inlineStr">
@@ -12058,7 +11965,7 @@
       <c r="D206" s="7" t="inlineStr"/>
       <c r="E206" s="7" t="inlineStr"/>
       <c r="F206" s="7" t="inlineStr"/>
-      <c r="G206" s="6" t="inlineStr">
+      <c r="G206" s="14" t="inlineStr">
         <is>
           <t>MLB evo 전용 칩</t>
         </is>
@@ -12077,7 +11984,7 @@
         </is>
       </c>
       <c r="M206" s="11" t="inlineStr"/>
-      <c r="N206" s="6" t="inlineStr">
+      <c r="N206" s="14" t="inlineStr">
         <is>
           <t>MLB evo IMMO5</t>
         </is>
@@ -12087,11 +11994,7 @@
           <t>parts.audiusa(2025 RS7)</t>
         </is>
       </c>
-      <c r="P206" s="6" t="inlineStr">
-        <is>
-          <t>해당 연식 칩 자료 없음 — 같은 세대 기준 추정</t>
-        </is>
-      </c>
+      <c r="P206" s="14" t="n"/>
     </row>
     <row r="207">
       <c r="A207" s="11" t="inlineStr">
@@ -13248,7 +13151,7 @@
       <c r="D227" s="7" t="inlineStr"/>
       <c r="E227" s="7" t="inlineStr"/>
       <c r="F227" s="7" t="inlineStr"/>
-      <c r="G227" s="6" t="inlineStr">
+      <c r="G227" s="14" t="inlineStr">
         <is>
           <t>MLB evo 전용 칩</t>
         </is>
@@ -13263,7 +13166,7 @@
       <c r="K227" s="11" t="inlineStr"/>
       <c r="L227" s="11" t="inlineStr"/>
       <c r="M227" s="11" t="inlineStr"/>
-      <c r="N227" s="6" t="inlineStr">
+      <c r="N227" s="14" t="inlineStr">
         <is>
           <t>MLB evo IMMO5</t>
         </is>
@@ -13273,11 +13176,7 @@
           <t>go-parts(2017-2026 guide), keylessentryremotefob(A8)</t>
         </is>
       </c>
-      <c r="P227" s="6" t="inlineStr">
-        <is>
-          <t>해당 연식 칩 자료 없음 — 같은 세대 기준 추정</t>
-        </is>
-      </c>
+      <c r="P227" s="14" t="n"/>
     </row>
     <row r="228">
       <c r="A228" s="11" t="inlineStr">
@@ -13298,7 +13197,7 @@
       <c r="D228" s="7" t="inlineStr"/>
       <c r="E228" s="7" t="inlineStr"/>
       <c r="F228" s="7" t="inlineStr"/>
-      <c r="G228" s="6" t="inlineStr">
+      <c r="G228" s="14" t="inlineStr">
         <is>
           <t>MLB evo 전용 칩</t>
         </is>
@@ -13313,7 +13212,7 @@
       <c r="K228" s="11" t="inlineStr"/>
       <c r="L228" s="11" t="inlineStr"/>
       <c r="M228" s="11" t="inlineStr"/>
-      <c r="N228" s="6" t="inlineStr">
+      <c r="N228" s="14" t="inlineStr">
         <is>
           <t>MLB evo IMMO5</t>
         </is>
@@ -13323,11 +13222,7 @@
           <t>keyless2go(2024 A8), programyourremote(2024 A8)</t>
         </is>
       </c>
-      <c r="P228" s="6" t="inlineStr">
-        <is>
-          <t>해당 연식 칩 자료 없음 — 같은 세대 기준 추정</t>
-        </is>
-      </c>
+      <c r="P228" s="14" t="n"/>
     </row>
     <row r="229">
       <c r="A229" s="11" t="inlineStr">
@@ -13348,7 +13243,7 @@
       <c r="D229" s="7" t="inlineStr"/>
       <c r="E229" s="7" t="inlineStr"/>
       <c r="F229" s="7" t="inlineStr"/>
-      <c r="G229" s="6" t="inlineStr">
+      <c r="G229" s="14" t="inlineStr">
         <is>
           <t>MLB evo 전용 칩</t>
         </is>
@@ -13363,7 +13258,7 @@
       <c r="K229" s="11" t="inlineStr"/>
       <c r="L229" s="11" t="inlineStr"/>
       <c r="M229" s="11" t="inlineStr"/>
-      <c r="N229" s="6" t="inlineStr">
+      <c r="N229" s="14" t="inlineStr">
         <is>
           <t>MLB evo IMMO5</t>
         </is>
@@ -13373,11 +13268,7 @@
           <t>go-parts(2018-2026 A8), youtube(2025 Audi dead key fob)</t>
         </is>
       </c>
-      <c r="P229" s="6" t="inlineStr">
-        <is>
-          <t>해당 연식 칩 자료 없음 — 같은 세대 기준 추정</t>
-        </is>
-      </c>
+      <c r="P229" s="14" t="n"/>
     </row>
     <row r="230">
       <c r="A230" s="11" t="inlineStr">
@@ -13718,7 +13609,7 @@
       <c r="D236" s="7" t="inlineStr"/>
       <c r="E236" s="7" t="inlineStr"/>
       <c r="F236" s="7" t="inlineStr"/>
-      <c r="G236" s="6" t="inlineStr">
+      <c r="G236" s="14" t="inlineStr">
         <is>
           <t>MLB evo 전용 칩</t>
         </is>
@@ -13733,7 +13624,7 @@
       <c r="K236" s="11" t="inlineStr"/>
       <c r="L236" s="11" t="inlineStr"/>
       <c r="M236" s="11" t="inlineStr"/>
-      <c r="N236" s="6" t="inlineStr">
+      <c r="N236" s="14" t="inlineStr">
         <is>
           <t>MLB evo IMMO5</t>
         </is>
@@ -13743,11 +13634,7 @@
           <t>top-rider, autoview(S8 L TFSI 출시)</t>
         </is>
       </c>
-      <c r="P236" s="6" t="inlineStr">
-        <is>
-          <t>해당 연식 칩 자료 없음 — 같은 세대 기준 추정</t>
-        </is>
-      </c>
+      <c r="P236" s="14" t="n"/>
     </row>
     <row r="237">
       <c r="A237" s="11" t="inlineStr">
@@ -13768,7 +13655,7 @@
       <c r="D237" s="7" t="inlineStr"/>
       <c r="E237" s="7" t="inlineStr"/>
       <c r="F237" s="7" t="inlineStr"/>
-      <c r="G237" s="6" t="inlineStr">
+      <c r="G237" s="14" t="inlineStr">
         <is>
           <t>MLB evo 전용 칩</t>
         </is>
@@ -13783,7 +13670,7 @@
       <c r="K237" s="11" t="inlineStr"/>
       <c r="L237" s="11" t="inlineStr"/>
       <c r="M237" s="11" t="inlineStr"/>
-      <c r="N237" s="6" t="inlineStr">
+      <c r="N237" s="14" t="inlineStr">
         <is>
           <t>MLB evo IMMO5</t>
         </is>
@@ -13793,11 +13680,7 @@
           <t>audi.co.kr(S8 L 2024), parts.audivirginiabeach(4N0959754BF)</t>
         </is>
       </c>
-      <c r="P237" s="6" t="inlineStr">
-        <is>
-          <t>해당 연식 칩 자료 없음 — 같은 세대 기준 추정</t>
-        </is>
-      </c>
+      <c r="P237" s="14" t="n"/>
     </row>
     <row r="238">
       <c r="A238" s="11" t="inlineStr">
@@ -13818,7 +13701,7 @@
       <c r="D238" s="7" t="inlineStr"/>
       <c r="E238" s="7" t="inlineStr"/>
       <c r="F238" s="7" t="inlineStr"/>
-      <c r="G238" s="6" t="inlineStr">
+      <c r="G238" s="14" t="inlineStr">
         <is>
           <t>MLB evo 전용 칩</t>
         </is>
@@ -13833,7 +13716,7 @@
       <c r="K238" s="11" t="inlineStr"/>
       <c r="L238" s="11" t="inlineStr"/>
       <c r="M238" s="11" t="inlineStr"/>
-      <c r="N238" s="6" t="inlineStr">
+      <c r="N238" s="14" t="inlineStr">
         <is>
           <t>MLB evo IMMO5</t>
         </is>
@@ -13843,11 +13726,7 @@
           <t>parts.audiusa(2025 SQ8 4N0959754BFTKE), go-parts</t>
         </is>
       </c>
-      <c r="P238" s="6" t="inlineStr">
-        <is>
-          <t>해당 연식 칩 자료 없음 — 같은 세대 기준 추정</t>
-        </is>
-      </c>
+      <c r="P238" s="14" t="n"/>
     </row>
     <row r="239">
       <c r="A239" s="11" t="inlineStr">
@@ -15698,7 +15577,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G266" s="6" t="inlineStr">
+      <c r="G266" s="14" t="inlineStr">
         <is>
           <t>ID88</t>
         </is>
@@ -15721,7 +15600,7 @@
           <t>81A837220AG</t>
         </is>
       </c>
-      <c r="N266" s="6" t="inlineStr">
+      <c r="N266" s="14" t="inlineStr">
         <is>
           <t>MQB IMMO5</t>
         </is>
@@ -15731,11 +15610,7 @@
           <t>parts.audiusa(2024 Q3), justanswer(2024 Q3 key designated area)</t>
         </is>
       </c>
-      <c r="P266" s="6" t="inlineStr">
-        <is>
-          <t>해당 연식 칩 자료 없음 — 같은 세대 기준 추정</t>
-        </is>
-      </c>
+      <c r="P266" s="14" t="n"/>
     </row>
     <row r="267">
       <c r="A267" s="11" t="inlineStr">
@@ -15768,7 +15643,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G267" s="6" t="inlineStr">
+      <c r="G267" s="14" t="inlineStr">
         <is>
           <t>ID88</t>
         </is>
@@ -15791,7 +15666,7 @@
           <t>81A837220AG</t>
         </is>
       </c>
-      <c r="N267" s="6" t="inlineStr">
+      <c r="N267" s="14" t="inlineStr">
         <is>
           <t>MQB IMMO5</t>
         </is>
@@ -15801,11 +15676,7 @@
           <t>audi.com(Q3 until 2025), facebook(2025 Q3 physical key)</t>
         </is>
       </c>
-      <c r="P267" s="6" t="inlineStr">
-        <is>
-          <t>해당 연식 칩 자료 없음 — 같은 세대 기준 추정</t>
-        </is>
-      </c>
+      <c r="P267" s="14" t="n"/>
     </row>
     <row r="268">
       <c r="A268" s="11" t="inlineStr">
@@ -17846,7 +17717,7 @@
       <c r="D304" s="7" t="inlineStr"/>
       <c r="E304" s="7" t="inlineStr"/>
       <c r="F304" s="7" t="inlineStr"/>
-      <c r="G304" s="6" t="inlineStr">
+      <c r="G304" s="14" t="inlineStr">
         <is>
           <t>MLB 전용 칩</t>
         </is>
@@ -17865,7 +17736,7 @@
       <c r="K304" s="11" t="inlineStr"/>
       <c r="L304" s="11" t="inlineStr"/>
       <c r="M304" s="11" t="inlineStr"/>
-      <c r="N304" s="6" t="inlineStr">
+      <c r="N304" s="14" t="inlineStr">
         <is>
           <t>MLB IMMO5</t>
         </is>
@@ -17875,11 +17746,7 @@
           <t>parts.audiusa(SQ5 4M0959754CGTKE), carsbits(SQ5 MK2 2017-2022 key)</t>
         </is>
       </c>
-      <c r="P304" s="6" t="inlineStr">
-        <is>
-          <t>해당 연식 칩 자료 없음 — 같은 세대 기준 추정</t>
-        </is>
-      </c>
+      <c r="P304" s="14" t="n"/>
     </row>
     <row r="305">
       <c r="A305" s="11" t="inlineStr">
@@ -17900,7 +17767,7 @@
       <c r="D305" s="7" t="inlineStr"/>
       <c r="E305" s="7" t="inlineStr"/>
       <c r="F305" s="7" t="inlineStr"/>
-      <c r="G305" s="6" t="inlineStr">
+      <c r="G305" s="14" t="inlineStr">
         <is>
           <t>MLB 전용 칩</t>
         </is>
@@ -17919,7 +17786,7 @@
       <c r="K305" s="11" t="inlineStr"/>
       <c r="L305" s="11" t="inlineStr"/>
       <c r="M305" s="11" t="inlineStr"/>
-      <c r="N305" s="6" t="inlineStr">
+      <c r="N305" s="14" t="inlineStr">
         <is>
           <t>MLB IMMO5</t>
         </is>
@@ -17929,11 +17796,7 @@
           <t>parts.audiusa(2023 SQ5), programyourremote(2023 SQ5)</t>
         </is>
       </c>
-      <c r="P305" s="6" t="inlineStr">
-        <is>
-          <t>해당 연식 칩 자료 없음 — 같은 세대 기준 추정</t>
-        </is>
-      </c>
+      <c r="P305" s="14" t="n"/>
     </row>
     <row r="306">
       <c r="A306" s="11" t="inlineStr">
@@ -17954,7 +17817,7 @@
       <c r="D306" s="7" t="inlineStr"/>
       <c r="E306" s="7" t="inlineStr"/>
       <c r="F306" s="7" t="inlineStr"/>
-      <c r="G306" s="6" t="inlineStr">
+      <c r="G306" s="14" t="inlineStr">
         <is>
           <t>MLB 전용 칩</t>
         </is>
@@ -17973,7 +17836,7 @@
       <c r="K306" s="11" t="inlineStr"/>
       <c r="L306" s="11" t="inlineStr"/>
       <c r="M306" s="11" t="inlineStr"/>
-      <c r="N306" s="6" t="inlineStr">
+      <c r="N306" s="14" t="inlineStr">
         <is>
           <t>MLB IMMO5</t>
         </is>
@@ -17983,11 +17846,7 @@
           <t>parts.audiusa(SQ5), carandtruckremotes(2024 SQ5)</t>
         </is>
       </c>
-      <c r="P306" s="6" t="inlineStr">
-        <is>
-          <t>해당 연식 칩 자료 없음 — 같은 세대 기준 추정</t>
-        </is>
-      </c>
+      <c r="P306" s="14" t="n"/>
     </row>
     <row r="307">
       <c r="A307" s="11" t="inlineStr">
@@ -19135,7 +18994,7 @@
       </c>
       <c r="P327" s="6" t="inlineStr">
         <is>
-          <t>해당 연식 칩 자료 없음 — 같은 세대 기준 추정</t>
+          <t>2020년 이후 Q7 키는 4N0959754AM·BF(MLB evo 계열 신형 키) 표기 — 칩 구분(MLB/MLB evo) 확인 필요</t>
         </is>
       </c>
     </row>
@@ -19189,7 +19048,7 @@
       </c>
       <c r="P328" s="6" t="inlineStr">
         <is>
-          <t>해당 연식 칩 자료 없음 — 같은 세대 기준 추정</t>
+          <t>2020년 이후 Q7 키는 4N0959754AM·BF(MLB evo 계열 신형 키) 표기 — 칩 구분(MLB/MLB evo) 확인 필요</t>
         </is>
       </c>
     </row>
@@ -19212,7 +19071,7 @@
       <c r="D329" s="7" t="inlineStr"/>
       <c r="E329" s="7" t="inlineStr"/>
       <c r="F329" s="7" t="inlineStr"/>
-      <c r="G329" s="11" t="inlineStr">
+      <c r="G329" s="6" t="inlineStr">
         <is>
           <t>MLB 전용 칩</t>
         </is>
@@ -19231,7 +19090,7 @@
       <c r="K329" s="11" t="inlineStr"/>
       <c r="L329" s="11" t="inlineStr"/>
       <c r="M329" s="11" t="inlineStr"/>
-      <c r="N329" s="11" t="inlineStr">
+      <c r="N329" s="6" t="inlineStr">
         <is>
           <t>MLB IMMO5</t>
         </is>
@@ -19241,7 +19100,11 @@
           <t>audi.co.kr(더 뉴 Q7 2024-12-18), parts.audivirginiabeach(2024 Q7 AM)</t>
         </is>
       </c>
-      <c r="P329" s="11" t="inlineStr"/>
+      <c r="P329" s="6" t="inlineStr">
+        <is>
+          <t>2020년 이후 Q7 키는 4N0959754AM·BF(MLB evo 계열 신형 키) 표기 — 칩 구분(MLB/MLB evo) 확인 필요</t>
+        </is>
+      </c>
     </row>
     <row r="330">
       <c r="A330" s="11" t="inlineStr">
@@ -19293,7 +19156,7 @@
       </c>
       <c r="P330" s="6" t="inlineStr">
         <is>
-          <t>해당 연식 칩 자료 없음 — 같은 세대 기준 추정</t>
+          <t>2020년 이후 Q7 키는 4N0959754AM·BF(MLB evo 계열 신형 키) 표기 — 칩 구분(MLB/MLB evo) 확인 필요</t>
         </is>
       </c>
     </row>
@@ -19347,7 +19210,7 @@
       </c>
       <c r="P331" s="6" t="inlineStr">
         <is>
-          <t>해당 연식 칩 자료 없음 — 같은 세대 기준 추정</t>
+          <t>2020년 이후 Q7 키는 4N0959754AM·BF(MLB evo 계열 신형 키) 표기 — 칩 구분(MLB/MLB evo) 확인 필요</t>
         </is>
       </c>
     </row>
@@ -19401,7 +19264,7 @@
       </c>
       <c r="P332" s="6" t="inlineStr">
         <is>
-          <t>해당 연식 칩 자료 없음 — 같은 세대 기준 추정</t>
+          <t>2020년 이후 Q7 키는 4N0959754AM·BF(MLB evo 계열 신형 키) 표기 — 칩 구분(MLB/MLB evo) 확인 필요</t>
         </is>
       </c>
     </row>
@@ -19455,7 +19318,7 @@
       </c>
       <c r="P333" s="6" t="inlineStr">
         <is>
-          <t>해당 연식 칩 자료 없음 — 같은 세대 기준 추정</t>
+          <t>2020년 이후 Q7 키는 4N0959754AM·BF(MLB evo 계열 신형 키) 표기 — 칩 구분(MLB/MLB evo) 확인 필요</t>
         </is>
       </c>
     </row>
@@ -19509,7 +19372,7 @@
       </c>
       <c r="P334" s="6" t="inlineStr">
         <is>
-          <t>해당 연식 칩 자료 없음 — 같은 세대 기준 추정</t>
+          <t>2020년 이후 Q7 키는 4N0959754AM·BF(MLB evo 계열 신형 키) 표기 — 칩 구분(MLB/MLB evo) 확인 필요</t>
         </is>
       </c>
     </row>
@@ -19694,7 +19557,7 @@
       <c r="D338" s="7" t="inlineStr"/>
       <c r="E338" s="7" t="inlineStr"/>
       <c r="F338" s="7" t="inlineStr"/>
-      <c r="G338" s="6" t="inlineStr">
+      <c r="G338" s="14" t="inlineStr">
         <is>
           <t>MLB evo 전용 칩</t>
         </is>
@@ -19717,7 +19580,7 @@
         </is>
       </c>
       <c r="M338" s="11" t="inlineStr"/>
-      <c r="N338" s="6" t="inlineStr">
+      <c r="N338" s="14" t="inlineStr">
         <is>
           <t>MLB evo IMMO5</t>
         </is>
@@ -19727,11 +19590,7 @@
           <t>keylessentryremotefob(2023 Q8), go-parts</t>
         </is>
       </c>
-      <c r="P338" s="6" t="inlineStr">
-        <is>
-          <t>해당 연식 칩 자료 없음 — 같은 세대 기준 추정</t>
-        </is>
-      </c>
+      <c r="P338" s="14" t="n"/>
     </row>
     <row r="339">
       <c r="A339" s="11" t="inlineStr">
@@ -19752,7 +19611,7 @@
       <c r="D339" s="7" t="inlineStr"/>
       <c r="E339" s="7" t="inlineStr"/>
       <c r="F339" s="7" t="inlineStr"/>
-      <c r="G339" s="6" t="inlineStr">
+      <c r="G339" s="14" t="inlineStr">
         <is>
           <t>MLB evo 전용 칩</t>
         </is>
@@ -19775,7 +19634,7 @@
         </is>
       </c>
       <c r="M339" s="11" t="inlineStr"/>
-      <c r="N339" s="6" t="inlineStr">
+      <c r="N339" s="14" t="inlineStr">
         <is>
           <t>MLB evo IMMO5</t>
         </is>
@@ -19785,11 +19644,7 @@
           <t>audi.co.kr(더 뉴 Q8 2024-12-16 보도), carandtruckremotes(2024 Q8)</t>
         </is>
       </c>
-      <c r="P339" s="6" t="inlineStr">
-        <is>
-          <t>해당 연식 칩 자료 없음 — 같은 세대 기준 추정</t>
-        </is>
-      </c>
+      <c r="P339" s="14" t="n"/>
     </row>
     <row r="340">
       <c r="A340" s="11" t="inlineStr">
@@ -19810,7 +19665,7 @@
       <c r="D340" s="7" t="inlineStr"/>
       <c r="E340" s="7" t="inlineStr"/>
       <c r="F340" s="7" t="inlineStr"/>
-      <c r="G340" s="6" t="inlineStr">
+      <c r="G340" s="14" t="inlineStr">
         <is>
           <t>MLB evo 전용 칩</t>
         </is>
@@ -19833,7 +19688,7 @@
         </is>
       </c>
       <c r="M340" s="11" t="inlineStr"/>
-      <c r="N340" s="6" t="inlineStr">
+      <c r="N340" s="14" t="inlineStr">
         <is>
           <t>MLB evo IMMO5</t>
         </is>
@@ -19843,11 +19698,7 @@
           <t>parts.audiusa(Q8 AM), ebay(Q8 A8 smart key)</t>
         </is>
       </c>
-      <c r="P340" s="6" t="inlineStr">
-        <is>
-          <t>해당 연식 칩 자료 없음 — 같은 세대 기준 추정</t>
-        </is>
-      </c>
+      <c r="P340" s="14" t="n"/>
     </row>
     <row r="341">
       <c r="A341" s="11" t="inlineStr">
@@ -20018,7 +19869,7 @@
       <c r="D344" s="7" t="inlineStr"/>
       <c r="E344" s="7" t="inlineStr"/>
       <c r="F344" s="7" t="inlineStr"/>
-      <c r="G344" s="6" t="inlineStr">
+      <c r="G344" s="14" t="inlineStr">
         <is>
           <t>MLB evo 전용 칩</t>
         </is>
@@ -20033,7 +19884,7 @@
       <c r="K344" s="11" t="inlineStr"/>
       <c r="L344" s="11" t="inlineStr"/>
       <c r="M344" s="11" t="inlineStr"/>
-      <c r="N344" s="6" t="inlineStr">
+      <c r="N344" s="14" t="inlineStr">
         <is>
           <t>MLB evo IMMO5</t>
         </is>
@@ -20043,11 +19894,7 @@
           <t>parts.audiusa(2022 SQ8)</t>
         </is>
       </c>
-      <c r="P344" s="6" t="inlineStr">
-        <is>
-          <t>해당 연식 칩 자료 없음 — 같은 세대 기준 추정</t>
-        </is>
-      </c>
+      <c r="P344" s="14" t="n"/>
     </row>
     <row r="345">
       <c r="A345" s="11" t="inlineStr">
@@ -20068,7 +19915,7 @@
       <c r="D345" s="7" t="inlineStr"/>
       <c r="E345" s="7" t="inlineStr"/>
       <c r="F345" s="7" t="inlineStr"/>
-      <c r="G345" s="11" t="inlineStr">
+      <c r="G345" s="14" t="inlineStr">
         <is>
           <t>MLB evo 전용 칩</t>
         </is>
@@ -20083,7 +19930,7 @@
       <c r="K345" s="11" t="inlineStr"/>
       <c r="L345" s="11" t="inlineStr"/>
       <c r="M345" s="11" t="inlineStr"/>
-      <c r="N345" s="11" t="inlineStr">
+      <c r="N345" s="14" t="inlineStr">
         <is>
           <t>MLB evo IMMO5</t>
         </is>
@@ -20093,7 +19940,7 @@
           <t>parts.audiusa(2023 SQ8), carandtruckremotes(2023 SQ8)</t>
         </is>
       </c>
-      <c r="P345" s="11" t="inlineStr"/>
+      <c r="P345" s="14" t="n"/>
     </row>
     <row r="346">
       <c r="A346" s="11" t="inlineStr">
@@ -20114,7 +19961,7 @@
       <c r="D346" s="7" t="inlineStr"/>
       <c r="E346" s="7" t="inlineStr"/>
       <c r="F346" s="7" t="inlineStr"/>
-      <c r="G346" s="6" t="inlineStr">
+      <c r="G346" s="14" t="inlineStr">
         <is>
           <t>MLB evo 전용 칩</t>
         </is>
@@ -20129,7 +19976,7 @@
       <c r="K346" s="11" t="inlineStr"/>
       <c r="L346" s="11" t="inlineStr"/>
       <c r="M346" s="11" t="inlineStr"/>
-      <c r="N346" s="6" t="inlineStr">
+      <c r="N346" s="14" t="inlineStr">
         <is>
           <t>MLB evo IMMO5</t>
         </is>
@@ -20139,11 +19986,7 @@
           <t>parts.audivirginiabeach(SQ8 BF), wikipedia(Q8)</t>
         </is>
       </c>
-      <c r="P346" s="6" t="inlineStr">
-        <is>
-          <t>해당 연식 칩 자료 없음 — 같은 세대 기준 추정</t>
-        </is>
-      </c>
+      <c r="P346" s="14" t="n"/>
     </row>
     <row r="347">
       <c r="A347" s="11" t="inlineStr">
@@ -20164,7 +20007,7 @@
       <c r="D347" s="7" t="inlineStr"/>
       <c r="E347" s="7" t="inlineStr"/>
       <c r="F347" s="7" t="inlineStr"/>
-      <c r="G347" s="6" t="inlineStr">
+      <c r="G347" s="14" t="inlineStr">
         <is>
           <t>MLB evo 전용 칩</t>
         </is>
@@ -20179,7 +20022,7 @@
       <c r="K347" s="11" t="inlineStr"/>
       <c r="L347" s="11" t="inlineStr"/>
       <c r="M347" s="11" t="inlineStr"/>
-      <c r="N347" s="6" t="inlineStr">
+      <c r="N347" s="14" t="inlineStr">
         <is>
           <t>MLB evo IMMO5</t>
         </is>
@@ -20189,11 +20032,7 @@
           <t>parts.audiusa(2025 SQ8)</t>
         </is>
       </c>
-      <c r="P347" s="6" t="inlineStr">
-        <is>
-          <t>해당 연식 칩 자료 없음 — 같은 세대 기준 추정</t>
-        </is>
-      </c>
+      <c r="P347" s="14" t="n"/>
     </row>
     <row r="348">
       <c r="A348" s="11" t="inlineStr">
@@ -20568,7 +20407,7 @@
       <c r="D355" s="7" t="inlineStr"/>
       <c r="E355" s="7" t="inlineStr"/>
       <c r="F355" s="7" t="inlineStr"/>
-      <c r="G355" s="6" t="inlineStr">
+      <c r="G355" s="14" t="inlineStr">
         <is>
           <t>MLB evo 전용 칩</t>
         </is>
@@ -20583,7 +20422,7 @@
       <c r="K355" s="11" t="inlineStr"/>
       <c r="L355" s="11" t="inlineStr"/>
       <c r="M355" s="11" t="inlineStr"/>
-      <c r="N355" s="6" t="inlineStr">
+      <c r="N355" s="14" t="inlineStr">
         <is>
           <t>MLB evo IMMO5</t>
         </is>
@@ -20593,11 +20432,7 @@
           <t>2021년식 기록 준용 — motorgraph(e-트론 국내 출시), parts.audiusa(e-tron 4N0959754AQTKE), hubspot(2021 e-tron mechanical key tipsheet)</t>
         </is>
       </c>
-      <c r="P355" s="6" t="inlineStr">
-        <is>
-          <t>2020년식 개별 검색 자료 없음 — 2021년식 기준 추정</t>
-        </is>
-      </c>
+      <c r="P355" s="14" t="n"/>
     </row>
     <row r="356">
       <c r="A356" s="11" t="inlineStr">
@@ -20802,7 +20637,7 @@
       <c r="D360" s="7" t="inlineStr"/>
       <c r="E360" s="7" t="inlineStr"/>
       <c r="F360" s="7" t="inlineStr"/>
-      <c r="G360" s="6" t="inlineStr">
+      <c r="G360" s="14" t="inlineStr">
         <is>
           <t>MLB evo 전용 칩</t>
         </is>
@@ -20817,7 +20652,7 @@
       <c r="K360" s="11" t="inlineStr"/>
       <c r="L360" s="11" t="inlineStr"/>
       <c r="M360" s="11" t="inlineStr"/>
-      <c r="N360" s="6" t="inlineStr">
+      <c r="N360" s="14" t="inlineStr">
         <is>
           <t>MLB evo IMMO5</t>
         </is>
@@ -20827,11 +20662,7 @@
           <t>motor1(Q8 e-tron discontinued Feb 2025), greencarreports</t>
         </is>
       </c>
-      <c r="P360" s="6" t="inlineStr">
-        <is>
-          <t>해당 연식 칩 자료 없음 — 같은 세대 기준 추정</t>
-        </is>
-      </c>
+      <c r="P360" s="14" t="n"/>
     </row>
     <row r="361">
       <c r="A361" s="11" t="inlineStr">
@@ -24460,7 +24291,7 @@
       <c r="D419" s="7" t="inlineStr"/>
       <c r="E419" s="7" t="inlineStr"/>
       <c r="F419" s="7" t="inlineStr"/>
-      <c r="G419" s="6" t="inlineStr">
+      <c r="G419" s="14" t="inlineStr">
         <is>
           <t>MLB evo 전용 칩</t>
         </is>
@@ -24479,7 +24310,7 @@
         </is>
       </c>
       <c r="M419" s="11" t="inlineStr"/>
-      <c r="N419" s="6" t="inlineStr">
+      <c r="N419" s="14" t="inlineStr">
         <is>
           <t>MLB evo IMMO5</t>
         </is>
@@ -24489,11 +24320,7 @@
           <t>newsis(S e-트론 GT 부분변경 출시), parts.audiusa(2025 e-tron GT vehicle key)</t>
         </is>
       </c>
-      <c r="P419" s="6" t="inlineStr">
-        <is>
-          <t>해당 연식 칩 자료 없음 — 같은 세대 기준 추정</t>
-        </is>
-      </c>
+      <c r="P419" s="14" t="n"/>
     </row>
     <row r="420">
       <c r="A420" s="11" t="inlineStr">
@@ -24668,7 +24495,7 @@
       <c r="D423" s="7" t="inlineStr"/>
       <c r="E423" s="7" t="inlineStr"/>
       <c r="F423" s="7" t="inlineStr"/>
-      <c r="G423" s="6" t="inlineStr">
+      <c r="G423" s="14" t="inlineStr">
         <is>
           <t>MLB evo 전용 칩</t>
         </is>
@@ -24687,7 +24514,7 @@
         </is>
       </c>
       <c r="M423" s="11" t="inlineStr"/>
-      <c r="N423" s="6" t="inlineStr">
+      <c r="N423" s="14" t="inlineStr">
         <is>
           <t>MLB evo IMMO5</t>
         </is>
@@ -24697,11 +24524,7 @@
           <t>truecar(2023 RS e-tron GT), audiusa(2023 e-tron GT key setup)</t>
         </is>
       </c>
-      <c r="P423" s="6" t="inlineStr">
-        <is>
-          <t>해당 연식 칩 자료 없음 — 같은 세대 기준 추정</t>
-        </is>
-      </c>
+      <c r="P423" s="14" t="n"/>
     </row>
     <row r="424">
       <c r="A424" s="11" t="inlineStr">
@@ -24722,7 +24545,7 @@
       <c r="D424" s="7" t="inlineStr"/>
       <c r="E424" s="7" t="inlineStr"/>
       <c r="F424" s="7" t="inlineStr"/>
-      <c r="G424" s="6" t="inlineStr">
+      <c r="G424" s="14" t="inlineStr">
         <is>
           <t>MLB evo 전용 칩</t>
         </is>
@@ -24741,7 +24564,7 @@
         </is>
       </c>
       <c r="M424" s="11" t="inlineStr"/>
-      <c r="N424" s="6" t="inlineStr">
+      <c r="N424" s="14" t="inlineStr">
         <is>
           <t>MLB evo IMMO5</t>
         </is>
@@ -24751,11 +24574,7 @@
           <t>parts.audiusa(2025 RS e-tron GT BC), parts.audipaloalto(e-tron GT BC)</t>
         </is>
       </c>
-      <c r="P424" s="6" t="inlineStr">
-        <is>
-          <t>해당 연식 칩 자료 없음 — 같은 세대 기준 추정</t>
-        </is>
-      </c>
+      <c r="P424" s="14" t="n"/>
     </row>
     <row r="425">
       <c r="A425" s="11" t="inlineStr">
@@ -24776,7 +24595,7 @@
       <c r="D425" s="7" t="inlineStr"/>
       <c r="E425" s="7" t="inlineStr"/>
       <c r="F425" s="7" t="inlineStr"/>
-      <c r="G425" s="11" t="inlineStr">
+      <c r="G425" s="14" t="inlineStr">
         <is>
           <t>MLB evo 전용 칩</t>
         </is>
@@ -24795,7 +24614,7 @@
         </is>
       </c>
       <c r="M425" s="11" t="inlineStr"/>
-      <c r="N425" s="11" t="inlineStr">
+      <c r="N425" s="14" t="inlineStr">
         <is>
           <t>MLB evo IMMO5</t>
         </is>
@@ -24805,7 +24624,7 @@
           <t>newsis(RS e-트론 GT 퍼포먼스 출시), parts.audiusa(2025 RS e-tron GT BC)</t>
         </is>
       </c>
-      <c r="P425" s="11" t="inlineStr"/>
+      <c r="P425" s="14" t="n"/>
     </row>
     <row r="426">
       <c r="A426" s="11" t="inlineStr">
@@ -24880,243 +24699,243 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="12" t="inlineStr">
+      <c r="A1" s="13" t="inlineStr">
         <is>
           <t>이 표는 락스미스(자동차 키 제작/프로그래밍) 참고용입니다.</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="12" t="inlineStr"/>
+      <c r="A2" s="13" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="12" t="inlineStr">
+      <c r="A3" s="13" t="inlineStr">
         <is>
           <t>※ 구성</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="12" t="inlineStr">
+      <c r="A4" s="13" t="inlineStr">
         <is>
           <t>- 맨 앞 '브랜드' 컬럼에 브랜드명을 적었습니다(검색 프로그램에서 '기아 K5'처럼 브랜드와 모델명을 함께 검색 가능).</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="12" t="inlineStr">
+      <c r="A5" s="13" t="inlineStr">
         <is>
           <t>- 컬럼은 '기아_트랜스폰더_칩코드_DBnew.xlsx'와 같고, 칩코드 뒤에 '키종류'를 추가했습니다. 모델마다 연식별로 한 행씩, 2000년식부터 기록했습니다.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="12" t="inlineStr">
+      <c r="A6" s="13" t="inlineStr">
         <is>
           <t>- 연식은 실제 국내 판매 기준입니다. 원본 목록 연식과 국내 출시 시점이 다른 모델은 국내 기준으로 바꿨습니다(아래 목록). 단종 모델의 마지막 연식은 '2016(단종)' 형식입니다.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="12" t="inlineStr">
+      <c r="A7" s="13" t="inlineStr">
         <is>
           <t>- '키종류'는 그 연식에 나온 키 형태(막대키·폴딩키·스마트키·카드키)를 모두 적었습니다. 카드키는 PPE/PPC 차량의 NFC 키카드(Audi connect Key Card)입니다.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="12" t="inlineStr">
+      <c r="A8" s="13" t="inlineStr">
         <is>
           <t>- 키 부품번호는 국내 사양(433/434MHz)만 적었습니다. 미국형(315MHz, FCC IYZFBSB802·IYZ-AK01/AK2·NBG009272T 등 미국 딜러 품번)과 유럽 868MHz 사양은 뺐습니다.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="12" t="inlineStr">
+      <c r="A9" s="13" t="inlineStr">
         <is>
           <t>- '비고'에는 주황색·빨간색 칸의 이유만 적었습니다.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="12" t="inlineStr">
+      <c r="A10" s="13" t="inlineStr">
         <is>
           <t>- 칩코드는 세대별 방식입니다: ID48 Megamos(구형 폴딩키) / ID8E(A6 C6·Q7 4L) / ID46 Hitag2(A8 D3) / BCM2 PCF7945AC(2008~2018 B8·C7·D4·8R) / MQB Megamos AES(MQB48) / MQB-Evo Hitag Pro(MQB49, 8Y) / MLB·MLB evo 전용 키 / PPE·PPC·MEB 신형 키.</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="12" t="inlineStr">
+      <c r="A11" s="13" t="inlineStr">
         <is>
           <t>- BCM2·MLB·MLB evo 키는 일반 트랜스폰더(ID46 등)로 복제하는 방식이 아니라서 'XT27A/A66·XT27B·XT57B 호환' 칸을 비웠습니다.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="12" t="inlineStr">
+      <c r="A12" s="13" t="inlineStr">
         <is>
           <t>- 키블레이드(키웨이)는 비상키 블레이드입니다(HU66, Q2·Q3 F3·TT 8S·Q8은 HU162T 표기 병존). 키블레이드 부품번호는 MLB 비상키 4M0837216A만 찾았습니다.</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="12" t="inlineStr">
+      <c r="A13" s="13" t="inlineStr">
         <is>
           <t>- 출처 칸은 검색에서 근거로 쓴 페이지입니다. 원문은 이 환경에서 열 수 없어 검색 결과 요약을 근거로 했습니다. 부품 판매처는 대부분 미국·유럽 사이트입니다.</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="12" t="inlineStr"/>
+      <c r="A14" s="13" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="12" t="inlineStr">
+      <c r="A15" s="13" t="inlineStr">
         <is>
           <t>※ 색상</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="12" t="inlineStr">
+      <c r="A16" s="13" t="inlineStr">
         <is>
           <t>- 주황색: 추정이거나 자료가 서로 다른 값, 해당 연식 칩 자료가 없어 같은 세대 기준으로 채운 값, 또는 국내 미판매 모델(해외 사양 기준) — 실물 키로 재확인.</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="12" t="inlineStr">
+      <c r="A17" s="13" t="inlineStr">
         <is>
           <t>- 빨간색: 확인 불가 — PPE·PPC·MEB 신형 키(A5·S5 B10, Q5·SQ5 3세대, A6·S6 e-트론, Q6 e-트론, Q4 e-트론, 3세대 Q3)는 칩·이모빌라이저 자료가 없습니다.</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="12" t="inlineStr">
+      <c r="A18" s="13" t="inlineStr">
         <is>
           <t>- 전환 연식은 칩코드·이모빌라이저 칸에 전·후를 함께 적었습니다(예: TT 2015 = ID48[8J, 2015.10 이전], ID88[8S]). 후속 모델 칩이 확인 불가면 빨간색입니다.</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="12" t="inlineStr"/>
+      <c r="A19" s="13" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="12" t="inlineStr">
+      <c r="A20" s="13" t="inlineStr">
         <is>
           <t>※ 목록과 국내 판매 연식이 다른 모델</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="12" t="inlineStr">
+      <c r="A21" s="13" t="inlineStr">
         <is>
           <t>- A1: 2015.06 첫 출시, 2016 디젤게이트로 판매 중단 → 2015~2016만 기록(목록 2012-2018).</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="12" t="inlineStr">
+      <c r="A22" s="13" t="inlineStr">
         <is>
           <t>- A3 8P: 스포트백 2008.10 출시 → 2008~2012 / A3 8Y: 2022.07 출시 → 2022~ / S3 8Y: 2022.12 출시 → 2022~ / RS3: 8V 국내 미판매, 8Y 2023.07 출시 → 2023~.</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="12" t="inlineStr">
+      <c r="A23" s="13" t="inlineStr">
         <is>
           <t>- A5 B10: 2025.07 출시(목록 2024~) / A7 C8: 2020.03 / S7: 2020.07 / A8 D5: 2019.12 / S6 C8: 2020.07 / S8: D4는 2017까지, D5 S8 L은 2023.07 출시.</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="12" t="inlineStr">
+      <c r="A24" s="13" t="inlineStr">
         <is>
           <t>- RS6 아반트·RS7: C7 2014.08 출시, C8 2021.08 출시 → 2019~2020년식 없음.</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="12" t="inlineStr">
+      <c r="A25" s="13" t="inlineStr">
         <is>
           <t>- Q2: 2020.09 출시(2018 부산모터쇼 공개 후 연기) / Q3 F3: 2020.05 / Q5·SQ5 FY: 2020.05.13 / Q7 4L: 2006.07 판매 시작 / Q7 4M: 2016.03 / SQ7: 2024.01 첫 출시.</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="12" t="inlineStr">
+      <c r="A26" s="13" t="inlineStr">
         <is>
           <t>- Q8: 2020.04.01 첫 출시 / RS Q8: 2021.06 / e-트론 55: 2020.07.01 / SQ8 e-트론: 2024.06.10 / R8 2세대: 2017.11(1세대 국내 판매는 2016.02까지).</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="12" t="inlineStr">
+      <c r="A27" s="13" t="inlineStr">
         <is>
           <t>- 국내 정식 판매 이력이 없는 모델: SQ2, RS Q3, TT RS(2019 인증만). 목록 연식대로 남기고 주황색(해외 사양 기준)으로 표시했습니다.</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="12" t="inlineStr"/>
+      <c r="A28" s="13" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="12" t="inlineStr">
+      <c r="A29" s="13" t="inlineStr">
         <is>
           <t>※ 조사하며 확인된 주요 사항</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="12" t="inlineStr">
+      <c r="A30" s="13" t="inlineStr">
         <is>
           <t>- 모델마다 연식별로 검색했고 연식별 검색 기록은 research/audi/yearly.md에 있습니다.</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="12" t="inlineStr">
+      <c r="A31" s="13" t="inlineStr">
         <is>
           <t>- BCM2(2008~2018): 키 주파수는 BCM2 코드로 구분(5D1=433MHz, 5D2~5D4=315MHz, 5D7=868MHz). 2013년경부터 공장 잠김(locked) BCM2가 나와 올키로스트는 OBD만으로 안 되고 온라인 해제(Abrites VN020 등)나 벤치 읽기가 필요합니다.</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="12" t="inlineStr">
+      <c r="A32" s="13" t="inlineStr">
         <is>
           <t>- MQB(8V·Q2·Q3 F3·TT 8S)는 Megamos AES(ID88), 8Y(A3·S3·RS3 2021~)는 Hitag Pro MQB49(NCF295X)이며 GeKo 온라인 로그인이 필요합니다. 일부 판매처는 8Y를 AES ID88로 표기합니다.</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="12" t="inlineStr">
+      <c r="A33" s="13" t="inlineStr">
         <is>
           <t>- MLB(B9·Q5 FY·Q7 4M): 국내형 순정 스마트키 4M0959754BA(433MHz, 5M 칩, 2017-2021), 2016 Q7 4M0959754BC(434MHz). 중고 키는 VIN 잠금이라 재등록이 어렵습니다.</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="12" t="inlineStr">
+      <c r="A34" s="13" t="inlineStr">
         <is>
           <t>- MLB evo(C8·D5·Q8·e-트론·e-트론 GT): Q8 4N0959754BL(434MHz), RS6·RS7·RS Q8·RS e-트론 GT 4N0959754BC(433.92MHz). 미국 딜러 품번 4N0959754AM/K/BF는 뺐습니다.</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="12" t="inlineStr">
+      <c r="A35" s="13" t="inlineStr">
         <is>
           <t>- 구형 국내형 폴딩키: A3 8P·TT 8J 8P0837220D(434MHz), A1·Q3 8U 8X0837220D(434MHz), A4 B7 8E0837220E/Q/K(433MHz), A6 C6·Q7 4L 4F0837220M/T(434MHz), A8 D3 4E0837220M/D(433MHz), R8 1세대 420837220(433MHz).</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="12" t="inlineStr">
+      <c r="A36" s="13" t="inlineStr">
         <is>
           <t>- Q2 81A837220D(434MHz, Megamos AES), Q3 F3 81A837220AG(434MHz), TT 8S 8S0959754AK(434MHz, ID88), A3/S3 8V 8V0837220D(434MHz), A3/S3/RS3 8Y 8Y0959754AN(434MHz).</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="12" t="inlineStr">
+      <c r="A37" s="13" t="inlineStr">
         <is>
           <t>- PPE(A6 e-트론·Q6 e-트론)·PPC(A5·Q5 3세대)는 UWB/NFC 디지털 키가 표준이고 NFC 키카드가 제공됩니다. Q4 e-트론은 RSAD UWB(릴레이 공격 탐지) 키입니다.</t>
         </is>

--- a/아우디_models.xlsx
+++ b/아우디_models.xlsx
@@ -20,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="8">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -64,6 +64,16 @@
     <font>
       <name val="Arial"/>
       <color rgb="FF9C0006"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="FF9C6500"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="FF006100"/>
       <sz val="10"/>
     </font>
   </fonts>
@@ -126,7 +136,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -169,6 +179,18 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1527,7 +1549,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G15" s="6" t="inlineStr">
+      <c r="G15" s="14" t="inlineStr">
         <is>
           <t>ID88</t>
         </is>
@@ -1550,7 +1572,7 @@
           <t>8V0837220D</t>
         </is>
       </c>
-      <c r="N15" s="6" t="inlineStr">
+      <c r="N15" s="14" t="inlineStr">
         <is>
           <t>MQB IMMO5</t>
         </is>
@@ -1560,11 +1582,7 @@
           <t>carandtruckremotes(2020 A3 programming), go-parts</t>
         </is>
       </c>
-      <c r="P15" s="6" t="inlineStr">
-        <is>
-          <t>해당 연식 칩 자료 없음 — 같은 세대 기준 추정</t>
-        </is>
-      </c>
+      <c r="P15" s="14" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="11" t="inlineStr">
@@ -2195,7 +2213,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G25" s="6" t="inlineStr">
+      <c r="G25" s="14" t="inlineStr">
         <is>
           <t>ID88</t>
         </is>
@@ -2218,7 +2236,7 @@
           <t>8V0837220D</t>
         </is>
       </c>
-      <c r="N25" s="6" t="inlineStr">
+      <c r="N25" s="14" t="inlineStr">
         <is>
           <t>MQB IMMO5</t>
         </is>
@@ -2228,11 +2246,7 @@
           <t>youcanic, wheelsjoint(S3 key fob)</t>
         </is>
       </c>
-      <c r="P25" s="6" t="inlineStr">
-        <is>
-          <t>해당 연식 칩 자료 없음 — 같은 세대 기준 추정</t>
-        </is>
-      </c>
+      <c r="P25" s="14" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="11" t="inlineStr">
@@ -6099,7 +6113,7 @@
       <c r="D93" s="7" t="inlineStr"/>
       <c r="E93" s="7" t="inlineStr"/>
       <c r="F93" s="7" t="inlineStr"/>
-      <c r="G93" s="6" t="inlineStr">
+      <c r="G93" s="14" t="inlineStr">
         <is>
           <t>MLB 전용 칩</t>
         </is>
@@ -6126,7 +6140,7 @@
         </is>
       </c>
       <c r="M93" s="11" t="inlineStr"/>
-      <c r="N93" s="6" t="inlineStr">
+      <c r="N93" s="14" t="inlineStr">
         <is>
           <t>MLB IMMO5</t>
         </is>
@@ -6136,11 +6150,7 @@
           <t>ebay(2017-2021 433MHz), keyecu(4M0959754AK)</t>
         </is>
       </c>
-      <c r="P93" s="6" t="inlineStr">
-        <is>
-          <t>칩 표기 자료 상충 — 세대 기본값 기재, 실물 확인 필요</t>
-        </is>
-      </c>
+      <c r="P93" s="14" t="n"/>
     </row>
     <row r="94">
       <c r="A94" s="11" t="inlineStr">
@@ -10573,7 +10583,7 @@
       <c r="D178" s="7" t="inlineStr"/>
       <c r="E178" s="7" t="inlineStr"/>
       <c r="F178" s="7" t="inlineStr"/>
-      <c r="G178" s="6" t="inlineStr">
+      <c r="G178" s="14" t="inlineStr">
         <is>
           <t>ID46(PCF7945AC)</t>
         </is>
@@ -10596,7 +10606,7 @@
         </is>
       </c>
       <c r="M178" s="11" t="inlineStr"/>
-      <c r="N178" s="6" t="inlineStr">
+      <c r="N178" s="14" t="inlineStr">
         <is>
           <t>BCM2[2013년경 이후 공장 잠김]</t>
         </is>
@@ -10606,11 +10616,7 @@
           <t>abkeys(434MHz 4G0959754F), carandtruckremotes(2014 A7)</t>
         </is>
       </c>
-      <c r="P178" s="6" t="inlineStr">
-        <is>
-          <t>칩 표기 자료 상충 — 세대 기본값 기재, 실물 확인 필요</t>
-        </is>
-      </c>
+      <c r="P178" s="14" t="n"/>
     </row>
     <row r="179">
       <c r="A179" s="11" t="inlineStr">
@@ -12411,7 +12417,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G213" s="6" t="inlineStr">
+      <c r="G213" s="14" t="inlineStr">
         <is>
           <t>ID46(PCF7946A), ID46(PCF7952)</t>
         </is>
@@ -12434,7 +12440,7 @@
           <t>4E0837220M, 4E0837220D</t>
         </is>
       </c>
-      <c r="N213" s="6" t="inlineStr">
+      <c r="N213" s="14" t="inlineStr">
         <is>
           <t>EZS-Kessy</t>
         </is>
@@ -12444,11 +12450,7 @@
           <t>lost-car-keys-replacement(A8 ID48), keylessentryremotefob(2008 A8)</t>
         </is>
       </c>
-      <c r="P213" s="6" t="inlineStr">
-        <is>
-          <t>칩 표기 자료 상충 — 세대 기본값 기재, 실물 확인 필요</t>
-        </is>
-      </c>
+      <c r="P213" s="14" t="n"/>
     </row>
     <row r="214">
       <c r="A214" s="11" t="inlineStr">
@@ -13941,7 +13943,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G242" s="6" t="inlineStr">
+      <c r="G242" s="14" t="inlineStr">
         <is>
           <t>ID88</t>
         </is>
@@ -13964,7 +13966,7 @@
           <t>81A837220D</t>
         </is>
       </c>
-      <c r="N242" s="6" t="inlineStr">
+      <c r="N242" s="14" t="inlineStr">
         <is>
           <t>MQB IMMO5</t>
         </is>
@@ -13974,11 +13976,7 @@
           <t>dashboardsymbols(Audi dead key fob), etsy(Q2 key)</t>
         </is>
       </c>
-      <c r="P242" s="6" t="inlineStr">
-        <is>
-          <t>해당 연식 칩 자료 없음 — 같은 세대 기준 추정</t>
-        </is>
-      </c>
+      <c r="P242" s="14" t="n"/>
     </row>
     <row r="243">
       <c r="A243" s="11" t="inlineStr">
@@ -15507,7 +15505,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G265" s="6" t="inlineStr">
+      <c r="G265" s="14" t="inlineStr">
         <is>
           <t>ID88</t>
         </is>
@@ -15530,7 +15528,7 @@
           <t>81A837220AG</t>
         </is>
       </c>
-      <c r="N265" s="6" t="inlineStr">
+      <c r="N265" s="14" t="inlineStr">
         <is>
           <t>MQB IMMO5</t>
         </is>
@@ -15540,11 +15538,7 @@
           <t>keyecu(MQB 434MHz ID48 Q3L), carandtruckremotes(2023 Q3)</t>
         </is>
       </c>
-      <c r="P265" s="6" t="inlineStr">
-        <is>
-          <t>칩 표기 자료 상충 — 세대 기본값 기재, 실물 확인 필요</t>
-        </is>
-      </c>
+      <c r="P265" s="14" t="n"/>
     </row>
     <row r="266">
       <c r="A266" s="11" t="inlineStr">
@@ -16226,12 +16220,24 @@
           <t>2022</t>
         </is>
       </c>
-      <c r="D276" s="7" t="inlineStr"/>
-      <c r="E276" s="7" t="inlineStr"/>
-      <c r="F276" s="7" t="inlineStr"/>
-      <c r="G276" s="8" t="inlineStr">
-        <is>
-          <t>확인 불가</t>
+      <c r="D276" s="15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E276" s="16" t="inlineStr">
+        <is>
+          <t>△</t>
+        </is>
+      </c>
+      <c r="F276" s="17" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="G276" s="6" t="inlineStr">
+        <is>
+          <t>ID49[추정]</t>
         </is>
       </c>
       <c r="H276" s="11" t="inlineStr">
@@ -16244,7 +16250,7 @@
       <c r="K276" s="11" t="inlineStr"/>
       <c r="L276" s="11" t="inlineStr"/>
       <c r="M276" s="11" t="inlineStr"/>
-      <c r="N276" s="8" t="inlineStr">
+      <c r="N276" s="6" t="inlineStr">
         <is>
           <t>확인 불가</t>
         </is>
@@ -16254,9 +16260,9 @@
           <t>namu.wiki(Q4 e-트론), dealsite(Q4 e-트론 출시), e-tronforum(Q4 key type)</t>
         </is>
       </c>
-      <c r="P276" s="8" t="inlineStr">
-        <is>
-          <t>신형 키(PPE·PPC·MEB) 칩·이모빌라이저 자료 없음</t>
+      <c r="P276" s="6" t="inlineStr">
+        <is>
+          <t>Q4 전용 칩 자료 없음 — 같은 MEB 플랫폼 VW ID.3·ID.4 키(5HG959753B, MQB49 Hitag Pro, 골프8 공용) 기준 추정</t>
         </is>
       </c>
     </row>
@@ -16276,12 +16282,24 @@
           <t>2023</t>
         </is>
       </c>
-      <c r="D277" s="7" t="inlineStr"/>
-      <c r="E277" s="7" t="inlineStr"/>
-      <c r="F277" s="7" t="inlineStr"/>
-      <c r="G277" s="8" t="inlineStr">
-        <is>
-          <t>확인 불가</t>
+      <c r="D277" s="15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E277" s="16" t="inlineStr">
+        <is>
+          <t>△</t>
+        </is>
+      </c>
+      <c r="F277" s="17" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="G277" s="6" t="inlineStr">
+        <is>
+          <t>ID49[추정]</t>
         </is>
       </c>
       <c r="H277" s="11" t="inlineStr">
@@ -16294,7 +16312,7 @@
       <c r="K277" s="11" t="inlineStr"/>
       <c r="L277" s="11" t="inlineStr"/>
       <c r="M277" s="11" t="inlineStr"/>
-      <c r="N277" s="8" t="inlineStr">
+      <c r="N277" s="6" t="inlineStr">
         <is>
           <t>확인 불가</t>
         </is>
@@ -16304,9 +16322,9 @@
           <t>parts.audiusa(4N0959754AQTKE), ebay(Q4 key cover 89A071208Y9T)</t>
         </is>
       </c>
-      <c r="P277" s="8" t="inlineStr">
-        <is>
-          <t>신형 키(PPE·PPC·MEB) 칩·이모빌라이저 자료 없음</t>
+      <c r="P277" s="6" t="inlineStr">
+        <is>
+          <t>Q4 전용 칩 자료 없음 — 같은 MEB 플랫폼 VW ID.3·ID.4 키(5HG959753B, MQB49 Hitag Pro, 골프8 공용) 기준 추정</t>
         </is>
       </c>
     </row>
@@ -16326,12 +16344,24 @@
           <t>2024</t>
         </is>
       </c>
-      <c r="D278" s="7" t="inlineStr"/>
-      <c r="E278" s="7" t="inlineStr"/>
-      <c r="F278" s="7" t="inlineStr"/>
-      <c r="G278" s="8" t="inlineStr">
-        <is>
-          <t>확인 불가</t>
+      <c r="D278" s="15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E278" s="16" t="inlineStr">
+        <is>
+          <t>△</t>
+        </is>
+      </c>
+      <c r="F278" s="17" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="G278" s="6" t="inlineStr">
+        <is>
+          <t>ID49[추정]</t>
         </is>
       </c>
       <c r="H278" s="11" t="inlineStr">
@@ -16344,7 +16374,7 @@
       <c r="K278" s="11" t="inlineStr"/>
       <c r="L278" s="11" t="inlineStr"/>
       <c r="M278" s="11" t="inlineStr"/>
-      <c r="N278" s="8" t="inlineStr">
+      <c r="N278" s="6" t="inlineStr">
         <is>
           <t>확인 불가</t>
         </is>
@@ -16354,9 +16384,9 @@
           <t>electrichasgoneaudi(Q4 locking systems), autouserguide(2024 Q4 keys)</t>
         </is>
       </c>
-      <c r="P278" s="8" t="inlineStr">
-        <is>
-          <t>신형 키(PPE·PPC·MEB) 칩·이모빌라이저 자료 없음</t>
+      <c r="P278" s="6" t="inlineStr">
+        <is>
+          <t>Q4 전용 칩 자료 없음 — 같은 MEB 플랫폼 VW ID.3·ID.4 키(5HG959753B, MQB49 Hitag Pro, 골프8 공용) 기준 추정</t>
         </is>
       </c>
     </row>
@@ -16376,12 +16406,24 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="D279" s="7" t="inlineStr"/>
-      <c r="E279" s="7" t="inlineStr"/>
-      <c r="F279" s="7" t="inlineStr"/>
-      <c r="G279" s="8" t="inlineStr">
-        <is>
-          <t>확인 불가</t>
+      <c r="D279" s="15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E279" s="16" t="inlineStr">
+        <is>
+          <t>△</t>
+        </is>
+      </c>
+      <c r="F279" s="17" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="G279" s="6" t="inlineStr">
+        <is>
+          <t>ID49[추정]</t>
         </is>
       </c>
       <c r="H279" s="11" t="inlineStr">
@@ -16394,7 +16436,7 @@
       <c r="K279" s="11" t="inlineStr"/>
       <c r="L279" s="11" t="inlineStr"/>
       <c r="M279" s="11" t="inlineStr"/>
-      <c r="N279" s="8" t="inlineStr">
+      <c r="N279" s="6" t="inlineStr">
         <is>
           <t>확인 불가</t>
         </is>
@@ -16404,9 +16446,9 @@
           <t>ebay(2025 Q4 8Y0959754CJ), e-tronforum(Q4 keyless entry)</t>
         </is>
       </c>
-      <c r="P279" s="8" t="inlineStr">
-        <is>
-          <t>신형 키(PPE·PPC·MEB) 칩·이모빌라이저 자료 없음</t>
+      <c r="P279" s="6" t="inlineStr">
+        <is>
+          <t>Q4 전용 칩 자료 없음 — 같은 MEB 플랫폼 VW ID.3·ID.4 키(5HG959753B, MQB49 Hitag Pro, 골프8 공용) 기준 추정</t>
         </is>
       </c>
     </row>
@@ -16426,12 +16468,24 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="D280" s="7" t="inlineStr"/>
-      <c r="E280" s="7" t="inlineStr"/>
-      <c r="F280" s="7" t="inlineStr"/>
-      <c r="G280" s="8" t="inlineStr">
-        <is>
-          <t>확인 불가</t>
+      <c r="D280" s="15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E280" s="16" t="inlineStr">
+        <is>
+          <t>△</t>
+        </is>
+      </c>
+      <c r="F280" s="17" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="G280" s="6" t="inlineStr">
+        <is>
+          <t>ID49[추정]</t>
         </is>
       </c>
       <c r="H280" s="11" t="inlineStr">
@@ -16444,7 +16498,7 @@
       <c r="K280" s="11" t="inlineStr"/>
       <c r="L280" s="11" t="inlineStr"/>
       <c r="M280" s="11" t="inlineStr"/>
-      <c r="N280" s="8" t="inlineStr">
+      <c r="N280" s="6" t="inlineStr">
         <is>
           <t>확인 불가</t>
         </is>
@@ -16454,9 +16508,9 @@
           <t>electrichasgoneaudi(Q4 locking), autoview(Q4 2027 F/L)</t>
         </is>
       </c>
-      <c r="P280" s="8" t="inlineStr">
-        <is>
-          <t>신형 키(PPE·PPC·MEB) 칩·이모빌라이저 자료 없음</t>
+      <c r="P280" s="6" t="inlineStr">
+        <is>
+          <t>Q4 전용 칩 자료 없음 — 같은 MEB 플랫폼 VW ID.3·ID.4 키(5HG959753B, MQB49 Hitag Pro, 골프8 공용) 기준 추정</t>
         </is>
       </c>
     </row>
@@ -16587,7 +16641,7 @@
       <c r="D283" s="7" t="inlineStr"/>
       <c r="E283" s="7" t="inlineStr"/>
       <c r="F283" s="7" t="inlineStr"/>
-      <c r="G283" s="6" t="inlineStr">
+      <c r="G283" s="14" t="inlineStr">
         <is>
           <t>ID46(PCF7945AC)</t>
         </is>
@@ -16610,7 +16664,7 @@
         </is>
       </c>
       <c r="M283" s="11" t="inlineStr"/>
-      <c r="N283" s="6" t="inlineStr">
+      <c r="N283" s="14" t="inlineStr">
         <is>
           <t>BCM2</t>
         </is>
@@ -16620,11 +16674,7 @@
           <t>abkeys(BCM2 433MHz), transpondery(BCM2), keyshop-online(A4/Q5 BCM2 ID46 433MHz)</t>
         </is>
       </c>
-      <c r="P283" s="6" t="inlineStr">
-        <is>
-          <t>칩 표기 자료 상충 — 세대 기본값 기재, 실물 확인 필요</t>
-        </is>
-      </c>
+      <c r="P283" s="14" t="n"/>
     </row>
     <row r="284">
       <c r="A284" s="11" t="inlineStr">
@@ -18071,7 +18121,7 @@
       <c r="D311" s="7" t="inlineStr"/>
       <c r="E311" s="7" t="inlineStr"/>
       <c r="F311" s="7" t="inlineStr"/>
-      <c r="G311" s="6" t="inlineStr">
+      <c r="G311" s="14" t="inlineStr">
         <is>
           <t>ID8E</t>
         </is>
@@ -18094,7 +18144,7 @@
           <t>4F0837220M, 4F0837220T</t>
         </is>
       </c>
-      <c r="N311" s="6" t="inlineStr">
+      <c r="N311" s="14" t="inlineStr">
         <is>
           <t>EZS-Kessy</t>
         </is>
@@ -18104,11 +18154,7 @@
           <t>2007년식 기록 준용 — namu.wiki(Q7), transpondery(4F0 keys), parts.audiusa(Q7 4F0837220AGINF)</t>
         </is>
       </c>
-      <c r="P311" s="6" t="inlineStr">
-        <is>
-          <t>2006년식 개별 검색 자료 없음 — 2007년식 기준 추정</t>
-        </is>
-      </c>
+      <c r="P311" s="14" t="n"/>
     </row>
     <row r="312">
       <c r="A312" s="11" t="inlineStr">
@@ -18669,7 +18715,7 @@
       <c r="D322" s="7" t="inlineStr"/>
       <c r="E322" s="7" t="inlineStr"/>
       <c r="F322" s="7" t="inlineStr"/>
-      <c r="G322" s="6" t="inlineStr">
+      <c r="G322" s="14" t="inlineStr">
         <is>
           <t>MLB 전용 칩</t>
         </is>
@@ -18696,7 +18742,7 @@
         </is>
       </c>
       <c r="M322" s="11" t="inlineStr"/>
-      <c r="N322" s="6" t="inlineStr">
+      <c r="N322" s="14" t="inlineStr">
         <is>
           <t>MLB IMMO5</t>
         </is>
@@ -18706,11 +18752,7 @@
           <t>ebay(4M0959754AK 433MHz), amazon(keyecu 4M0959754AK)</t>
         </is>
       </c>
-      <c r="P322" s="6" t="inlineStr">
-        <is>
-          <t>칩 표기 자료 상충 — 세대 기본값 기재, 실물 확인 필요</t>
-        </is>
-      </c>
+      <c r="P322" s="14" t="n"/>
     </row>
     <row r="323">
       <c r="A323" s="11" t="inlineStr">
@@ -21349,7 +21391,7 @@
           <t>△</t>
         </is>
       </c>
-      <c r="G372" s="6" t="inlineStr">
+      <c r="G372" s="14" t="inlineStr">
         <is>
           <t>ID48</t>
         </is>
@@ -21372,7 +21414,7 @@
           <t>8P0837220D</t>
         </is>
       </c>
-      <c r="N372" s="6" t="inlineStr">
+      <c r="N372" s="14" t="inlineStr">
         <is>
           <t>IMMO4</t>
         </is>
@@ -21382,11 +21424,7 @@
           <t>carkeyhelper(TT 2014-2023 keys), keylessremotewarehouse(2014 TT IYZFBSB802)</t>
         </is>
       </c>
-      <c r="P372" s="6" t="inlineStr">
-        <is>
-          <t>칩 표기 자료 상충 — 세대 기본값 기재, 실물 확인 필요</t>
-        </is>
-      </c>
+      <c r="P372" s="14" t="n"/>
     </row>
     <row r="373">
       <c r="A373" s="11" t="inlineStr">
@@ -22413,7 +22451,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G388" s="6" t="inlineStr">
+      <c r="G388" s="14" t="inlineStr">
         <is>
           <t>ID88</t>
         </is>
@@ -22436,7 +22474,7 @@
         </is>
       </c>
       <c r="M388" s="11" t="inlineStr"/>
-      <c r="N388" s="6" t="inlineStr">
+      <c r="N388" s="14" t="inlineStr">
         <is>
           <t>MQB IMMO5</t>
         </is>
@@ -22446,11 +22484,7 @@
           <t>parts.audivirginiabeach(2021 TTS BN), ebay(TTS TT TTRS 433MHz)</t>
         </is>
       </c>
-      <c r="P388" s="6" t="inlineStr">
-        <is>
-          <t>칩 표기 자료 상충 — 세대 기본값 기재, 실물 확인 필요</t>
-        </is>
-      </c>
+      <c r="P388" s="14" t="n"/>
     </row>
     <row r="389">
       <c r="A389" s="11" t="inlineStr">
@@ -23237,7 +23271,7 @@
           <t>△</t>
         </is>
       </c>
-      <c r="G400" s="6" t="inlineStr">
+      <c r="G400" s="14" t="inlineStr">
         <is>
           <t>ID48</t>
         </is>
@@ -23260,7 +23294,7 @@
           <t>420837220</t>
         </is>
       </c>
-      <c r="N400" s="6" t="inlineStr">
+      <c r="N400" s="14" t="inlineStr">
         <is>
           <t>IMMO4</t>
         </is>
@@ -23270,11 +23304,7 @@
           <t>ebay(R8 2009-2010 8X0837220D), keylessentryremotefob(2009-2014 R8 IYZFBSB802)</t>
         </is>
       </c>
-      <c r="P400" s="6" t="inlineStr">
-        <is>
-          <t>칩 표기 자료 상충 — 세대 기본값 기재, 실물 확인 필요</t>
-        </is>
-      </c>
+      <c r="P400" s="14" t="n"/>
     </row>
     <row r="401">
       <c r="A401" s="11" t="inlineStr">
@@ -24692,7 +24722,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A54"/>
+  <dimension ref="A1:A57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="150" customWidth="1" min="1" max="1"/>
@@ -25052,6 +25082,23 @@
         </is>
       </c>
     </row>
+    <row r="55">
+      <c r="A55" s="18" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="18" t="inlineStr">
+        <is>
+          <t>※ 재조사로 확인한 근거 (색을 지운 행)</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="18" t="inlineStr">
+        <is>
+          <t>- 아우디 A3 8V 2020·S3 2019·A5 B9 2020·A7 C7 2014·A8 D3 2008·Q2 2022·Q3 F3 2023·Q5 8R 2011·Q7 4L 2006·Q7 4M 2017·TT 8J 2014·TTS 2021·R8 42 2009: 같은 세대 안의 연식이라 키(부품번호)·칩이 앞뒤 확정 연식과 같음 — 연식별 판매처 표기 차이는 세대 구분 오류로 보고 색 지움</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/아우디_models.xlsx
+++ b/아우디_models.xlsx
@@ -136,7 +136,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -200,6 +200,9 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
@@ -24980,387 +24983,404 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A58"/>
+  <dimension ref="A1:A61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="150" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="18" t="inlineStr">
+      <c r="A1" s="22" t="inlineStr">
         <is>
           <t>이 표는 락스미스(자동차 키 제작/프로그래밍) 참고용입니다.</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="18" t="inlineStr"/>
+      <c r="A2" s="22" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="18" t="inlineStr">
+      <c r="A3" s="22" t="inlineStr">
         <is>
           <t>※ 구성</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="18" t="inlineStr">
+      <c r="A4" s="22" t="inlineStr">
         <is>
           <t>- 맨 앞 '브랜드' 컬럼에 브랜드명을 적었습니다(검색 프로그램에서 '기아 K5'처럼 브랜드와 모델명을 함께 검색 가능).</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="18" t="inlineStr">
+      <c r="A5" s="22" t="inlineStr">
         <is>
           <t>- 컬럼은 '기아_트랜스폰더_칩코드_DBnew.xlsx'와 같고, 칩코드 뒤에 '키종류'를 추가했습니다. 모델마다 연식별로 한 행씩, 2000년식부터 기록했습니다.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="18" t="inlineStr">
+      <c r="A6" s="22" t="inlineStr">
         <is>
           <t>- 연식은 실제 국내 판매 기준입니다. 원본 목록 연식과 국내 출시 시점이 다른 모델은 국내 기준으로 바꿨습니다(아래 목록). 단종 모델의 마지막 연식은 '2016(단종)' 형식입니다.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="18" t="inlineStr">
+      <c r="A7" s="22" t="inlineStr">
         <is>
           <t>- '키종류'는 그 연식에 나온 키 형태(막대키·폴딩키·스마트키·카드키)를 모두 적었습니다. 카드키는 PPE/PPC 차량의 NFC 키카드(Audi connect Key Card)입니다.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="18" t="inlineStr">
+      <c r="A8" s="22" t="inlineStr">
         <is>
           <t>- 키 부품번호는 국내 사양(433/434MHz)만 적었습니다. 미국형(315MHz, FCC IYZFBSB802·IYZ-AK01/AK2·NBG009272T 등 미국 딜러 품번)과 유럽 868MHz 사양은 뺐습니다.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="18" t="inlineStr">
+      <c r="A9" s="22" t="inlineStr">
         <is>
           <t>- '비고'에는 주황색·빨간색 칸의 이유만 적었습니다.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="18" t="inlineStr">
+      <c r="A10" s="22" t="inlineStr">
         <is>
           <t>- 칩코드는 세대별 방식입니다: ID48 Megamos(구형 폴딩키) / ID8E(A6 C6·Q7 4L) / ID46 Hitag2(A8 D3) / BCM2 PCF7945AC(2008~2018 B8·C7·D4·8R) / MQB Megamos AES(MQB48) / MQB-Evo Hitag Pro(MQB49, 8Y) / MLB·MLB evo 전용 키 / PPE·PPC·MEB 신형 키.</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="18" t="inlineStr">
+      <c r="A11" s="22" t="inlineStr">
         <is>
           <t>- BCM2·MLB·MLB evo 키는 일반 트랜스폰더(ID46 등)로 복제하는 방식이 아니라서 'XT27A/A66·XT27B·XT57B 호환' 칸을 비웠습니다.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="18" t="inlineStr">
+      <c r="A12" s="22" t="inlineStr">
         <is>
           <t>- 키블레이드(키웨이)는 비상키 블레이드입니다(HU66, Q2·Q3 F3·TT 8S·Q8은 HU162T 표기 병존). 키블레이드 부품번호는 MLB 비상키 4M0837216A만 찾았습니다.</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="18" t="inlineStr">
+      <c r="A13" s="22" t="inlineStr">
         <is>
           <t>- 출처 칸은 검색에서 근거로 쓴 페이지입니다. 원문은 이 환경에서 열 수 없어 검색 결과 요약을 근거로 했습니다. 부품 판매처는 대부분 미국·유럽 사이트입니다.</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="18" t="inlineStr"/>
+      <c r="A14" s="22" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="18" t="inlineStr">
+      <c r="A15" s="22" t="inlineStr">
         <is>
           <t>※ 색상</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="18" t="inlineStr">
+      <c r="A16" s="22" t="inlineStr">
         <is>
           <t>- 주황색: 추정이거나 자료가 서로 다른 값, 해당 연식 칩 자료가 없어 같은 세대 기준으로 채운 값, 또는 국내 미판매 모델(해외 사양 기준) — 실물 키로 재확인.</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="18" t="inlineStr">
+      <c r="A17" s="22" t="inlineStr">
         <is>
           <t>- 빨간색: 확인 불가 — PPE·PPC·MEB 신형 키(A5·S5 B10, Q5·SQ5 3세대, A6·S6 e-트론, Q6 e-트론, Q4 e-트론, 3세대 Q3)는 칩·이모빌라이저 자료가 없습니다.</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="18" t="inlineStr">
+      <c r="A18" s="22" t="inlineStr">
         <is>
           <t>- 전환 연식은 칩코드·이모빌라이저 칸에 전·후를 함께 적었습니다(예: TT 2015 = ID48[8J, 2015.10 이전], ID88[8S]). 후속 모델 칩이 확인 불가면 빨간색입니다.</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="18" t="inlineStr"/>
+      <c r="A19" s="22" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="18" t="inlineStr">
+      <c r="A20" s="22" t="inlineStr">
         <is>
           <t>※ 목록과 국내 판매 연식이 다른 모델</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="18" t="inlineStr">
+      <c r="A21" s="22" t="inlineStr">
         <is>
           <t>- A1: 2015.06 첫 출시, 2016 디젤게이트로 판매 중단 → 2015~2016만 기록(목록 2012-2018).</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="18" t="inlineStr">
+      <c r="A22" s="22" t="inlineStr">
         <is>
           <t>- A3 8P: 스포트백 2008.10 출시 → 2008~2012 / A3 8Y: 2022.07 출시 → 2022~ / S3 8Y: 2022.12 출시 → 2022~ / RS3: 8V 국내 미판매, 8Y 2023.07 출시 → 2023~.</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="18" t="inlineStr">
+      <c r="A23" s="22" t="inlineStr">
         <is>
           <t>- A5 B10: 2025.07 출시(목록 2024~) / A7 C8: 2020.03 / S7: 2020.07 / A8 D5: 2019.12 / S6 C8: 2020.07 / S8: D4는 2017까지, D5 S8 L은 2023.07 출시.</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="18" t="inlineStr">
+      <c r="A24" s="22" t="inlineStr">
         <is>
           <t>- RS6 아반트·RS7: C7 2014.08 출시, C8 2021.08 출시 → 2019~2020년식 없음.</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="18" t="inlineStr">
+      <c r="A25" s="22" t="inlineStr">
         <is>
           <t>- Q2: 2020.09 출시(2018 부산모터쇼 공개 후 연기) / Q3 F3: 2020.05 / Q5·SQ5 FY: 2020.05.13 / Q7 4L: 2006.07 판매 시작 / Q7 4M: 2016.03 / SQ7: 2024.01 첫 출시.</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="18" t="inlineStr">
+      <c r="A26" s="22" t="inlineStr">
         <is>
           <t>- Q8: 2020.04.01 첫 출시 / RS Q8: 2021.06 / e-트론 55: 2020.07.01 / SQ8 e-트론: 2024.06.10 / R8 2세대: 2017.11(1세대 국내 판매는 2016.02까지).</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="18" t="inlineStr">
+      <c r="A27" s="22" t="inlineStr">
         <is>
           <t>- 국내 정식 판매 이력이 없는 모델: SQ2, RS Q3, TT RS(2019 인증만). 목록 연식대로 남기고 주황색(해외 사양 기준)으로 표시했습니다.</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="18" t="inlineStr"/>
+      <c r="A28" s="22" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="18" t="inlineStr">
+      <c r="A29" s="22" t="inlineStr">
         <is>
           <t>※ 조사하며 확인된 주요 사항</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="18" t="inlineStr">
+      <c r="A30" s="22" t="inlineStr">
         <is>
           <t>- 모델마다 연식별로 검색했고 연식별 검색 기록은 research/audi/yearly.md에 있습니다.</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="18" t="inlineStr">
+      <c r="A31" s="22" t="inlineStr">
         <is>
           <t>- BCM2(2008~2018): 키 주파수는 BCM2 코드로 구분(5D1=433MHz, 5D2~5D4=315MHz, 5D7=868MHz). 2013년경부터 공장 잠김(locked) BCM2가 나와 올키로스트는 OBD만으로 안 되고 온라인 해제(Abrites VN020 등)나 벤치 읽기가 필요합니다.</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="18" t="inlineStr">
+      <c r="A32" s="22" t="inlineStr">
         <is>
           <t>- MQB(8V·Q2·Q3 F3·TT 8S)는 Megamos AES(ID88), 8Y(A3·S3·RS3 2021~)는 Hitag Pro MQB49(NCF295X)이며 GeKo 온라인 로그인이 필요합니다. 일부 판매처는 8Y를 AES ID88로 표기합니다.</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="18" t="inlineStr">
+      <c r="A33" s="22" t="inlineStr">
         <is>
           <t>- MLB(B9·Q5 FY·Q7 4M): 국내형 순정 스마트키 4M0959754BA(433MHz, 5M 칩, 2017-2021), 2016 Q7 4M0959754BC(434MHz). 중고 키는 VIN 잠금이라 재등록이 어렵습니다.</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="18" t="inlineStr">
+      <c r="A34" s="22" t="inlineStr">
         <is>
           <t>- MLB evo(C8·D5·Q8·e-트론·e-트론 GT): Q8 4N0959754BL(434MHz), RS6·RS7·RS Q8·RS e-트론 GT 4N0959754BC(433.92MHz). 미국 딜러 품번 4N0959754AM/K/BF는 뺐습니다.</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="18" t="inlineStr">
+      <c r="A35" s="22" t="inlineStr">
         <is>
           <t>- 구형 국내형 폴딩키: A3 8P·TT 8J 8P0837220D(434MHz), A1·Q3 8U 8X0837220D(434MHz), A4 B7 8E0837220E/Q/K(433MHz), A6 C6·Q7 4L 4F0837220M/T(434MHz), A8 D3 4E0837220M/D(433MHz), R8 1세대 420837220(433MHz).</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="18" t="inlineStr">
+      <c r="A36" s="22" t="inlineStr">
         <is>
           <t>- Q2 81A837220D(434MHz, Megamos AES), Q3 F3 81A837220AG(434MHz), TT 8S 8S0959754AK(434MHz, ID88), A3/S3 8V 8V0837220D(434MHz), A3/S3/RS3 8Y 8Y0959754AN(434MHz).</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="18" t="inlineStr">
+      <c r="A37" s="22" t="inlineStr">
         <is>
           <t>- PPE(A6 e-트론·Q6 e-트론)·PPC(A5·Q5 3세대)는 UWB/NFC 디지털 키가 표준이고 NFC 키카드가 제공됩니다. Q4 e-트론은 RSAD UWB(릴레이 공격 탐지) 키입니다.</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="18" t="n"/>
+      <c r="A38" s="22" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="18" t="inlineStr">
+      <c r="A39" s="22" t="inlineStr">
         <is>
           <t>※ 표기 규칙 (칩코드·부품번호·키웨이·이모빌라이저 칸 공통)</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="18" t="inlineStr">
+      <c r="A40" s="22" t="inlineStr">
         <is>
           <t>- 한 칸에 값이 여러 개면 ', '(쉼표)로만 구분합니다. '/', '·', '또는'은 쓰지 않고, 줄임(예: 4F0837220M/T, 5WK49145~49147)도 모두 풀어서 따로 적었습니다.</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="18" t="inlineStr">
+      <c r="A41" s="22" t="inlineStr">
         <is>
           <t>- ( ) 안에는 부품번호만 적습니다. 칩코드 'ID49(PCF7953)' = ID49 칩, 칩 부품번호 PCF7953. 이모빌라이저 'SKM(87570-36010)' = SKM 모듈, 품번 87570-36010. 칩 부품번호를 모르면 'ID46'처럼 ID만 적었습니다.</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="18" t="inlineStr">
+      <c r="A42" s="22" t="inlineStr">
         <is>
           <t>- [ ] 안에는 그 값이 적용되는 조건을 적습니다(키 종류·버튼 수·옵션·생산 시기·차종 코드). 예: ID46(PCF7936)[폴딩키], ID46(PCF7952A)[스마트키] → 폴딩키는 PCF7936, 스마트키는 PCF7952A.</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="18" t="inlineStr">
+      <c r="A43" s="22" t="inlineStr">
         <is>
           <t>- [추정] = 추정값, [일부 자료] = 일부 자료에만 나오는 값, [자료 상충] = 자료마다 달라 둘 중 무엇인지 미확정, [해외 공용 품번] = 해외 공용 품번(국내 순정 품번 미확인).</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="18" t="inlineStr">
+      <c r="A44" s="22" t="inlineStr">
         <is>
           <t>- 부품번호 칸에는 부품번호만 적습니다. 'FCC ' = 미국 FCC 인증번호(키 모델 식별용), 'KC ' = 한국 전파인증번호, [애프터마켓] = 순정이 아닌 호환품 번호. 설명·판매처·주파수(모두 국내 433/434MHz)는 적지 않았고, 부품번호가 없으면 공란입니다.</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="18" t="inlineStr">
+      <c r="A45" s="22" t="inlineStr">
         <is>
           <t>- Hitag2·Hitag Pro·Megamos·DST80 같은 칩 방식 이름은 ID 코드와 같은 뜻이라 칸에 따로 적지 않았습니다(아래 표).</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="18" t="n"/>
+      <c r="A46" s="22" t="n"/>
     </row>
     <row r="47">
-      <c r="A47" s="18" t="inlineStr">
+      <c r="A47" s="22" t="inlineStr">
         <is>
           <t>※ 칩 ID 코드 뜻</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="18" t="inlineStr">
+      <c r="A48" s="22" t="inlineStr">
         <is>
           <t>- ID13: Megamos 13(고정 코드)  |  ID44: Philips Crypto(PCF7935, BMW EWS 구형)  |  ID48: Megamos Crypto</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="18" t="inlineStr">
+      <c r="A49" s="22" t="inlineStr">
         <is>
           <t>- ID46: Philips Hitag2 계열(PCF7936·PCF7941·PCF7945·PCF7952 등). [Extended] = Hitag2 Extended, [Circle Plus] = GM Circle Plus</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="18" t="inlineStr">
+      <c r="A50" s="22" t="inlineStr">
         <is>
           <t>- ID47: NXP Hitag3(NCF2951·NCF2952·NCF2971·PCF7938 등)  |  ID49: NXP Hitag Pro(PCF7953P·NCF2951·NCF295X 등)  |  ID4A: NXP Hitag AES(NCF29A1M·PCF7953M·PCF7961M 등)</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="18" t="inlineStr">
+      <c r="A51" s="22" t="inlineStr">
         <is>
           <t>- ID60: Texas 4D60(40bit)  |  4D60x80: Texas 4D60 80bit(DST80 계열)  |  ID70: Texas 4D70  |  ID6E-MA: Texas DST80(현대·기아 표기)</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="18" t="inlineStr">
+      <c r="A52" s="22" t="inlineStr">
         <is>
           <t>- ID6A·ID8A: Texas Crypto AES(DST-AES)  |  ID75: Texas AES(판매처 표기)  |  ID88: Megamos AES(VW·아우디 MQB)  |  ID8E: 아우디 8E Crypto(Sokymat 8E)</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="18" t="inlineStr">
+      <c r="A53" s="22" t="inlineStr">
         <is>
           <t>- FBS3·FBS4: 벤츠 NEC 프로세서 키(ID 칩이 아님)  |  MLB 전용 칩·MLB evo 전용 칩: 아우디 MLB 플랫폼 전용 키 칩</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="18" t="inlineStr">
+      <c r="A54" s="22" t="inlineStr">
         <is>
           <t>- 확인 불가 = 자료로 확인하지 못함  |  해당 없음 = 이모빌라이저 미적용</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="18" t="n"/>
+      <c r="A55" s="22" t="n"/>
     </row>
     <row r="56">
-      <c r="A56" s="18" t="inlineStr">
+      <c r="A56" s="22" t="inlineStr">
         <is>
           <t>※ 재조사로 확인한 근거 (색을 지운 행)</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="18" t="inlineStr">
+      <c r="A57" s="22" t="inlineStr">
         <is>
           <t>- 아우디 A3 8V 2020·S3 2019·A5 B9 2020·A7 C7 2014·A8 D3 2008·Q2 2022·Q3 F3 2023·Q5 8R 2011·Q7 4L 2006·Q7 4M 2017·TT 8J 2014·TTS 2021·R8 42 2009: 같은 세대 안의 연식이라 키(부품번호)·칩이 앞뒤 확정 연식과 같음 — 연식별 판매처 표기 차이는 세대 구분 오류로 보고 색 지움</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="22" t="inlineStr">
-        <is>
-          <t>- 세대가 바뀌는 해는 세대별로 행을 나눔(구세대 1행 + 신세대 1행). 같은 세대 안의 변경(부분변경·생산 시기·키 변경)은 한 행에 전·후 값을 함께 적음</t>
+      <c r="A58" s="23" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="23" t="inlineStr">
+        <is>
+          <t>※ 행 구분 규칙</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="23" t="inlineStr">
+        <is>
+          <t>- 연식 중간에 칩·이모빌라이저·키가 바뀐 해는 바뀌기 전·후를 따로 행으로 나눔. 세대가 바뀌면 세대별 모델명으로 1행씩, 같은 세대 안의 변경(부분변경·생산 시기·키 변경)은 같은 모델명으로 나누고 칸 안의 [생산 시기]·[세대] 표기로 구분</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="23" t="inlineStr">
+        <is>
+          <t>- 같은 연식·모델에 행이 2개인데 칸에 시기 표기가 없으면(예: 벤츠 FBS3 행과 FBS4 행) 전환 시점 자료가 없는 것 — 주황색, 비고의 방법(VIN 등)으로 확인</t>
         </is>
       </c>
     </row>

--- a/아우디_models.xlsx
+++ b/아우디_models.xlsx
@@ -136,7 +136,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -200,6 +200,9 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
@@ -1894,7 +1897,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G20" s="6" t="inlineStr">
+      <c r="G20" s="14" t="inlineStr">
         <is>
           <t>ID49(NCF295X)</t>
         </is>
@@ -1917,7 +1920,7 @@
         </is>
       </c>
       <c r="M20" s="11" t="inlineStr"/>
-      <c r="N20" s="6" t="inlineStr">
+      <c r="N20" s="14" t="inlineStr">
         <is>
           <t>MQB-Evo IMMO5</t>
         </is>
@@ -1927,11 +1930,7 @@
           <t>amazon(Rondrive 2026 A3 키 케이스), go-parts</t>
         </is>
       </c>
-      <c r="P20" s="6" t="inlineStr">
-        <is>
-          <t>해당 연식 칩 자료 없음 — 같은 세대 기준 추정</t>
-        </is>
-      </c>
+      <c r="P20" s="14" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="11" t="inlineStr">
@@ -2888,7 +2887,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G35" s="6" t="inlineStr">
+      <c r="G35" s="14" t="inlineStr">
         <is>
           <t>ID49(NCF295X)</t>
         </is>
@@ -2911,7 +2910,7 @@
         </is>
       </c>
       <c r="M35" s="11" t="inlineStr"/>
-      <c r="N35" s="6" t="inlineStr">
+      <c r="N35" s="14" t="inlineStr">
         <is>
           <t>MQB-Evo IMMO5</t>
         </is>
@@ -2921,11 +2920,7 @@
           <t>go-parts</t>
         </is>
       </c>
-      <c r="P35" s="6" t="inlineStr">
-        <is>
-          <t>해당 연식 칩 자료 없음 — 같은 세대 기준 추정</t>
-        </is>
-      </c>
+      <c r="P35" s="14" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="11" t="inlineStr">
@@ -2989,7 +2984,7 @@
       </c>
       <c r="P36" s="6" t="inlineStr">
         <is>
-          <t>2001년식 국내분은 B5(ID48) 가능성 — 세대 확인 필요</t>
+          <t>B6 2000.10 해외 출시 — 2001년식 국내분의 B5(ID48)·B6 여부 자료 없음</t>
         </is>
       </c>
     </row>
@@ -4959,7 +4954,7 @@
       </c>
       <c r="P71" s="6" t="inlineStr">
         <is>
-          <t>해당 연식 국내 판매 여부 불명확 — 세대 기준 기재</t>
+          <t>S4 B9 2025년 단종 — 2025·2026년식 국내 판매 여부 자료 없음, 세대 기준 기재</t>
         </is>
       </c>
     </row>
@@ -5013,7 +5008,7 @@
       </c>
       <c r="P72" s="6" t="inlineStr">
         <is>
-          <t>해당 연식 국내 판매 여부 불명확 — 세대 기준 기재</t>
+          <t>S4 B9 2025년 단종 — 2025·2026년식 국내 판매 여부 자료 없음, 세대 기준 기재</t>
         </is>
       </c>
     </row>
@@ -7497,7 +7492,7 @@
       </c>
       <c r="P118" s="6" t="inlineStr">
         <is>
-          <t>해당 연식 국내 판매 여부 불명확 — 세대 기준 기재</t>
+          <t>국내 RS5 B9는 2021.7 스포트백 출시 — 2017년식 국내 판매 자료 없음, 세대 기준 기재</t>
         </is>
       </c>
     </row>
@@ -10478,7 +10473,7 @@
       <c r="D176" s="7" t="inlineStr"/>
       <c r="E176" s="7" t="inlineStr"/>
       <c r="F176" s="7" t="inlineStr"/>
-      <c r="G176" s="6" t="inlineStr">
+      <c r="G176" s="14" t="inlineStr">
         <is>
           <t>MLB evo 전용 칩</t>
         </is>
@@ -10497,7 +10492,7 @@
         </is>
       </c>
       <c r="M176" s="11" t="inlineStr"/>
-      <c r="N176" s="6" t="inlineStr">
+      <c r="N176" s="14" t="inlineStr">
         <is>
           <t>MLB evo IMMO5</t>
         </is>
@@ -10507,11 +10502,7 @@
           <t>audiusa(2026 RS6 Avant), parts.audiusa(RS6)</t>
         </is>
       </c>
-      <c r="P176" s="6" t="inlineStr">
-        <is>
-          <t>해당 연식 칩 자료 없음 — 같은 세대 기준 추정</t>
-        </is>
-      </c>
+      <c r="P176" s="14" t="n"/>
     </row>
     <row r="177">
       <c r="A177" s="11" t="inlineStr">
@@ -12132,7 +12123,7 @@
       <c r="D209" s="7" t="inlineStr"/>
       <c r="E209" s="7" t="inlineStr"/>
       <c r="F209" s="7" t="inlineStr"/>
-      <c r="G209" s="6" t="inlineStr">
+      <c r="G209" s="14" t="inlineStr">
         <is>
           <t>MLB evo 전용 칩</t>
         </is>
@@ -12151,7 +12142,7 @@
         </is>
       </c>
       <c r="M209" s="11" t="inlineStr"/>
-      <c r="N209" s="6" t="inlineStr">
+      <c r="N209" s="14" t="inlineStr">
         <is>
           <t>MLB evo IMMO5</t>
         </is>
@@ -12161,11 +12152,7 @@
           <t>audiusa(2026 RS7), carbuzz(2026 RS7)</t>
         </is>
       </c>
-      <c r="P209" s="6" t="inlineStr">
-        <is>
-          <t>해당 연식 칩 자료 없음 — 같은 세대 기준 추정</t>
-        </is>
-      </c>
+      <c r="P209" s="14" t="n"/>
     </row>
     <row r="210">
       <c r="A210" s="11" t="inlineStr">
@@ -14186,7 +14173,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G246" s="6" t="inlineStr">
+      <c r="G246" s="14" t="inlineStr">
         <is>
           <t>ID88</t>
         </is>
@@ -14209,7 +14196,7 @@
           <t>81A837220D</t>
         </is>
       </c>
-      <c r="N246" s="6" t="inlineStr">
+      <c r="N246" s="14" t="inlineStr">
         <is>
           <t>MQB IMMO5</t>
         </is>
@@ -14219,11 +14206,7 @@
           <t>etsy(Q2 key covers), ebay(2023/2024 Audi key)</t>
         </is>
       </c>
-      <c r="P246" s="6" t="inlineStr">
-        <is>
-          <t>해당 연식 칩 자료 없음 — 같은 세대 기준 추정</t>
-        </is>
-      </c>
+      <c r="P246" s="14" t="n"/>
     </row>
     <row r="247">
       <c r="A247" s="11" t="inlineStr">
@@ -14256,7 +14239,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G247" s="6" t="inlineStr">
+      <c r="G247" s="14" t="inlineStr">
         <is>
           <t>ID88</t>
         </is>
@@ -14279,7 +14262,7 @@
           <t>81A837220D</t>
         </is>
       </c>
-      <c r="N247" s="6" t="inlineStr">
+      <c r="N247" s="14" t="inlineStr">
         <is>
           <t>MQB IMMO5</t>
         </is>
@@ -14289,11 +14272,7 @@
           <t>motor1(A1/Q2 production ends), cars.co.za(A1/Q2 end 2026)</t>
         </is>
       </c>
-      <c r="P247" s="6" t="inlineStr">
-        <is>
-          <t>해당 연식 칩 자료 없음 — 같은 세대 기준 추정</t>
-        </is>
-      </c>
+      <c r="P247" s="14" t="n"/>
     </row>
     <row r="248">
       <c r="A248" s="11" t="inlineStr">
@@ -14326,7 +14305,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G248" s="6" t="inlineStr">
+      <c r="G248" s="14" t="inlineStr">
         <is>
           <t>ID88</t>
         </is>
@@ -14349,7 +14328,7 @@
           <t>81A837220D</t>
         </is>
       </c>
-      <c r="N248" s="6" t="inlineStr">
+      <c r="N248" s="14" t="inlineStr">
         <is>
           <t>MQB IMMO5</t>
         </is>
@@ -14359,11 +14338,7 @@
           <t>audi.com(Q2 until 2026), wikipedia(Q2)</t>
         </is>
       </c>
-      <c r="P248" s="6" t="inlineStr">
-        <is>
-          <t>해당 연식 칩 자료 없음 — 같은 세대 기준 추정</t>
-        </is>
-      </c>
+      <c r="P248" s="14" t="n"/>
     </row>
     <row r="249">
       <c r="A249" s="11" t="inlineStr">
@@ -19201,12 +19176,12 @@
           <t>2022</t>
         </is>
       </c>
-      <c r="D331" s="7" t="inlineStr"/>
-      <c r="E331" s="7" t="inlineStr"/>
-      <c r="F331" s="7" t="inlineStr"/>
-      <c r="G331" s="6" t="inlineStr">
-        <is>
-          <t>MLB 전용 칩</t>
+      <c r="D331" s="7" t="n"/>
+      <c r="E331" s="7" t="n"/>
+      <c r="F331" s="7" t="n"/>
+      <c r="G331" s="14" t="inlineStr">
+        <is>
+          <t>MLB evo 전용 칩</t>
         </is>
       </c>
       <c r="H331" s="11" t="inlineStr">
@@ -19223,9 +19198,9 @@
       <c r="K331" s="11" t="inlineStr"/>
       <c r="L331" s="11" t="inlineStr"/>
       <c r="M331" s="11" t="inlineStr"/>
-      <c r="N331" s="6" t="inlineStr">
-        <is>
-          <t>MLB IMMO5</t>
+      <c r="N331" s="14" t="inlineStr">
+        <is>
+          <t>MLB evo IMMO5</t>
         </is>
       </c>
       <c r="O331" s="11" t="inlineStr">
@@ -19233,11 +19208,7 @@
           <t>parts.audibethesda(2022 Q7 BF), parts.audiusa(2022 Q7)</t>
         </is>
       </c>
-      <c r="P331" s="6" t="inlineStr">
-        <is>
-          <t>2020년 이후 Q7 키는 4N0959754AM·BF(MLB evo 계열 신형 키) 표기 — 칩 구분(MLB/MLB evo) 확인 필요</t>
-        </is>
-      </c>
+      <c r="P331" s="14" t="n"/>
     </row>
     <row r="332">
       <c r="A332" s="11" t="inlineStr">
@@ -19255,12 +19226,12 @@
           <t>2023</t>
         </is>
       </c>
-      <c r="D332" s="7" t="inlineStr"/>
-      <c r="E332" s="7" t="inlineStr"/>
-      <c r="F332" s="7" t="inlineStr"/>
-      <c r="G332" s="6" t="inlineStr">
-        <is>
-          <t>MLB 전용 칩</t>
+      <c r="D332" s="7" t="n"/>
+      <c r="E332" s="7" t="n"/>
+      <c r="F332" s="7" t="n"/>
+      <c r="G332" s="14" t="inlineStr">
+        <is>
+          <t>MLB evo 전용 칩</t>
         </is>
       </c>
       <c r="H332" s="11" t="inlineStr">
@@ -19277,9 +19248,9 @@
       <c r="K332" s="11" t="inlineStr"/>
       <c r="L332" s="11" t="inlineStr"/>
       <c r="M332" s="11" t="inlineStr"/>
-      <c r="N332" s="6" t="inlineStr">
-        <is>
-          <t>MLB IMMO5</t>
+      <c r="N332" s="14" t="inlineStr">
+        <is>
+          <t>MLB evo IMMO5</t>
         </is>
       </c>
       <c r="O332" s="11" t="inlineStr">
@@ -19287,11 +19258,7 @@
           <t>parts.audiusa(2023 Q7 4N0959754BFTKE)</t>
         </is>
       </c>
-      <c r="P332" s="6" t="inlineStr">
-        <is>
-          <t>2020년 이후 Q7 키는 4N0959754AM·BF(MLB evo 계열 신형 키) 표기 — 칩 구분(MLB/MLB evo) 확인 필요</t>
-        </is>
-      </c>
+      <c r="P332" s="14" t="n"/>
     </row>
     <row r="333">
       <c r="A333" s="11" t="inlineStr">
@@ -19309,12 +19276,12 @@
           <t>2024</t>
         </is>
       </c>
-      <c r="D333" s="7" t="inlineStr"/>
-      <c r="E333" s="7" t="inlineStr"/>
-      <c r="F333" s="7" t="inlineStr"/>
-      <c r="G333" s="6" t="inlineStr">
-        <is>
-          <t>MLB 전용 칩</t>
+      <c r="D333" s="7" t="n"/>
+      <c r="E333" s="7" t="n"/>
+      <c r="F333" s="7" t="n"/>
+      <c r="G333" s="14" t="inlineStr">
+        <is>
+          <t>MLB evo 전용 칩</t>
         </is>
       </c>
       <c r="H333" s="11" t="inlineStr">
@@ -19331,9 +19298,9 @@
       <c r="K333" s="11" t="inlineStr"/>
       <c r="L333" s="11" t="inlineStr"/>
       <c r="M333" s="11" t="inlineStr"/>
-      <c r="N333" s="6" t="inlineStr">
-        <is>
-          <t>MLB IMMO5</t>
+      <c r="N333" s="14" t="inlineStr">
+        <is>
+          <t>MLB evo IMMO5</t>
         </is>
       </c>
       <c r="O333" s="11" t="inlineStr">
@@ -19341,11 +19308,7 @@
           <t>audi.co.kr(더 뉴 Q7 2024-12-18), parts.audivirginiabeach(2024 Q7 AM)</t>
         </is>
       </c>
-      <c r="P333" s="6" t="inlineStr">
-        <is>
-          <t>2020년 이후 Q7 키는 4N0959754AM·BF(MLB evo 계열 신형 키) 표기 — 칩 구분(MLB/MLB evo) 확인 필요</t>
-        </is>
-      </c>
+      <c r="P333" s="14" t="n"/>
     </row>
     <row r="334">
       <c r="A334" s="11" t="inlineStr">
@@ -19363,12 +19326,12 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="D334" s="7" t="inlineStr"/>
-      <c r="E334" s="7" t="inlineStr"/>
-      <c r="F334" s="7" t="inlineStr"/>
-      <c r="G334" s="6" t="inlineStr">
-        <is>
-          <t>MLB 전용 칩</t>
+      <c r="D334" s="7" t="n"/>
+      <c r="E334" s="7" t="n"/>
+      <c r="F334" s="7" t="n"/>
+      <c r="G334" s="14" t="inlineStr">
+        <is>
+          <t>MLB evo 전용 칩</t>
         </is>
       </c>
       <c r="H334" s="11" t="inlineStr">
@@ -19385,9 +19348,9 @@
       <c r="K334" s="11" t="inlineStr"/>
       <c r="L334" s="11" t="inlineStr"/>
       <c r="M334" s="11" t="inlineStr"/>
-      <c r="N334" s="6" t="inlineStr">
-        <is>
-          <t>MLB IMMO5</t>
+      <c r="N334" s="14" t="inlineStr">
+        <is>
+          <t>MLB evo IMMO5</t>
         </is>
       </c>
       <c r="O334" s="11" t="inlineStr">
@@ -19395,11 +19358,7 @@
           <t>audiusa(2025 Q7 key user setup), audiworld(remote start key fob)</t>
         </is>
       </c>
-      <c r="P334" s="6" t="inlineStr">
-        <is>
-          <t>2020년 이후 Q7 키는 4N0959754AM·BF(MLB evo 계열 신형 키) 표기 — 칩 구분(MLB/MLB evo) 확인 필요</t>
-        </is>
-      </c>
+      <c r="P334" s="14" t="n"/>
     </row>
     <row r="335">
       <c r="A335" s="11" t="inlineStr">
@@ -19417,12 +19376,12 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="D335" s="7" t="inlineStr"/>
-      <c r="E335" s="7" t="inlineStr"/>
-      <c r="F335" s="7" t="inlineStr"/>
-      <c r="G335" s="6" t="inlineStr">
-        <is>
-          <t>MLB 전용 칩</t>
+      <c r="D335" s="7" t="n"/>
+      <c r="E335" s="7" t="n"/>
+      <c r="F335" s="7" t="n"/>
+      <c r="G335" s="14" t="inlineStr">
+        <is>
+          <t>MLB evo 전용 칩</t>
         </is>
       </c>
       <c r="H335" s="11" t="inlineStr">
@@ -19439,9 +19398,9 @@
       <c r="K335" s="11" t="inlineStr"/>
       <c r="L335" s="11" t="inlineStr"/>
       <c r="M335" s="11" t="inlineStr"/>
-      <c r="N335" s="6" t="inlineStr">
-        <is>
-          <t>MLB IMMO5</t>
+      <c r="N335" s="14" t="inlineStr">
+        <is>
+          <t>MLB evo IMMO5</t>
         </is>
       </c>
       <c r="O335" s="11" t="inlineStr">
@@ -19449,11 +19408,7 @@
           <t>parts.audiusa(Q7 4N0959754BFTKE), go-parts</t>
         </is>
       </c>
-      <c r="P335" s="6" t="inlineStr">
-        <is>
-          <t>2020년 이후 Q7 키는 4N0959754AM·BF(MLB evo 계열 신형 키) 표기 — 칩 구분(MLB/MLB evo) 확인 필요</t>
-        </is>
-      </c>
+      <c r="P335" s="14" t="n"/>
     </row>
     <row r="336">
       <c r="A336" s="11" t="inlineStr">
@@ -19471,12 +19426,12 @@
           <t>2024</t>
         </is>
       </c>
-      <c r="D336" s="7" t="inlineStr"/>
-      <c r="E336" s="7" t="inlineStr"/>
-      <c r="F336" s="7" t="inlineStr"/>
-      <c r="G336" s="6" t="inlineStr">
-        <is>
-          <t>MLB 전용 칩</t>
+      <c r="D336" s="7" t="n"/>
+      <c r="E336" s="7" t="n"/>
+      <c r="F336" s="7" t="n"/>
+      <c r="G336" s="14" t="inlineStr">
+        <is>
+          <t>MLB evo 전용 칩</t>
         </is>
       </c>
       <c r="H336" s="11" t="inlineStr">
@@ -19493,9 +19448,9 @@
       <c r="K336" s="11" t="inlineStr"/>
       <c r="L336" s="11" t="inlineStr"/>
       <c r="M336" s="11" t="inlineStr"/>
-      <c r="N336" s="6" t="inlineStr">
-        <is>
-          <t>MLB IMMO5</t>
+      <c r="N336" s="14" t="inlineStr">
+        <is>
+          <t>MLB evo IMMO5</t>
         </is>
       </c>
       <c r="O336" s="11" t="inlineStr">
@@ -19503,11 +19458,7 @@
           <t>top-rider(SQ7 TFSI 출시), parts.audiusa(2024 SQ7)</t>
         </is>
       </c>
-      <c r="P336" s="6" t="inlineStr">
-        <is>
-          <t>2020년 이후 Q7 키는 4N0959754AM·BF(MLB evo 계열 신형 키) 표기 — 칩 구분(MLB/MLB evo) 확인 필요</t>
-        </is>
-      </c>
+      <c r="P336" s="14" t="n"/>
     </row>
     <row r="337">
       <c r="A337" s="11" t="inlineStr">
@@ -19525,12 +19476,12 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="D337" s="7" t="inlineStr"/>
-      <c r="E337" s="7" t="inlineStr"/>
-      <c r="F337" s="7" t="inlineStr"/>
-      <c r="G337" s="6" t="inlineStr">
-        <is>
-          <t>MLB 전용 칩</t>
+      <c r="D337" s="7" t="n"/>
+      <c r="E337" s="7" t="n"/>
+      <c r="F337" s="7" t="n"/>
+      <c r="G337" s="14" t="inlineStr">
+        <is>
+          <t>MLB evo 전용 칩</t>
         </is>
       </c>
       <c r="H337" s="11" t="inlineStr">
@@ -19547,9 +19498,9 @@
       <c r="K337" s="11" t="inlineStr"/>
       <c r="L337" s="11" t="inlineStr"/>
       <c r="M337" s="11" t="inlineStr"/>
-      <c r="N337" s="6" t="inlineStr">
-        <is>
-          <t>MLB IMMO5</t>
+      <c r="N337" s="14" t="inlineStr">
+        <is>
+          <t>MLB evo IMMO5</t>
         </is>
       </c>
       <c r="O337" s="11" t="inlineStr">
@@ -19557,11 +19508,7 @@
           <t>parts.audiusa(2025 SQ8 BF), audiusa(2025 Q7 key setup)</t>
         </is>
       </c>
-      <c r="P337" s="6" t="inlineStr">
-        <is>
-          <t>2020년 이후 Q7 키는 4N0959754AM·BF(MLB evo 계열 신형 키) 표기 — 칩 구분(MLB/MLB evo) 확인 필요</t>
-        </is>
-      </c>
+      <c r="P337" s="14" t="n"/>
     </row>
     <row r="338">
       <c r="A338" s="11" t="inlineStr">
@@ -19579,12 +19526,12 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="D338" s="7" t="inlineStr"/>
-      <c r="E338" s="7" t="inlineStr"/>
-      <c r="F338" s="7" t="inlineStr"/>
-      <c r="G338" s="6" t="inlineStr">
-        <is>
-          <t>MLB 전용 칩</t>
+      <c r="D338" s="7" t="n"/>
+      <c r="E338" s="7" t="n"/>
+      <c r="F338" s="7" t="n"/>
+      <c r="G338" s="14" t="inlineStr">
+        <is>
+          <t>MLB evo 전용 칩</t>
         </is>
       </c>
       <c r="H338" s="11" t="inlineStr">
@@ -19601,9 +19548,9 @@
       <c r="K338" s="11" t="inlineStr"/>
       <c r="L338" s="11" t="inlineStr"/>
       <c r="M338" s="11" t="inlineStr"/>
-      <c r="N338" s="6" t="inlineStr">
-        <is>
-          <t>MLB IMMO5</t>
+      <c r="N338" s="14" t="inlineStr">
+        <is>
+          <t>MLB evo IMMO5</t>
         </is>
       </c>
       <c r="O338" s="11" t="inlineStr">
@@ -19611,11 +19558,7 @@
           <t>kbb(2026 SQ7 specs), cars.com(2026 SQ7)</t>
         </is>
       </c>
-      <c r="P338" s="6" t="inlineStr">
-        <is>
-          <t>2020년 이후 Q7 키는 4N0959754AM·BF(MLB evo 계열 신형 키) 표기 — 칩 구분(MLB/MLB evo) 확인 필요</t>
-        </is>
-      </c>
+      <c r="P338" s="14" t="n"/>
     </row>
     <row r="339">
       <c r="A339" s="11" t="inlineStr">
@@ -19960,7 +19903,7 @@
       <c r="D345" s="7" t="inlineStr"/>
       <c r="E345" s="7" t="inlineStr"/>
       <c r="F345" s="7" t="inlineStr"/>
-      <c r="G345" s="6" t="inlineStr">
+      <c r="G345" s="14" t="inlineStr">
         <is>
           <t>MLB evo 전용 칩</t>
         </is>
@@ -19983,7 +19926,7 @@
         </is>
       </c>
       <c r="M345" s="11" t="inlineStr"/>
-      <c r="N345" s="6" t="inlineStr">
+      <c r="N345" s="14" t="inlineStr">
         <is>
           <t>MLB evo IMMO5</t>
         </is>
@@ -19993,11 +19936,7 @@
           <t>go-parts(2017-2026 guide), keylessentryremotefob(Q8)</t>
         </is>
       </c>
-      <c r="P345" s="6" t="inlineStr">
-        <is>
-          <t>해당 연식 칩 자료 없음 — 같은 세대 기준 추정</t>
-        </is>
-      </c>
+      <c r="P345" s="14" t="n"/>
     </row>
     <row r="346">
       <c r="A346" s="11" t="inlineStr">
@@ -20594,7 +20533,7 @@
       <c r="D358" s="7" t="inlineStr"/>
       <c r="E358" s="7" t="inlineStr"/>
       <c r="F358" s="7" t="inlineStr"/>
-      <c r="G358" s="6" t="inlineStr">
+      <c r="G358" s="14" t="inlineStr">
         <is>
           <t>MLB evo 전용 칩</t>
         </is>
@@ -20613,7 +20552,7 @@
         </is>
       </c>
       <c r="M358" s="11" t="inlineStr"/>
-      <c r="N358" s="6" t="inlineStr">
+      <c r="N358" s="14" t="inlineStr">
         <is>
           <t>MLB evo IMMO5</t>
         </is>
@@ -20623,11 +20562,7 @@
           <t>audiusa(2026 RS Q8 performance), kbb(2026 RS Q8)</t>
         </is>
       </c>
-      <c r="P358" s="6" t="inlineStr">
-        <is>
-          <t>해당 연식 칩 자료 없음 — 같은 세대 기준 추정</t>
-        </is>
-      </c>
+      <c r="P358" s="14" t="n"/>
     </row>
     <row r="359">
       <c r="A359" s="11" t="inlineStr">
@@ -23979,12 +23914,24 @@
           <t>2017</t>
         </is>
       </c>
-      <c r="D412" s="7" t="inlineStr"/>
-      <c r="E412" s="7" t="inlineStr"/>
-      <c r="F412" s="7" t="inlineStr"/>
+      <c r="D412" s="17" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E412" s="17" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F412" s="17" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="G412" s="6" t="inlineStr">
         <is>
-          <t>확인 불가</t>
+          <t>ID46(PCF7945AC)[추정]</t>
         </is>
       </c>
       <c r="H412" s="11" t="inlineStr">
@@ -23999,7 +23946,7 @@
       <c r="M412" s="11" t="inlineStr"/>
       <c r="N412" s="6" t="inlineStr">
         <is>
-          <t>확인 불가</t>
+          <t>BCM2[추정]</t>
         </is>
       </c>
       <c r="O412" s="11" t="inlineStr">
@@ -24009,7 +23956,7 @@
       </c>
       <c r="P412" s="6" t="inlineStr">
         <is>
-          <t>R8 4S 키(4H0959754EB 계열) 칩 형식 자료 없음 — 이모빌라이저 확인 필요</t>
+          <t>R8 4S 키 4H0959754EB·FK는 A8 D4 계열(4H0) 키 — PCF7945AC·BCM2 기준 추정, R8 전용 칩 자료 없음</t>
         </is>
       </c>
     </row>
@@ -24029,12 +23976,24 @@
           <t>2018</t>
         </is>
       </c>
-      <c r="D413" s="7" t="inlineStr"/>
-      <c r="E413" s="7" t="inlineStr"/>
-      <c r="F413" s="7" t="inlineStr"/>
+      <c r="D413" s="17" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E413" s="17" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F413" s="17" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="G413" s="6" t="inlineStr">
         <is>
-          <t>확인 불가</t>
+          <t>ID46(PCF7945AC)[추정]</t>
         </is>
       </c>
       <c r="H413" s="11" t="inlineStr">
@@ -24049,7 +24008,7 @@
       <c r="M413" s="11" t="inlineStr"/>
       <c r="N413" s="6" t="inlineStr">
         <is>
-          <t>확인 불가</t>
+          <t>BCM2[추정]</t>
         </is>
       </c>
       <c r="O413" s="11" t="inlineStr">
@@ -24059,7 +24018,7 @@
       </c>
       <c r="P413" s="6" t="inlineStr">
         <is>
-          <t>R8 4S 키(4H0959754EB 계열) 칩 형식 자료 없음 — 이모빌라이저 확인 필요</t>
+          <t>R8 4S 키 4H0959754EB·FK는 A8 D4 계열(4H0) 키 — PCF7945AC·BCM2 기준 추정, R8 전용 칩 자료 없음</t>
         </is>
       </c>
     </row>
@@ -24079,12 +24038,24 @@
           <t>2019</t>
         </is>
       </c>
-      <c r="D414" s="7" t="inlineStr"/>
-      <c r="E414" s="7" t="inlineStr"/>
-      <c r="F414" s="7" t="inlineStr"/>
+      <c r="D414" s="17" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E414" s="17" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F414" s="17" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="G414" s="6" t="inlineStr">
         <is>
-          <t>확인 불가</t>
+          <t>ID46(PCF7945AC)[추정]</t>
         </is>
       </c>
       <c r="H414" s="11" t="inlineStr">
@@ -24099,7 +24070,7 @@
       <c r="M414" s="11" t="inlineStr"/>
       <c r="N414" s="6" t="inlineStr">
         <is>
-          <t>확인 불가</t>
+          <t>BCM2[추정]</t>
         </is>
       </c>
       <c r="O414" s="11" t="inlineStr">
@@ -24109,7 +24080,7 @@
       </c>
       <c r="P414" s="6" t="inlineStr">
         <is>
-          <t>R8 4S 키(4H0959754EB 계열) 칩 형식 자료 없음 — 이모빌라이저 확인 필요</t>
+          <t>R8 4S 키 4H0959754EB·FK는 A8 D4 계열(4H0) 키 — PCF7945AC·BCM2 기준 추정, R8 전용 칩 자료 없음</t>
         </is>
       </c>
     </row>
@@ -24129,12 +24100,24 @@
           <t>2020</t>
         </is>
       </c>
-      <c r="D415" s="7" t="inlineStr"/>
-      <c r="E415" s="7" t="inlineStr"/>
-      <c r="F415" s="7" t="inlineStr"/>
+      <c r="D415" s="17" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E415" s="17" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F415" s="17" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="G415" s="6" t="inlineStr">
         <is>
-          <t>확인 불가</t>
+          <t>ID46(PCF7945AC)[추정]</t>
         </is>
       </c>
       <c r="H415" s="11" t="inlineStr">
@@ -24149,7 +24132,7 @@
       <c r="M415" s="11" t="inlineStr"/>
       <c r="N415" s="6" t="inlineStr">
         <is>
-          <t>확인 불가</t>
+          <t>BCM2[추정]</t>
         </is>
       </c>
       <c r="O415" s="11" t="inlineStr">
@@ -24159,7 +24142,7 @@
       </c>
       <c r="P415" s="6" t="inlineStr">
         <is>
-          <t>R8 4S 키(4H0959754EB 계열) 칩 형식 자료 없음 — 이모빌라이저 확인 필요</t>
+          <t>R8 4S 키 4H0959754EB·FK는 A8 D4 계열(4H0) 키 — PCF7945AC·BCM2 기준 추정, R8 전용 칩 자료 없음</t>
         </is>
       </c>
     </row>
@@ -24179,12 +24162,24 @@
           <t>2021</t>
         </is>
       </c>
-      <c r="D416" s="7" t="inlineStr"/>
-      <c r="E416" s="7" t="inlineStr"/>
-      <c r="F416" s="7" t="inlineStr"/>
+      <c r="D416" s="17" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E416" s="17" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F416" s="17" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="G416" s="6" t="inlineStr">
         <is>
-          <t>확인 불가</t>
+          <t>ID46(PCF7945AC)[추정]</t>
         </is>
       </c>
       <c r="H416" s="11" t="inlineStr">
@@ -24199,7 +24194,7 @@
       <c r="M416" s="11" t="inlineStr"/>
       <c r="N416" s="6" t="inlineStr">
         <is>
-          <t>확인 불가</t>
+          <t>BCM2[추정]</t>
         </is>
       </c>
       <c r="O416" s="11" t="inlineStr">
@@ -24209,7 +24204,7 @@
       </c>
       <c r="P416" s="6" t="inlineStr">
         <is>
-          <t>R8 4S 키(4H0959754EB 계열) 칩 형식 자료 없음 — 이모빌라이저 확인 필요</t>
+          <t>R8 4S 키 4H0959754EB·FK는 A8 D4 계열(4H0) 키 — PCF7945AC·BCM2 기준 추정, R8 전용 칩 자료 없음</t>
         </is>
       </c>
     </row>
@@ -24229,12 +24224,24 @@
           <t>2022</t>
         </is>
       </c>
-      <c r="D417" s="7" t="inlineStr"/>
-      <c r="E417" s="7" t="inlineStr"/>
-      <c r="F417" s="7" t="inlineStr"/>
+      <c r="D417" s="17" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E417" s="17" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F417" s="17" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="G417" s="6" t="inlineStr">
         <is>
-          <t>확인 불가</t>
+          <t>ID46(PCF7945AC)[추정]</t>
         </is>
       </c>
       <c r="H417" s="11" t="inlineStr">
@@ -24249,7 +24256,7 @@
       <c r="M417" s="11" t="inlineStr"/>
       <c r="N417" s="6" t="inlineStr">
         <is>
-          <t>확인 불가</t>
+          <t>BCM2[추정]</t>
         </is>
       </c>
       <c r="O417" s="11" t="inlineStr">
@@ -24259,7 +24266,7 @@
       </c>
       <c r="P417" s="6" t="inlineStr">
         <is>
-          <t>R8 4S 키(4H0959754EB 계열) 칩 형식 자료 없음 — 이모빌라이저 확인 필요</t>
+          <t>R8 4S 키 4H0959754EB·FK는 A8 D4 계열(4H0) 키 — PCF7945AC·BCM2 기준 추정, R8 전용 칩 자료 없음</t>
         </is>
       </c>
     </row>
@@ -24279,12 +24286,24 @@
           <t>2023</t>
         </is>
       </c>
-      <c r="D418" s="7" t="inlineStr"/>
-      <c r="E418" s="7" t="inlineStr"/>
-      <c r="F418" s="7" t="inlineStr"/>
+      <c r="D418" s="17" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E418" s="17" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F418" s="17" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="G418" s="6" t="inlineStr">
         <is>
-          <t>확인 불가</t>
+          <t>ID46(PCF7945AC)[추정]</t>
         </is>
       </c>
       <c r="H418" s="11" t="inlineStr">
@@ -24299,7 +24318,7 @@
       <c r="M418" s="11" t="inlineStr"/>
       <c r="N418" s="6" t="inlineStr">
         <is>
-          <t>확인 불가</t>
+          <t>BCM2[추정]</t>
         </is>
       </c>
       <c r="O418" s="11" t="inlineStr">
@@ -24309,7 +24328,7 @@
       </c>
       <c r="P418" s="6" t="inlineStr">
         <is>
-          <t>R8 4S 키(4H0959754EB 계열) 칩 형식 자료 없음 — 이모빌라이저 확인 필요</t>
+          <t>R8 4S 키 4H0959754EB·FK는 A8 D4 계열(4H0) 키 — PCF7945AC·BCM2 기준 추정, R8 전용 칩 자료 없음</t>
         </is>
       </c>
     </row>
@@ -24329,12 +24348,24 @@
           <t>2024(단종)</t>
         </is>
       </c>
-      <c r="D419" s="7" t="inlineStr"/>
-      <c r="E419" s="7" t="inlineStr"/>
-      <c r="F419" s="7" t="inlineStr"/>
+      <c r="D419" s="17" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E419" s="17" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F419" s="17" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="G419" s="6" t="inlineStr">
         <is>
-          <t>확인 불가</t>
+          <t>ID46(PCF7945AC)[추정]</t>
         </is>
       </c>
       <c r="H419" s="11" t="inlineStr">
@@ -24349,7 +24380,7 @@
       <c r="M419" s="11" t="inlineStr"/>
       <c r="N419" s="6" t="inlineStr">
         <is>
-          <t>확인 불가</t>
+          <t>BCM2[추정]</t>
         </is>
       </c>
       <c r="O419" s="11" t="inlineStr">
@@ -24359,7 +24390,7 @@
       </c>
       <c r="P419" s="6" t="inlineStr">
         <is>
-          <t>R8 4S 키(4H0959754EB 계열) 칩 형식 자료 없음 — 이모빌라이저 확인 필요</t>
+          <t>R8 4S 키 4H0959754EB·FK는 A8 D4 계열(4H0) 키 — PCF7945AC·BCM2 기준 추정, R8 전용 칩 자료 없음</t>
         </is>
       </c>
     </row>
@@ -24983,404 +25014,460 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A61"/>
+  <dimension ref="A1:A69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="150" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="22" t="inlineStr">
+      <c r="A1" s="24" t="inlineStr">
         <is>
           <t>이 표는 락스미스(자동차 키 제작/프로그래밍) 참고용입니다.</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="22" t="inlineStr"/>
+      <c r="A2" s="24" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="22" t="inlineStr">
+      <c r="A3" s="24" t="inlineStr">
         <is>
           <t>※ 구성</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="22" t="inlineStr">
+      <c r="A4" s="24" t="inlineStr">
         <is>
           <t>- 맨 앞 '브랜드' 컬럼에 브랜드명을 적었습니다(검색 프로그램에서 '기아 K5'처럼 브랜드와 모델명을 함께 검색 가능).</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="22" t="inlineStr">
+      <c r="A5" s="24" t="inlineStr">
         <is>
           <t>- 컬럼은 '기아_트랜스폰더_칩코드_DBnew.xlsx'와 같고, 칩코드 뒤에 '키종류'를 추가했습니다. 모델마다 연식별로 한 행씩, 2000년식부터 기록했습니다.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="22" t="inlineStr">
+      <c r="A6" s="24" t="inlineStr">
         <is>
           <t>- 연식은 실제 국내 판매 기준입니다. 원본 목록 연식과 국내 출시 시점이 다른 모델은 국내 기준으로 바꿨습니다(아래 목록). 단종 모델의 마지막 연식은 '2016(단종)' 형식입니다.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="22" t="inlineStr">
+      <c r="A7" s="24" t="inlineStr">
         <is>
           <t>- '키종류'는 그 연식에 나온 키 형태(막대키·폴딩키·스마트키·카드키)를 모두 적었습니다. 카드키는 PPE/PPC 차량의 NFC 키카드(Audi connect Key Card)입니다.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="22" t="inlineStr">
+      <c r="A8" s="24" t="inlineStr">
         <is>
           <t>- 키 부품번호는 국내 사양(433/434MHz)만 적었습니다. 미국형(315MHz, FCC IYZFBSB802·IYZ-AK01/AK2·NBG009272T 등 미국 딜러 품번)과 유럽 868MHz 사양은 뺐습니다.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="22" t="inlineStr">
+      <c r="A9" s="24" t="inlineStr">
         <is>
           <t>- '비고'에는 주황색·빨간색 칸의 이유만 적었습니다.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="22" t="inlineStr">
+      <c r="A10" s="24" t="inlineStr">
         <is>
           <t>- 칩코드는 세대별 방식입니다: ID48 Megamos(구형 폴딩키) / ID8E(A6 C6·Q7 4L) / ID46 Hitag2(A8 D3) / BCM2 PCF7945AC(2008~2018 B8·C7·D4·8R) / MQB Megamos AES(MQB48) / MQB-Evo Hitag Pro(MQB49, 8Y) / MLB·MLB evo 전용 키 / PPE·PPC·MEB 신형 키.</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="22" t="inlineStr">
+      <c r="A11" s="24" t="inlineStr">
         <is>
           <t>- BCM2·MLB·MLB evo 키는 일반 트랜스폰더(ID46 등)로 복제하는 방식이 아니라서 'XT27A/A66·XT27B·XT57B 호환' 칸을 비웠습니다.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="22" t="inlineStr">
+      <c r="A12" s="24" t="inlineStr">
         <is>
           <t>- 키블레이드(키웨이)는 비상키 블레이드입니다(HU66, Q2·Q3 F3·TT 8S·Q8은 HU162T 표기 병존). 키블레이드 부품번호는 MLB 비상키 4M0837216A만 찾았습니다.</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="22" t="inlineStr">
+      <c r="A13" s="24" t="inlineStr">
         <is>
           <t>- 출처 칸은 검색에서 근거로 쓴 페이지입니다. 원문은 이 환경에서 열 수 없어 검색 결과 요약을 근거로 했습니다. 부품 판매처는 대부분 미국·유럽 사이트입니다.</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="22" t="inlineStr"/>
+      <c r="A14" s="24" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="22" t="inlineStr">
+      <c r="A15" s="24" t="inlineStr">
         <is>
           <t>※ 색상</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="22" t="inlineStr">
+      <c r="A16" s="24" t="inlineStr">
         <is>
           <t>- 주황색: 추정이거나 자료가 서로 다른 값, 해당 연식 칩 자료가 없어 같은 세대 기준으로 채운 값, 또는 국내 미판매 모델(해외 사양 기준) — 실물 키로 재확인.</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="22" t="inlineStr">
+      <c r="A17" s="24" t="inlineStr">
         <is>
           <t>- 빨간색: 확인 불가 — PPE·PPC·MEB 신형 키(A5·S5 B10, Q5·SQ5 3세대, A6·S6 e-트론, Q6 e-트론, Q4 e-트론, 3세대 Q3)는 칩·이모빌라이저 자료가 없습니다.</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="22" t="inlineStr">
+      <c r="A18" s="24" t="inlineStr">
         <is>
           <t>- 전환 연식은 칩코드·이모빌라이저 칸에 전·후를 함께 적었습니다(예: TT 2015 = ID48[8J, 2015.10 이전], ID88[8S]). 후속 모델 칩이 확인 불가면 빨간색입니다.</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="22" t="inlineStr"/>
+      <c r="A19" s="24" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="22" t="inlineStr">
+      <c r="A20" s="24" t="inlineStr">
         <is>
           <t>※ 목록과 국내 판매 연식이 다른 모델</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="22" t="inlineStr">
+      <c r="A21" s="24" t="inlineStr">
         <is>
           <t>- A1: 2015.06 첫 출시, 2016 디젤게이트로 판매 중단 → 2015~2016만 기록(목록 2012-2018).</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="22" t="inlineStr">
+      <c r="A22" s="24" t="inlineStr">
         <is>
           <t>- A3 8P: 스포트백 2008.10 출시 → 2008~2012 / A3 8Y: 2022.07 출시 → 2022~ / S3 8Y: 2022.12 출시 → 2022~ / RS3: 8V 국내 미판매, 8Y 2023.07 출시 → 2023~.</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="22" t="inlineStr">
+      <c r="A23" s="24" t="inlineStr">
         <is>
           <t>- A5 B10: 2025.07 출시(목록 2024~) / A7 C8: 2020.03 / S7: 2020.07 / A8 D5: 2019.12 / S6 C8: 2020.07 / S8: D4는 2017까지, D5 S8 L은 2023.07 출시.</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="22" t="inlineStr">
+      <c r="A24" s="24" t="inlineStr">
         <is>
           <t>- RS6 아반트·RS7: C7 2014.08 출시, C8 2021.08 출시 → 2019~2020년식 없음.</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="22" t="inlineStr">
+      <c r="A25" s="24" t="inlineStr">
         <is>
           <t>- Q2: 2020.09 출시(2018 부산모터쇼 공개 후 연기) / Q3 F3: 2020.05 / Q5·SQ5 FY: 2020.05.13 / Q7 4L: 2006.07 판매 시작 / Q7 4M: 2016.03 / SQ7: 2024.01 첫 출시.</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="22" t="inlineStr">
+      <c r="A26" s="24" t="inlineStr">
         <is>
           <t>- Q8: 2020.04.01 첫 출시 / RS Q8: 2021.06 / e-트론 55: 2020.07.01 / SQ8 e-트론: 2024.06.10 / R8 2세대: 2017.11(1세대 국내 판매는 2016.02까지).</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="22" t="inlineStr">
+      <c r="A27" s="24" t="inlineStr">
         <is>
           <t>- 국내 정식 판매 이력이 없는 모델: SQ2, RS Q3, TT RS(2019 인증만). 목록 연식대로 남기고 주황색(해외 사양 기준)으로 표시했습니다.</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="22" t="inlineStr"/>
+      <c r="A28" s="24" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="22" t="inlineStr">
+      <c r="A29" s="24" t="inlineStr">
         <is>
           <t>※ 조사하며 확인된 주요 사항</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="22" t="inlineStr">
+      <c r="A30" s="24" t="inlineStr">
         <is>
           <t>- 모델마다 연식별로 검색했고 연식별 검색 기록은 research/audi/yearly.md에 있습니다.</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="22" t="inlineStr">
+      <c r="A31" s="24" t="inlineStr">
         <is>
           <t>- BCM2(2008~2018): 키 주파수는 BCM2 코드로 구분(5D1=433MHz, 5D2~5D4=315MHz, 5D7=868MHz). 2013년경부터 공장 잠김(locked) BCM2가 나와 올키로스트는 OBD만으로 안 되고 온라인 해제(Abrites VN020 등)나 벤치 읽기가 필요합니다.</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="22" t="inlineStr">
+      <c r="A32" s="24" t="inlineStr">
         <is>
           <t>- MQB(8V·Q2·Q3 F3·TT 8S)는 Megamos AES(ID88), 8Y(A3·S3·RS3 2021~)는 Hitag Pro MQB49(NCF295X)이며 GeKo 온라인 로그인이 필요합니다. 일부 판매처는 8Y를 AES ID88로 표기합니다.</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="22" t="inlineStr">
+      <c r="A33" s="24" t="inlineStr">
         <is>
           <t>- MLB(B9·Q5 FY·Q7 4M): 국내형 순정 스마트키 4M0959754BA(433MHz, 5M 칩, 2017-2021), 2016 Q7 4M0959754BC(434MHz). 중고 키는 VIN 잠금이라 재등록이 어렵습니다.</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="22" t="inlineStr">
+      <c r="A34" s="24" t="inlineStr">
         <is>
           <t>- MLB evo(C8·D5·Q8·e-트론·e-트론 GT): Q8 4N0959754BL(434MHz), RS6·RS7·RS Q8·RS e-트론 GT 4N0959754BC(433.92MHz). 미국 딜러 품번 4N0959754AM/K/BF는 뺐습니다.</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="22" t="inlineStr">
+      <c r="A35" s="24" t="inlineStr">
         <is>
           <t>- 구형 국내형 폴딩키: A3 8P·TT 8J 8P0837220D(434MHz), A1·Q3 8U 8X0837220D(434MHz), A4 B7 8E0837220E/Q/K(433MHz), A6 C6·Q7 4L 4F0837220M/T(434MHz), A8 D3 4E0837220M/D(433MHz), R8 1세대 420837220(433MHz).</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="22" t="inlineStr">
+      <c r="A36" s="24" t="inlineStr">
         <is>
           <t>- Q2 81A837220D(434MHz, Megamos AES), Q3 F3 81A837220AG(434MHz), TT 8S 8S0959754AK(434MHz, ID88), A3/S3 8V 8V0837220D(434MHz), A3/S3/RS3 8Y 8Y0959754AN(434MHz).</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="22" t="inlineStr">
+      <c r="A37" s="24" t="inlineStr">
         <is>
           <t>- PPE(A6 e-트론·Q6 e-트론)·PPC(A5·Q5 3세대)는 UWB/NFC 디지털 키가 표준이고 NFC 키카드가 제공됩니다. Q4 e-트론은 RSAD UWB(릴레이 공격 탐지) 키입니다.</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="22" t="n"/>
+      <c r="A38" s="24" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="22" t="inlineStr">
+      <c r="A39" s="24" t="inlineStr">
         <is>
           <t>※ 표기 규칙 (칩코드·부품번호·키웨이·이모빌라이저 칸 공통)</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="22" t="inlineStr">
+      <c r="A40" s="24" t="inlineStr">
         <is>
           <t>- 한 칸에 값이 여러 개면 ', '(쉼표)로만 구분합니다. '/', '·', '또는'은 쓰지 않고, 줄임(예: 4F0837220M/T, 5WK49145~49147)도 모두 풀어서 따로 적었습니다.</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="22" t="inlineStr">
+      <c r="A41" s="24" t="inlineStr">
         <is>
           <t>- ( ) 안에는 부품번호만 적습니다. 칩코드 'ID49(PCF7953)' = ID49 칩, 칩 부품번호 PCF7953. 이모빌라이저 'SKM(87570-36010)' = SKM 모듈, 품번 87570-36010. 칩 부품번호를 모르면 'ID46'처럼 ID만 적었습니다.</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="22" t="inlineStr">
+      <c r="A42" s="24" t="inlineStr">
         <is>
           <t>- [ ] 안에는 그 값이 적용되는 조건을 적습니다(키 종류·버튼 수·옵션·생산 시기·차종 코드). 예: ID46(PCF7936)[폴딩키], ID46(PCF7952A)[스마트키] → 폴딩키는 PCF7936, 스마트키는 PCF7952A.</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="22" t="inlineStr">
+      <c r="A43" s="24" t="inlineStr">
         <is>
           <t>- [추정] = 추정값, [일부 자료] = 일부 자료에만 나오는 값, [자료 상충] = 자료마다 달라 둘 중 무엇인지 미확정, [해외 공용 품번] = 해외 공용 품번(국내 순정 품번 미확인).</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="22" t="inlineStr">
+      <c r="A44" s="24" t="inlineStr">
         <is>
           <t>- 부품번호 칸에는 부품번호만 적습니다. 'FCC ' = 미국 FCC 인증번호(키 모델 식별용), 'KC ' = 한국 전파인증번호, [애프터마켓] = 순정이 아닌 호환품 번호. 설명·판매처·주파수(모두 국내 433/434MHz)는 적지 않았고, 부품번호가 없으면 공란입니다.</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="22" t="inlineStr">
+      <c r="A45" s="24" t="inlineStr">
         <is>
           <t>- Hitag2·Hitag Pro·Megamos·DST80 같은 칩 방식 이름은 ID 코드와 같은 뜻이라 칸에 따로 적지 않았습니다(아래 표).</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="22" t="n"/>
+      <c r="A46" s="24" t="n"/>
     </row>
     <row r="47">
-      <c r="A47" s="22" t="inlineStr">
+      <c r="A47" s="24" t="inlineStr">
         <is>
           <t>※ 칩 ID 코드 뜻</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="22" t="inlineStr">
+      <c r="A48" s="24" t="inlineStr">
         <is>
           <t>- ID13: Megamos 13(고정 코드)  |  ID44: Philips Crypto(PCF7935, BMW EWS 구형)  |  ID48: Megamos Crypto</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="22" t="inlineStr">
+      <c r="A49" s="24" t="inlineStr">
         <is>
           <t>- ID46: Philips Hitag2 계열(PCF7936·PCF7941·PCF7945·PCF7952 등). [Extended] = Hitag2 Extended, [Circle Plus] = GM Circle Plus</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="22" t="inlineStr">
+      <c r="A50" s="24" t="inlineStr">
         <is>
           <t>- ID47: NXP Hitag3(NCF2951·NCF2952·NCF2971·PCF7938 등)  |  ID49: NXP Hitag Pro(PCF7953P·NCF2951·NCF295X 등)  |  ID4A: NXP Hitag AES(NCF29A1M·PCF7953M·PCF7961M 등)</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="22" t="inlineStr">
+      <c r="A51" s="24" t="inlineStr">
         <is>
           <t>- ID60: Texas 4D60(40bit)  |  4D60x80: Texas 4D60 80bit(DST80 계열)  |  ID70: Texas 4D70  |  ID6E-MA: Texas DST80(현대·기아 표기)</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="22" t="inlineStr">
+      <c r="A52" s="24" t="inlineStr">
         <is>
           <t>- ID6A·ID8A: Texas Crypto AES(DST-AES)  |  ID75: Texas AES(판매처 표기)  |  ID88: Megamos AES(VW·아우디 MQB)  |  ID8E: 아우디 8E Crypto(Sokymat 8E)</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="22" t="inlineStr">
+      <c r="A53" s="24" t="inlineStr">
         <is>
           <t>- FBS3·FBS4: 벤츠 NEC 프로세서 키(ID 칩이 아님)  |  MLB 전용 칩·MLB evo 전용 칩: 아우디 MLB 플랫폼 전용 키 칩</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="22" t="inlineStr">
+      <c r="A54" s="24" t="inlineStr">
         <is>
           <t>- 확인 불가 = 자료로 확인하지 못함  |  해당 없음 = 이모빌라이저 미적용</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="22" t="n"/>
+      <c r="A55" s="24" t="n"/>
     </row>
     <row r="56">
-      <c r="A56" s="22" t="inlineStr">
+      <c r="A56" s="24" t="inlineStr">
         <is>
           <t>※ 재조사로 확인한 근거 (색을 지운 행)</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="22" t="inlineStr">
+      <c r="A57" s="24" t="inlineStr">
         <is>
           <t>- 아우디 A3 8V 2020·S3 2019·A5 B9 2020·A7 C7 2014·A8 D3 2008·Q2 2022·Q3 F3 2023·Q5 8R 2011·Q7 4L 2006·Q7 4M 2017·TT 8J 2014·TTS 2021·R8 42 2009: 같은 세대 안의 연식이라 키(부품번호)·칩이 앞뒤 확정 연식과 같음 — 연식별 판매처 표기 차이는 세대 구분 오류로 보고 색 지움</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="23" t="n"/>
+      <c r="A58" s="24" t="n"/>
     </row>
     <row r="59">
-      <c r="A59" s="23" t="inlineStr">
+      <c r="A59" s="24" t="inlineStr">
         <is>
           <t>※ 행 구분 규칙</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="23" t="inlineStr">
+      <c r="A60" s="24" t="inlineStr">
         <is>
           <t>- 연식 중간에 칩·이모빌라이저·키가 바뀐 해는 바뀌기 전·후를 따로 행으로 나눔. 세대가 바뀌면 세대별 모델명으로 1행씩, 같은 세대 안의 변경(부분변경·생산 시기·키 변경)은 같은 모델명으로 나누고 칸 안의 [생산 시기]·[세대] 표기로 구분</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="23" t="inlineStr">
+      <c r="A61" s="24" t="inlineStr">
         <is>
           <t>- 같은 연식·모델에 행이 2개인데 칸에 시기 표기가 없으면(예: 벤츠 FBS3 행과 FBS4 행) 전환 시점 자료가 없는 것 — 주황색, 비고의 방법(VIN 등)으로 확인</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="24" t="inlineStr">
+        <is>
+          <t>- A3 8Y 2026: 스마트키 8Y0959754 계열 적용 연식 2020~2026(go-parts) — 같은 세대 키 계속 사용 확인</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="24" t="inlineStr">
+        <is>
+          <t>- RS3 2026: 8Y0959754DD 적용(2022~2026) — 8Y 공용 키 확인</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="24" t="inlineStr">
+        <is>
+          <t>- Q2 2024~2026: 국내 2026년까지 판매, MQB 키 81A837220(ID88) 적용 연식 계속 — 추정 해제</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="24" t="inlineStr">
+        <is>
+          <t>- Q8 2026: 4N0959754AM 적용 2019~2026 — MLB evo 키 확인</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="24" t="inlineStr">
+        <is>
+          <t>- RS7 2026: 4N0959754BC 적용 2021~2026 — MLB evo 키 확인</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="24" t="inlineStr">
+        <is>
+          <t>- RS Q8 2026: 4N0959754BC 적용 2020~2026 — MLB evo 키 확인</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="24" t="inlineStr">
+        <is>
+          <t>- RS6 아반트 2026: 4N0959754BC(C8 공용) 적용 — MLB evo 키 확인</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="24" t="inlineStr">
+        <is>
+          <t>- Q7 4M 2022~2026·SQ7 2024~2026: 2023·2024 Q7/SQ7 키 4N0959754BF·AM(A8 D5·Q8과 같은 MLB evo 키) — 칩·이모빌라이저를 MLB evo로 정정</t>
         </is>
       </c>
     </row>

--- a/아우디_models.xlsx
+++ b/아우디_models.xlsx
@@ -25304,7 +25304,7 @@
     <row r="44">
       <c r="A44" s="24" t="inlineStr">
         <is>
-          <t>- 부품번호 칸에는 부품번호만 적습니다. 'FCC ' = 미국 FCC 인증번호(키 모델 식별용), 'KC ' = 한국 전파인증번호, [애프터마켓] = 순정이 아닌 호환품 번호. 설명·판매처·주파수(모두 국내 433/434MHz)는 적지 않았고, 부품번호가 없으면 공란입니다.</t>
+          <t>- 부품번호 칸에는 부품번호만 적습니다. 'FCC ' = 미국 FCC 인증번호(키 모델 식별용), 'KC ' = 한국 전파인증번호. 순정(제조사) 부품번호만 적고 애프터마켓 호환품 번호는 넣지 않았습니다. 설명·판매처·주파수(모두 국내 433/434MHz)는 적지 않았고, 부품번호가 없으면 공란입니다.</t>
         </is>
       </c>
     </row>

--- a/아우디_models.xlsx
+++ b/아우디_models.xlsx
@@ -136,7 +136,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -200,6 +200,9 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
@@ -3037,7 +3040,11 @@
       </c>
       <c r="K37" s="11" t="inlineStr"/>
       <c r="L37" s="11" t="inlineStr"/>
-      <c r="M37" s="11" t="inlineStr"/>
+      <c r="M37" s="11" t="inlineStr">
+        <is>
+          <t>8E0837220Q, 8E0837220K</t>
+        </is>
+      </c>
       <c r="N37" s="11" t="inlineStr">
         <is>
           <t>IMMO3</t>
@@ -3099,7 +3106,11 @@
       </c>
       <c r="K38" s="11" t="inlineStr"/>
       <c r="L38" s="11" t="inlineStr"/>
-      <c r="M38" s="11" t="inlineStr"/>
+      <c r="M38" s="11" t="inlineStr">
+        <is>
+          <t>8E0837220Q, 8E0837220K</t>
+        </is>
+      </c>
       <c r="N38" s="11" t="inlineStr">
         <is>
           <t>IMMO3</t>
@@ -4184,7 +4195,11 @@
         </is>
       </c>
       <c r="K57" s="11" t="inlineStr"/>
-      <c r="L57" s="11" t="inlineStr"/>
+      <c r="L57" s="11" t="inlineStr">
+        <is>
+          <t>4M0959754CG[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M57" s="11" t="inlineStr"/>
       <c r="N57" s="11" t="inlineStr">
         <is>
@@ -4234,7 +4249,11 @@
         </is>
       </c>
       <c r="K58" s="11" t="inlineStr"/>
-      <c r="L58" s="11" t="inlineStr"/>
+      <c r="L58" s="11" t="inlineStr">
+        <is>
+          <t>4M0959754CG[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M58" s="11" t="inlineStr"/>
       <c r="N58" s="11" t="inlineStr">
         <is>
@@ -4790,7 +4809,11 @@
         </is>
       </c>
       <c r="K68" s="11" t="inlineStr"/>
-      <c r="L68" s="11" t="inlineStr"/>
+      <c r="L68" s="11" t="inlineStr">
+        <is>
+          <t>4M0959754CG[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M68" s="11" t="inlineStr"/>
       <c r="N68" s="11" t="inlineStr">
         <is>
@@ -4840,7 +4863,11 @@
         </is>
       </c>
       <c r="K69" s="11" t="inlineStr"/>
-      <c r="L69" s="11" t="inlineStr"/>
+      <c r="L69" s="11" t="inlineStr">
+        <is>
+          <t>4M0959754CG[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M69" s="11" t="inlineStr"/>
       <c r="N69" s="14" t="inlineStr">
         <is>
@@ -4890,7 +4917,11 @@
         </is>
       </c>
       <c r="K70" s="11" t="inlineStr"/>
-      <c r="L70" s="11" t="inlineStr"/>
+      <c r="L70" s="11" t="inlineStr">
+        <is>
+          <t>4M0959754CG[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M70" s="11" t="inlineStr"/>
       <c r="N70" s="11" t="inlineStr">
         <is>
@@ -5280,7 +5311,11 @@
         </is>
       </c>
       <c r="K77" s="11" t="inlineStr"/>
-      <c r="L77" s="11" t="inlineStr"/>
+      <c r="L77" s="11" t="inlineStr">
+        <is>
+          <t>4M0959754CG[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M77" s="11" t="inlineStr"/>
       <c r="N77" s="11" t="inlineStr">
         <is>
@@ -5330,7 +5365,11 @@
         </is>
       </c>
       <c r="K78" s="11" t="inlineStr"/>
-      <c r="L78" s="11" t="inlineStr"/>
+      <c r="L78" s="11" t="inlineStr">
+        <is>
+          <t>4M0959754CG[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M78" s="11" t="inlineStr"/>
       <c r="N78" s="14" t="inlineStr">
         <is>
@@ -5380,7 +5419,11 @@
         </is>
       </c>
       <c r="K79" s="11" t="inlineStr"/>
-      <c r="L79" s="11" t="inlineStr"/>
+      <c r="L79" s="11" t="inlineStr">
+        <is>
+          <t>4M0959754CG[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M79" s="11" t="inlineStr"/>
       <c r="N79" s="14" t="inlineStr">
         <is>
@@ -6256,7 +6299,11 @@
         </is>
       </c>
       <c r="K95" s="11" t="inlineStr"/>
-      <c r="L95" s="11" t="inlineStr"/>
+      <c r="L95" s="11" t="inlineStr">
+        <is>
+          <t>4M0959754CG[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M95" s="11" t="inlineStr"/>
       <c r="N95" s="11" t="inlineStr">
         <is>
@@ -6306,7 +6353,11 @@
         </is>
       </c>
       <c r="K96" s="11" t="inlineStr"/>
-      <c r="L96" s="11" t="inlineStr"/>
+      <c r="L96" s="11" t="inlineStr">
+        <is>
+          <t>4M0959754CG[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M96" s="11" t="inlineStr"/>
       <c r="N96" s="14" t="inlineStr">
         <is>
@@ -6962,7 +7013,11 @@
         </is>
       </c>
       <c r="K108" s="11" t="inlineStr"/>
-      <c r="L108" s="11" t="inlineStr"/>
+      <c r="L108" s="11" t="inlineStr">
+        <is>
+          <t>4M0959754CG[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M108" s="11" t="inlineStr"/>
       <c r="N108" s="14" t="inlineStr">
         <is>
@@ -7012,7 +7067,11 @@
         </is>
       </c>
       <c r="K109" s="11" t="inlineStr"/>
-      <c r="L109" s="11" t="inlineStr"/>
+      <c r="L109" s="11" t="inlineStr">
+        <is>
+          <t>4M0959754CG[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M109" s="11" t="inlineStr"/>
       <c r="N109" s="11" t="inlineStr">
         <is>
@@ -7062,7 +7121,11 @@
         </is>
       </c>
       <c r="K110" s="11" t="inlineStr"/>
-      <c r="L110" s="11" t="inlineStr"/>
+      <c r="L110" s="11" t="inlineStr">
+        <is>
+          <t>4M0959754CG[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M110" s="11" t="inlineStr"/>
       <c r="N110" s="11" t="inlineStr">
         <is>
@@ -7764,7 +7827,11 @@
         </is>
       </c>
       <c r="K123" s="11" t="inlineStr"/>
-      <c r="L123" s="11" t="inlineStr"/>
+      <c r="L123" s="11" t="inlineStr">
+        <is>
+          <t>4M0959754CG[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M123" s="11" t="inlineStr"/>
       <c r="N123" s="11" t="inlineStr">
         <is>
@@ -7814,7 +7881,11 @@
         </is>
       </c>
       <c r="K124" s="11" t="inlineStr"/>
-      <c r="L124" s="11" t="inlineStr"/>
+      <c r="L124" s="11" t="inlineStr">
+        <is>
+          <t>4M0959754CG[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M124" s="11" t="inlineStr"/>
       <c r="N124" s="14" t="inlineStr">
         <is>
@@ -7864,7 +7935,11 @@
         </is>
       </c>
       <c r="K125" s="11" t="inlineStr"/>
-      <c r="L125" s="11" t="inlineStr"/>
+      <c r="L125" s="11" t="inlineStr">
+        <is>
+          <t>4M0959754CG[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M125" s="11" t="inlineStr"/>
       <c r="N125" s="14" t="inlineStr">
         <is>
@@ -8936,7 +9011,11 @@
       <c r="I145" s="11" t="inlineStr"/>
       <c r="J145" s="11" t="inlineStr"/>
       <c r="K145" s="11" t="inlineStr"/>
-      <c r="L145" s="11" t="inlineStr"/>
+      <c r="L145" s="11" t="inlineStr">
+        <is>
+          <t>4N0959754[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M145" s="11" t="inlineStr"/>
       <c r="N145" s="11" t="inlineStr">
         <is>
@@ -8982,7 +9061,11 @@
       <c r="I146" s="11" t="inlineStr"/>
       <c r="J146" s="11" t="inlineStr"/>
       <c r="K146" s="11" t="inlineStr"/>
-      <c r="L146" s="11" t="inlineStr"/>
+      <c r="L146" s="11" t="inlineStr">
+        <is>
+          <t>4N0959754[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M146" s="11" t="inlineStr"/>
       <c r="N146" s="11" t="inlineStr">
         <is>
@@ -9028,7 +9111,11 @@
       <c r="I147" s="11" t="inlineStr"/>
       <c r="J147" s="11" t="inlineStr"/>
       <c r="K147" s="11" t="inlineStr"/>
-      <c r="L147" s="11" t="inlineStr"/>
+      <c r="L147" s="11" t="inlineStr">
+        <is>
+          <t>4N0959754[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M147" s="11" t="inlineStr"/>
       <c r="N147" s="11" t="inlineStr">
         <is>
@@ -9074,7 +9161,11 @@
       <c r="I148" s="11" t="inlineStr"/>
       <c r="J148" s="11" t="inlineStr"/>
       <c r="K148" s="11" t="inlineStr"/>
-      <c r="L148" s="11" t="inlineStr"/>
+      <c r="L148" s="11" t="inlineStr">
+        <is>
+          <t>4N0959754[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M148" s="11" t="inlineStr"/>
       <c r="N148" s="11" t="inlineStr">
         <is>
@@ -9120,7 +9211,11 @@
       <c r="I149" s="11" t="inlineStr"/>
       <c r="J149" s="11" t="inlineStr"/>
       <c r="K149" s="11" t="inlineStr"/>
-      <c r="L149" s="11" t="inlineStr"/>
+      <c r="L149" s="11" t="inlineStr">
+        <is>
+          <t>4N0959754[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M149" s="11" t="inlineStr"/>
       <c r="N149" s="11" t="inlineStr">
         <is>
@@ -9166,7 +9261,11 @@
       <c r="I150" s="11" t="inlineStr"/>
       <c r="J150" s="11" t="inlineStr"/>
       <c r="K150" s="11" t="inlineStr"/>
-      <c r="L150" s="11" t="inlineStr"/>
+      <c r="L150" s="11" t="inlineStr">
+        <is>
+          <t>4N0959754[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M150" s="11" t="inlineStr"/>
       <c r="N150" s="14" t="inlineStr">
         <is>
@@ -9636,7 +9735,11 @@
       <c r="I159" s="11" t="inlineStr"/>
       <c r="J159" s="11" t="inlineStr"/>
       <c r="K159" s="11" t="inlineStr"/>
-      <c r="L159" s="11" t="inlineStr"/>
+      <c r="L159" s="11" t="inlineStr">
+        <is>
+          <t>4N0959754[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M159" s="11" t="inlineStr"/>
       <c r="N159" s="11" t="inlineStr">
         <is>
@@ -9682,7 +9785,11 @@
       <c r="I160" s="11" t="inlineStr"/>
       <c r="J160" s="11" t="inlineStr"/>
       <c r="K160" s="11" t="inlineStr"/>
-      <c r="L160" s="11" t="inlineStr"/>
+      <c r="L160" s="11" t="inlineStr">
+        <is>
+          <t>4N0959754[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M160" s="11" t="inlineStr"/>
       <c r="N160" s="11" t="inlineStr">
         <is>
@@ -9728,7 +9835,11 @@
       <c r="I161" s="11" t="inlineStr"/>
       <c r="J161" s="11" t="inlineStr"/>
       <c r="K161" s="11" t="inlineStr"/>
-      <c r="L161" s="11" t="inlineStr"/>
+      <c r="L161" s="11" t="inlineStr">
+        <is>
+          <t>4N0959754[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M161" s="11" t="inlineStr"/>
       <c r="N161" s="14" t="inlineStr">
         <is>
@@ -9774,7 +9885,11 @@
       <c r="I162" s="11" t="inlineStr"/>
       <c r="J162" s="11" t="inlineStr"/>
       <c r="K162" s="11" t="inlineStr"/>
-      <c r="L162" s="11" t="inlineStr"/>
+      <c r="L162" s="11" t="inlineStr">
+        <is>
+          <t>4N0959754[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M162" s="11" t="inlineStr"/>
       <c r="N162" s="14" t="inlineStr">
         <is>
@@ -9820,7 +9935,11 @@
       <c r="I163" s="11" t="inlineStr"/>
       <c r="J163" s="11" t="inlineStr"/>
       <c r="K163" s="11" t="inlineStr"/>
-      <c r="L163" s="11" t="inlineStr"/>
+      <c r="L163" s="11" t="inlineStr">
+        <is>
+          <t>4N0959754[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M163" s="11" t="inlineStr"/>
       <c r="N163" s="14" t="inlineStr">
         <is>
@@ -9866,7 +9985,11 @@
       <c r="I164" s="11" t="inlineStr"/>
       <c r="J164" s="11" t="inlineStr"/>
       <c r="K164" s="11" t="inlineStr"/>
-      <c r="L164" s="11" t="inlineStr"/>
+      <c r="L164" s="11" t="inlineStr">
+        <is>
+          <t>4N0959754[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M164" s="11" t="inlineStr"/>
       <c r="N164" s="8" t="inlineStr">
         <is>
@@ -9916,7 +10039,11 @@
       <c r="I165" s="11" t="inlineStr"/>
       <c r="J165" s="11" t="inlineStr"/>
       <c r="K165" s="11" t="inlineStr"/>
-      <c r="L165" s="11" t="inlineStr"/>
+      <c r="L165" s="11" t="inlineStr">
+        <is>
+          <t>4N0959754[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M165" s="11" t="inlineStr"/>
       <c r="N165" s="8" t="inlineStr">
         <is>
@@ -10968,7 +11095,11 @@
       <c r="I185" s="11" t="inlineStr"/>
       <c r="J185" s="11" t="inlineStr"/>
       <c r="K185" s="11" t="inlineStr"/>
-      <c r="L185" s="11" t="inlineStr"/>
+      <c r="L185" s="11" t="inlineStr">
+        <is>
+          <t>4N0959754[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M185" s="11" t="inlineStr"/>
       <c r="N185" s="11" t="inlineStr">
         <is>
@@ -11014,7 +11145,11 @@
       <c r="I186" s="11" t="inlineStr"/>
       <c r="J186" s="11" t="inlineStr"/>
       <c r="K186" s="11" t="inlineStr"/>
-      <c r="L186" s="11" t="inlineStr"/>
+      <c r="L186" s="11" t="inlineStr">
+        <is>
+          <t>4N0959754[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M186" s="11" t="inlineStr"/>
       <c r="N186" s="11" t="inlineStr">
         <is>
@@ -11060,7 +11195,11 @@
       <c r="I187" s="11" t="inlineStr"/>
       <c r="J187" s="11" t="inlineStr"/>
       <c r="K187" s="11" t="inlineStr"/>
-      <c r="L187" s="11" t="inlineStr"/>
+      <c r="L187" s="11" t="inlineStr">
+        <is>
+          <t>4N0959754[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M187" s="11" t="inlineStr"/>
       <c r="N187" s="14" t="inlineStr">
         <is>
@@ -11106,7 +11245,11 @@
       <c r="I188" s="11" t="inlineStr"/>
       <c r="J188" s="11" t="inlineStr"/>
       <c r="K188" s="11" t="inlineStr"/>
-      <c r="L188" s="11" t="inlineStr"/>
+      <c r="L188" s="11" t="inlineStr">
+        <is>
+          <t>4N0959754[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M188" s="11" t="inlineStr"/>
       <c r="N188" s="14" t="inlineStr">
         <is>
@@ -11152,7 +11295,11 @@
       <c r="I189" s="11" t="inlineStr"/>
       <c r="J189" s="11" t="inlineStr"/>
       <c r="K189" s="11" t="inlineStr"/>
-      <c r="L189" s="11" t="inlineStr"/>
+      <c r="L189" s="11" t="inlineStr">
+        <is>
+          <t>4N0959754[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M189" s="11" t="inlineStr"/>
       <c r="N189" s="14" t="inlineStr">
         <is>
@@ -11198,7 +11345,11 @@
       <c r="I190" s="11" t="inlineStr"/>
       <c r="J190" s="11" t="inlineStr"/>
       <c r="K190" s="11" t="inlineStr"/>
-      <c r="L190" s="11" t="inlineStr"/>
+      <c r="L190" s="11" t="inlineStr">
+        <is>
+          <t>4N0959754[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M190" s="11" t="inlineStr"/>
       <c r="N190" s="14" t="inlineStr">
         <is>
@@ -11244,7 +11395,11 @@
       <c r="I191" s="11" t="inlineStr"/>
       <c r="J191" s="11" t="inlineStr"/>
       <c r="K191" s="11" t="inlineStr"/>
-      <c r="L191" s="11" t="inlineStr"/>
+      <c r="L191" s="11" t="inlineStr">
+        <is>
+          <t>4N0959754[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M191" s="11" t="inlineStr"/>
       <c r="N191" s="11" t="inlineStr">
         <is>
@@ -11290,7 +11445,11 @@
       <c r="I192" s="11" t="inlineStr"/>
       <c r="J192" s="11" t="inlineStr"/>
       <c r="K192" s="11" t="inlineStr"/>
-      <c r="L192" s="11" t="inlineStr"/>
+      <c r="L192" s="11" t="inlineStr">
+        <is>
+          <t>4N0959754[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M192" s="11" t="inlineStr"/>
       <c r="N192" s="11" t="inlineStr">
         <is>
@@ -11336,7 +11495,11 @@
       <c r="I193" s="11" t="inlineStr"/>
       <c r="J193" s="11" t="inlineStr"/>
       <c r="K193" s="11" t="inlineStr"/>
-      <c r="L193" s="11" t="inlineStr"/>
+      <c r="L193" s="11" t="inlineStr">
+        <is>
+          <t>4N0959754[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M193" s="11" t="inlineStr"/>
       <c r="N193" s="14" t="inlineStr">
         <is>
@@ -11382,7 +11545,11 @@
       <c r="I194" s="11" t="inlineStr"/>
       <c r="J194" s="11" t="inlineStr"/>
       <c r="K194" s="11" t="inlineStr"/>
-      <c r="L194" s="11" t="inlineStr"/>
+      <c r="L194" s="11" t="inlineStr">
+        <is>
+          <t>4N0959754[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M194" s="11" t="inlineStr"/>
       <c r="N194" s="14" t="inlineStr">
         <is>
@@ -11428,7 +11595,11 @@
       <c r="I195" s="11" t="inlineStr"/>
       <c r="J195" s="11" t="inlineStr"/>
       <c r="K195" s="11" t="inlineStr"/>
-      <c r="L195" s="11" t="inlineStr"/>
+      <c r="L195" s="11" t="inlineStr">
+        <is>
+          <t>4N0959754[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M195" s="11" t="inlineStr"/>
       <c r="N195" s="14" t="inlineStr">
         <is>
@@ -11474,7 +11645,11 @@
       <c r="I196" s="11" t="inlineStr"/>
       <c r="J196" s="11" t="inlineStr"/>
       <c r="K196" s="11" t="inlineStr"/>
-      <c r="L196" s="11" t="inlineStr"/>
+      <c r="L196" s="11" t="inlineStr">
+        <is>
+          <t>4N0959754[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M196" s="11" t="inlineStr"/>
       <c r="N196" s="14" t="inlineStr">
         <is>
@@ -11520,7 +11695,11 @@
       <c r="I197" s="11" t="inlineStr"/>
       <c r="J197" s="11" t="inlineStr"/>
       <c r="K197" s="11" t="inlineStr"/>
-      <c r="L197" s="11" t="inlineStr"/>
+      <c r="L197" s="11" t="inlineStr">
+        <is>
+          <t>4N0959754[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M197" s="11" t="inlineStr"/>
       <c r="N197" s="14" t="inlineStr">
         <is>
@@ -11566,7 +11745,11 @@
       <c r="I198" s="11" t="inlineStr"/>
       <c r="J198" s="11" t="inlineStr"/>
       <c r="K198" s="11" t="inlineStr"/>
-      <c r="L198" s="11" t="inlineStr"/>
+      <c r="L198" s="11" t="inlineStr">
+        <is>
+          <t>4N0959754[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M198" s="11" t="inlineStr"/>
       <c r="N198" s="6" t="inlineStr">
         <is>
@@ -13080,7 +13263,11 @@
       <c r="I225" s="11" t="inlineStr"/>
       <c r="J225" s="11" t="inlineStr"/>
       <c r="K225" s="11" t="inlineStr"/>
-      <c r="L225" s="11" t="inlineStr"/>
+      <c r="L225" s="11" t="inlineStr">
+        <is>
+          <t>4N0959754[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M225" s="11" t="inlineStr"/>
       <c r="N225" s="11" t="inlineStr">
         <is>
@@ -13126,7 +13313,11 @@
       <c r="I226" s="11" t="inlineStr"/>
       <c r="J226" s="11" t="inlineStr"/>
       <c r="K226" s="11" t="inlineStr"/>
-      <c r="L226" s="11" t="inlineStr"/>
+      <c r="L226" s="11" t="inlineStr">
+        <is>
+          <t>4N0959754[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M226" s="11" t="inlineStr"/>
       <c r="N226" s="11" t="inlineStr">
         <is>
@@ -13172,7 +13363,11 @@
       <c r="I227" s="11" t="inlineStr"/>
       <c r="J227" s="11" t="inlineStr"/>
       <c r="K227" s="11" t="inlineStr"/>
-      <c r="L227" s="11" t="inlineStr"/>
+      <c r="L227" s="11" t="inlineStr">
+        <is>
+          <t>4N0959754[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M227" s="11" t="inlineStr"/>
       <c r="N227" s="11" t="inlineStr">
         <is>
@@ -13218,7 +13413,11 @@
       <c r="I228" s="11" t="inlineStr"/>
       <c r="J228" s="11" t="inlineStr"/>
       <c r="K228" s="11" t="inlineStr"/>
-      <c r="L228" s="11" t="inlineStr"/>
+      <c r="L228" s="11" t="inlineStr">
+        <is>
+          <t>4N0959754[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M228" s="11" t="inlineStr"/>
       <c r="N228" s="11" t="inlineStr">
         <is>
@@ -13264,7 +13463,11 @@
       <c r="I229" s="11" t="inlineStr"/>
       <c r="J229" s="11" t="inlineStr"/>
       <c r="K229" s="11" t="inlineStr"/>
-      <c r="L229" s="11" t="inlineStr"/>
+      <c r="L229" s="11" t="inlineStr">
+        <is>
+          <t>4N0959754[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M229" s="11" t="inlineStr"/>
       <c r="N229" s="14" t="inlineStr">
         <is>
@@ -13310,7 +13513,11 @@
       <c r="I230" s="11" t="inlineStr"/>
       <c r="J230" s="11" t="inlineStr"/>
       <c r="K230" s="11" t="inlineStr"/>
-      <c r="L230" s="11" t="inlineStr"/>
+      <c r="L230" s="11" t="inlineStr">
+        <is>
+          <t>4N0959754[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M230" s="11" t="inlineStr"/>
       <c r="N230" s="14" t="inlineStr">
         <is>
@@ -13356,7 +13563,11 @@
       <c r="I231" s="11" t="inlineStr"/>
       <c r="J231" s="11" t="inlineStr"/>
       <c r="K231" s="11" t="inlineStr"/>
-      <c r="L231" s="11" t="inlineStr"/>
+      <c r="L231" s="11" t="inlineStr">
+        <is>
+          <t>4N0959754[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M231" s="11" t="inlineStr"/>
       <c r="N231" s="14" t="inlineStr">
         <is>
@@ -13402,7 +13613,11 @@
       <c r="I232" s="11" t="inlineStr"/>
       <c r="J232" s="11" t="inlineStr"/>
       <c r="K232" s="11" t="inlineStr"/>
-      <c r="L232" s="11" t="inlineStr"/>
+      <c r="L232" s="11" t="inlineStr">
+        <is>
+          <t>4N0959754[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M232" s="11" t="inlineStr"/>
       <c r="N232" s="6" t="inlineStr">
         <is>
@@ -13722,7 +13937,11 @@
       <c r="I238" s="11" t="inlineStr"/>
       <c r="J238" s="11" t="inlineStr"/>
       <c r="K238" s="11" t="inlineStr"/>
-      <c r="L238" s="11" t="inlineStr"/>
+      <c r="L238" s="11" t="inlineStr">
+        <is>
+          <t>4N0959754[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M238" s="11" t="inlineStr"/>
       <c r="N238" s="14" t="inlineStr">
         <is>
@@ -13768,7 +13987,11 @@
       <c r="I239" s="11" t="inlineStr"/>
       <c r="J239" s="11" t="inlineStr"/>
       <c r="K239" s="11" t="inlineStr"/>
-      <c r="L239" s="11" t="inlineStr"/>
+      <c r="L239" s="11" t="inlineStr">
+        <is>
+          <t>4N0959754[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M239" s="11" t="inlineStr"/>
       <c r="N239" s="14" t="inlineStr">
         <is>
@@ -13814,7 +14037,11 @@
       <c r="I240" s="11" t="inlineStr"/>
       <c r="J240" s="11" t="inlineStr"/>
       <c r="K240" s="11" t="inlineStr"/>
-      <c r="L240" s="11" t="inlineStr"/>
+      <c r="L240" s="11" t="inlineStr">
+        <is>
+          <t>4N0959754[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M240" s="11" t="inlineStr"/>
       <c r="N240" s="14" t="inlineStr">
         <is>
@@ -13860,7 +14087,11 @@
       <c r="I241" s="11" t="inlineStr"/>
       <c r="J241" s="11" t="inlineStr"/>
       <c r="K241" s="11" t="inlineStr"/>
-      <c r="L241" s="11" t="inlineStr"/>
+      <c r="L241" s="11" t="inlineStr">
+        <is>
+          <t>4N0959754[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M241" s="11" t="inlineStr"/>
       <c r="N241" s="6" t="inlineStr">
         <is>
@@ -15919,7 +16150,11 @@
       </c>
       <c r="K272" s="11" t="inlineStr"/>
       <c r="L272" s="11" t="inlineStr"/>
-      <c r="M272" s="11" t="inlineStr"/>
+      <c r="M272" s="11" t="inlineStr">
+        <is>
+          <t>81A837220AG[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="N272" s="6" t="inlineStr">
         <is>
           <t>MQB IMMO5</t>
@@ -15985,7 +16220,11 @@
       </c>
       <c r="K273" s="11" t="inlineStr"/>
       <c r="L273" s="11" t="inlineStr"/>
-      <c r="M273" s="11" t="inlineStr"/>
+      <c r="M273" s="11" t="inlineStr">
+        <is>
+          <t>81A837220AG[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="N273" s="6" t="inlineStr">
         <is>
           <t>MQB IMMO5</t>
@@ -16051,7 +16290,11 @@
       </c>
       <c r="K274" s="11" t="inlineStr"/>
       <c r="L274" s="11" t="inlineStr"/>
-      <c r="M274" s="11" t="inlineStr"/>
+      <c r="M274" s="11" t="inlineStr">
+        <is>
+          <t>81A837220AG[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="N274" s="6" t="inlineStr">
         <is>
           <t>MQB IMMO5</t>
@@ -16117,7 +16360,11 @@
       </c>
       <c r="K275" s="11" t="inlineStr"/>
       <c r="L275" s="11" t="inlineStr"/>
-      <c r="M275" s="11" t="inlineStr"/>
+      <c r="M275" s="11" t="inlineStr">
+        <is>
+          <t>81A837220AG[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="N275" s="6" t="inlineStr">
         <is>
           <t>MQB IMMO5</t>
@@ -16183,7 +16430,11 @@
       </c>
       <c r="K276" s="11" t="inlineStr"/>
       <c r="L276" s="11" t="inlineStr"/>
-      <c r="M276" s="11" t="inlineStr"/>
+      <c r="M276" s="11" t="inlineStr">
+        <is>
+          <t>81A837220AG[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="N276" s="6" t="inlineStr">
         <is>
           <t>MQB IMMO5</t>
@@ -16249,7 +16500,11 @@
       </c>
       <c r="K277" s="11" t="inlineStr"/>
       <c r="L277" s="11" t="inlineStr"/>
-      <c r="M277" s="11" t="inlineStr"/>
+      <c r="M277" s="11" t="inlineStr">
+        <is>
+          <t>81A837220AG[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="N277" s="6" t="inlineStr">
         <is>
           <t>MQB IMMO5</t>
@@ -16315,7 +16570,11 @@
       </c>
       <c r="K278" s="11" t="inlineStr"/>
       <c r="L278" s="11" t="inlineStr"/>
-      <c r="M278" s="11" t="inlineStr"/>
+      <c r="M278" s="11" t="inlineStr">
+        <is>
+          <t>81A837220AG[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="N278" s="6" t="inlineStr">
         <is>
           <t>MQB IMMO5</t>
@@ -17280,7 +17539,11 @@
         </is>
       </c>
       <c r="K295" s="11" t="inlineStr"/>
-      <c r="L295" s="11" t="inlineStr"/>
+      <c r="L295" s="11" t="inlineStr">
+        <is>
+          <t>4M0959754CG[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M295" s="11" t="inlineStr"/>
       <c r="N295" s="11" t="inlineStr">
         <is>
@@ -17330,7 +17593,11 @@
         </is>
       </c>
       <c r="K296" s="11" t="inlineStr"/>
-      <c r="L296" s="11" t="inlineStr"/>
+      <c r="L296" s="11" t="inlineStr">
+        <is>
+          <t>4M0959754CG[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M296" s="11" t="inlineStr"/>
       <c r="N296" s="11" t="inlineStr">
         <is>
@@ -17380,7 +17647,11 @@
         </is>
       </c>
       <c r="K297" s="11" t="inlineStr"/>
-      <c r="L297" s="11" t="inlineStr"/>
+      <c r="L297" s="11" t="inlineStr">
+        <is>
+          <t>4M0959754CG[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M297" s="11" t="inlineStr"/>
       <c r="N297" s="11" t="inlineStr">
         <is>
@@ -17912,7 +18183,11 @@
         </is>
       </c>
       <c r="K307" s="11" t="inlineStr"/>
-      <c r="L307" s="11" t="inlineStr"/>
+      <c r="L307" s="11" t="inlineStr">
+        <is>
+          <t>4M0959754CG[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M307" s="11" t="inlineStr"/>
       <c r="N307" s="14" t="inlineStr">
         <is>
@@ -17962,7 +18237,11 @@
         </is>
       </c>
       <c r="K308" s="11" t="inlineStr"/>
-      <c r="L308" s="11" t="inlineStr"/>
+      <c r="L308" s="11" t="inlineStr">
+        <is>
+          <t>4M0959754CG[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M308" s="11" t="inlineStr"/>
       <c r="N308" s="14" t="inlineStr">
         <is>
@@ -18012,7 +18291,11 @@
         </is>
       </c>
       <c r="K309" s="11" t="inlineStr"/>
-      <c r="L309" s="11" t="inlineStr"/>
+      <c r="L309" s="11" t="inlineStr">
+        <is>
+          <t>4M0959754CG[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M309" s="11" t="inlineStr"/>
       <c r="N309" s="14" t="inlineStr">
         <is>
@@ -19196,7 +19479,11 @@
         </is>
       </c>
       <c r="K331" s="11" t="inlineStr"/>
-      <c r="L331" s="11" t="inlineStr"/>
+      <c r="L331" s="11" t="inlineStr">
+        <is>
+          <t>4N0959754AM[해외 공용 품번], 4N0959754BF[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M331" s="11" t="inlineStr"/>
       <c r="N331" s="14" t="inlineStr">
         <is>
@@ -19246,7 +19533,11 @@
         </is>
       </c>
       <c r="K332" s="11" t="inlineStr"/>
-      <c r="L332" s="11" t="inlineStr"/>
+      <c r="L332" s="11" t="inlineStr">
+        <is>
+          <t>4N0959754AM[해외 공용 품번], 4N0959754BF[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M332" s="11" t="inlineStr"/>
       <c r="N332" s="14" t="inlineStr">
         <is>
@@ -19296,7 +19587,11 @@
         </is>
       </c>
       <c r="K333" s="11" t="inlineStr"/>
-      <c r="L333" s="11" t="inlineStr"/>
+      <c r="L333" s="11" t="inlineStr">
+        <is>
+          <t>4N0959754AM[해외 공용 품번], 4N0959754BF[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M333" s="11" t="inlineStr"/>
       <c r="N333" s="14" t="inlineStr">
         <is>
@@ -19346,7 +19641,11 @@
         </is>
       </c>
       <c r="K334" s="11" t="inlineStr"/>
-      <c r="L334" s="11" t="inlineStr"/>
+      <c r="L334" s="11" t="inlineStr">
+        <is>
+          <t>4N0959754AM[해외 공용 품번], 4N0959754BF[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M334" s="11" t="inlineStr"/>
       <c r="N334" s="14" t="inlineStr">
         <is>
@@ -19396,7 +19695,11 @@
         </is>
       </c>
       <c r="K335" s="11" t="inlineStr"/>
-      <c r="L335" s="11" t="inlineStr"/>
+      <c r="L335" s="11" t="inlineStr">
+        <is>
+          <t>4N0959754AM[해외 공용 품번], 4N0959754BF[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M335" s="11" t="inlineStr"/>
       <c r="N335" s="14" t="inlineStr">
         <is>
@@ -19446,7 +19749,11 @@
         </is>
       </c>
       <c r="K336" s="11" t="inlineStr"/>
-      <c r="L336" s="11" t="inlineStr"/>
+      <c r="L336" s="11" t="inlineStr">
+        <is>
+          <t>4N0959754AM[해외 공용 품번], 4N0959754BF[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M336" s="11" t="inlineStr"/>
       <c r="N336" s="14" t="inlineStr">
         <is>
@@ -19496,7 +19803,11 @@
         </is>
       </c>
       <c r="K337" s="11" t="inlineStr"/>
-      <c r="L337" s="11" t="inlineStr"/>
+      <c r="L337" s="11" t="inlineStr">
+        <is>
+          <t>4N0959754AM[해외 공용 품번], 4N0959754BF[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M337" s="11" t="inlineStr"/>
       <c r="N337" s="14" t="inlineStr">
         <is>
@@ -19546,7 +19857,11 @@
         </is>
       </c>
       <c r="K338" s="11" t="inlineStr"/>
-      <c r="L338" s="11" t="inlineStr"/>
+      <c r="L338" s="11" t="inlineStr">
+        <is>
+          <t>4N0959754AM[해외 공용 품번], 4N0959754BF[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M338" s="11" t="inlineStr"/>
       <c r="N338" s="14" t="inlineStr">
         <is>
@@ -19970,7 +20285,11 @@
       <c r="I346" s="11" t="inlineStr"/>
       <c r="J346" s="11" t="inlineStr"/>
       <c r="K346" s="11" t="inlineStr"/>
-      <c r="L346" s="11" t="inlineStr"/>
+      <c r="L346" s="11" t="inlineStr">
+        <is>
+          <t>4N0959754AM[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M346" s="11" t="inlineStr"/>
       <c r="N346" s="11" t="inlineStr">
         <is>
@@ -20016,7 +20335,11 @@
       <c r="I347" s="11" t="inlineStr"/>
       <c r="J347" s="11" t="inlineStr"/>
       <c r="K347" s="11" t="inlineStr"/>
-      <c r="L347" s="11" t="inlineStr"/>
+      <c r="L347" s="11" t="inlineStr">
+        <is>
+          <t>4N0959754AM[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M347" s="11" t="inlineStr"/>
       <c r="N347" s="11" t="inlineStr">
         <is>
@@ -20062,7 +20385,11 @@
       <c r="I348" s="11" t="inlineStr"/>
       <c r="J348" s="11" t="inlineStr"/>
       <c r="K348" s="11" t="inlineStr"/>
-      <c r="L348" s="11" t="inlineStr"/>
+      <c r="L348" s="11" t="inlineStr">
+        <is>
+          <t>4N0959754AM[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M348" s="11" t="inlineStr"/>
       <c r="N348" s="14" t="inlineStr">
         <is>
@@ -20108,7 +20435,11 @@
       <c r="I349" s="11" t="inlineStr"/>
       <c r="J349" s="11" t="inlineStr"/>
       <c r="K349" s="11" t="inlineStr"/>
-      <c r="L349" s="11" t="inlineStr"/>
+      <c r="L349" s="11" t="inlineStr">
+        <is>
+          <t>4N0959754AM[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M349" s="11" t="inlineStr"/>
       <c r="N349" s="14" t="inlineStr">
         <is>
@@ -20154,7 +20485,11 @@
       <c r="I350" s="11" t="inlineStr"/>
       <c r="J350" s="11" t="inlineStr"/>
       <c r="K350" s="11" t="inlineStr"/>
-      <c r="L350" s="11" t="inlineStr"/>
+      <c r="L350" s="11" t="inlineStr">
+        <is>
+          <t>4N0959754AM[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M350" s="11" t="inlineStr"/>
       <c r="N350" s="14" t="inlineStr">
         <is>
@@ -20200,7 +20535,11 @@
       <c r="I351" s="11" t="inlineStr"/>
       <c r="J351" s="11" t="inlineStr"/>
       <c r="K351" s="11" t="inlineStr"/>
-      <c r="L351" s="11" t="inlineStr"/>
+      <c r="L351" s="11" t="inlineStr">
+        <is>
+          <t>4N0959754AM[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M351" s="11" t="inlineStr"/>
       <c r="N351" s="14" t="inlineStr">
         <is>
@@ -20246,7 +20585,11 @@
       <c r="I352" s="11" t="inlineStr"/>
       <c r="J352" s="11" t="inlineStr"/>
       <c r="K352" s="11" t="inlineStr"/>
-      <c r="L352" s="11" t="inlineStr"/>
+      <c r="L352" s="11" t="inlineStr">
+        <is>
+          <t>4N0959754AM[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M352" s="11" t="inlineStr"/>
       <c r="N352" s="6" t="inlineStr">
         <is>
@@ -20596,7 +20939,11 @@
       <c r="I359" s="11" t="inlineStr"/>
       <c r="J359" s="11" t="inlineStr"/>
       <c r="K359" s="11" t="inlineStr"/>
-      <c r="L359" s="11" t="inlineStr"/>
+      <c r="L359" s="11" t="inlineStr">
+        <is>
+          <t>4N0959754AQ[해외 공용 품번], 4N0959754BQ[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M359" s="11" t="inlineStr"/>
       <c r="N359" s="14" t="inlineStr">
         <is>
@@ -20642,7 +20989,11 @@
       <c r="I360" s="11" t="inlineStr"/>
       <c r="J360" s="11" t="inlineStr"/>
       <c r="K360" s="11" t="inlineStr"/>
-      <c r="L360" s="11" t="inlineStr"/>
+      <c r="L360" s="11" t="inlineStr">
+        <is>
+          <t>4N0959754AQ[해외 공용 품번], 4N0959754BQ[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M360" s="11" t="inlineStr"/>
       <c r="N360" s="11" t="inlineStr">
         <is>
@@ -20688,7 +21039,11 @@
       <c r="I361" s="11" t="inlineStr"/>
       <c r="J361" s="11" t="inlineStr"/>
       <c r="K361" s="11" t="inlineStr"/>
-      <c r="L361" s="11" t="inlineStr"/>
+      <c r="L361" s="11" t="inlineStr">
+        <is>
+          <t>4N0959754AQ[해외 공용 품번], 4N0959754BQ[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M361" s="11" t="inlineStr"/>
       <c r="N361" s="11" t="inlineStr">
         <is>
@@ -20734,7 +21089,11 @@
       <c r="I362" s="11" t="inlineStr"/>
       <c r="J362" s="11" t="inlineStr"/>
       <c r="K362" s="11" t="inlineStr"/>
-      <c r="L362" s="11" t="inlineStr"/>
+      <c r="L362" s="11" t="inlineStr">
+        <is>
+          <t>4N0959754AQ[해외 공용 품번], 4N0959754BQ[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M362" s="11" t="inlineStr"/>
       <c r="N362" s="11" t="inlineStr">
         <is>
@@ -20780,7 +21139,11 @@
       <c r="I363" s="11" t="inlineStr"/>
       <c r="J363" s="11" t="inlineStr"/>
       <c r="K363" s="11" t="inlineStr"/>
-      <c r="L363" s="11" t="inlineStr"/>
+      <c r="L363" s="11" t="inlineStr">
+        <is>
+          <t>4N0959754AQ[해외 공용 품번], 4N0959754BQ[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M363" s="11" t="inlineStr"/>
       <c r="N363" s="11" t="inlineStr">
         <is>
@@ -20826,7 +21189,11 @@
       <c r="I364" s="11" t="inlineStr"/>
       <c r="J364" s="11" t="inlineStr"/>
       <c r="K364" s="11" t="inlineStr"/>
-      <c r="L364" s="11" t="inlineStr"/>
+      <c r="L364" s="11" t="inlineStr">
+        <is>
+          <t>4N0959754AQ[해외 공용 품번], 4N0959754BQ[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M364" s="11" t="inlineStr"/>
       <c r="N364" s="14" t="inlineStr">
         <is>
@@ -20872,7 +21239,11 @@
       <c r="I365" s="11" t="inlineStr"/>
       <c r="J365" s="11" t="inlineStr"/>
       <c r="K365" s="11" t="inlineStr"/>
-      <c r="L365" s="11" t="inlineStr"/>
+      <c r="L365" s="11" t="inlineStr">
+        <is>
+          <t>4N0959754AQ[해외 공용 품번], 4N0959754BQ[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M365" s="11" t="inlineStr"/>
       <c r="N365" s="6" t="inlineStr">
         <is>
@@ -20922,7 +21293,11 @@
       <c r="I366" s="11" t="inlineStr"/>
       <c r="J366" s="11" t="inlineStr"/>
       <c r="K366" s="11" t="inlineStr"/>
-      <c r="L366" s="11" t="inlineStr"/>
+      <c r="L366" s="11" t="inlineStr">
+        <is>
+          <t>4N0959754AQ[해외 공용 품번], 4N0959754BQ[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M366" s="11" t="inlineStr"/>
       <c r="N366" s="11" t="inlineStr">
         <is>
@@ -20968,7 +21343,11 @@
       <c r="I367" s="11" t="inlineStr"/>
       <c r="J367" s="11" t="inlineStr"/>
       <c r="K367" s="11" t="inlineStr"/>
-      <c r="L367" s="11" t="inlineStr"/>
+      <c r="L367" s="11" t="inlineStr">
+        <is>
+          <t>4N0959754AQ[해외 공용 품번], 4N0959754BQ[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M367" s="11" t="inlineStr"/>
       <c r="N367" s="11" t="inlineStr">
         <is>
@@ -21014,7 +21393,11 @@
       <c r="I368" s="11" t="inlineStr"/>
       <c r="J368" s="11" t="inlineStr"/>
       <c r="K368" s="11" t="inlineStr"/>
-      <c r="L368" s="11" t="inlineStr"/>
+      <c r="L368" s="11" t="inlineStr">
+        <is>
+          <t>4N0959754AQ[해외 공용 품번], 4N0959754BQ[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M368" s="11" t="inlineStr"/>
       <c r="N368" s="6" t="inlineStr">
         <is>
@@ -23942,7 +24325,11 @@
       <c r="I412" s="11" t="inlineStr"/>
       <c r="J412" s="11" t="inlineStr"/>
       <c r="K412" s="11" t="inlineStr"/>
-      <c r="L412" s="11" t="inlineStr"/>
+      <c r="L412" s="11" t="inlineStr">
+        <is>
+          <t>4H0959754EB[해외 공용 품번], 4H0959754FK[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M412" s="11" t="inlineStr"/>
       <c r="N412" s="6" t="inlineStr">
         <is>
@@ -24004,7 +24391,11 @@
       <c r="I413" s="11" t="inlineStr"/>
       <c r="J413" s="11" t="inlineStr"/>
       <c r="K413" s="11" t="inlineStr"/>
-      <c r="L413" s="11" t="inlineStr"/>
+      <c r="L413" s="11" t="inlineStr">
+        <is>
+          <t>4H0959754EB[해외 공용 품번], 4H0959754FK[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M413" s="11" t="inlineStr"/>
       <c r="N413" s="6" t="inlineStr">
         <is>
@@ -24066,7 +24457,11 @@
       <c r="I414" s="11" t="inlineStr"/>
       <c r="J414" s="11" t="inlineStr"/>
       <c r="K414" s="11" t="inlineStr"/>
-      <c r="L414" s="11" t="inlineStr"/>
+      <c r="L414" s="11" t="inlineStr">
+        <is>
+          <t>4H0959754EB[해외 공용 품번], 4H0959754FK[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M414" s="11" t="inlineStr"/>
       <c r="N414" s="6" t="inlineStr">
         <is>
@@ -24128,7 +24523,11 @@
       <c r="I415" s="11" t="inlineStr"/>
       <c r="J415" s="11" t="inlineStr"/>
       <c r="K415" s="11" t="inlineStr"/>
-      <c r="L415" s="11" t="inlineStr"/>
+      <c r="L415" s="11" t="inlineStr">
+        <is>
+          <t>4H0959754EB[해외 공용 품번], 4H0959754FK[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M415" s="11" t="inlineStr"/>
       <c r="N415" s="6" t="inlineStr">
         <is>
@@ -24190,7 +24589,11 @@
       <c r="I416" s="11" t="inlineStr"/>
       <c r="J416" s="11" t="inlineStr"/>
       <c r="K416" s="11" t="inlineStr"/>
-      <c r="L416" s="11" t="inlineStr"/>
+      <c r="L416" s="11" t="inlineStr">
+        <is>
+          <t>4H0959754EB[해외 공용 품번], 4H0959754FK[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M416" s="11" t="inlineStr"/>
       <c r="N416" s="6" t="inlineStr">
         <is>
@@ -24252,7 +24655,11 @@
       <c r="I417" s="11" t="inlineStr"/>
       <c r="J417" s="11" t="inlineStr"/>
       <c r="K417" s="11" t="inlineStr"/>
-      <c r="L417" s="11" t="inlineStr"/>
+      <c r="L417" s="11" t="inlineStr">
+        <is>
+          <t>4H0959754EB[해외 공용 품번], 4H0959754FK[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M417" s="11" t="inlineStr"/>
       <c r="N417" s="6" t="inlineStr">
         <is>
@@ -24314,7 +24721,11 @@
       <c r="I418" s="11" t="inlineStr"/>
       <c r="J418" s="11" t="inlineStr"/>
       <c r="K418" s="11" t="inlineStr"/>
-      <c r="L418" s="11" t="inlineStr"/>
+      <c r="L418" s="11" t="inlineStr">
+        <is>
+          <t>4H0959754EB[해외 공용 품번], 4H0959754FK[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M418" s="11" t="inlineStr"/>
       <c r="N418" s="6" t="inlineStr">
         <is>
@@ -24376,7 +24787,11 @@
       <c r="I419" s="11" t="inlineStr"/>
       <c r="J419" s="11" t="inlineStr"/>
       <c r="K419" s="11" t="inlineStr"/>
-      <c r="L419" s="11" t="inlineStr"/>
+      <c r="L419" s="11" t="inlineStr">
+        <is>
+          <t>4H0959754EB[해외 공용 품번], 4H0959754FK[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M419" s="11" t="inlineStr"/>
       <c r="N419" s="6" t="inlineStr">
         <is>
@@ -25014,460 +25429,467 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A69"/>
+  <dimension ref="A1:A70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="150" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="24" t="inlineStr">
+      <c r="A1" s="25" t="inlineStr">
         <is>
           <t>이 표는 락스미스(자동차 키 제작/프로그래밍) 참고용입니다.</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="24" t="inlineStr"/>
+      <c r="A2" s="25" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="24" t="inlineStr">
+      <c r="A3" s="25" t="inlineStr">
         <is>
           <t>※ 구성</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="24" t="inlineStr">
+      <c r="A4" s="25" t="inlineStr">
         <is>
           <t>- 맨 앞 '브랜드' 컬럼에 브랜드명을 적었습니다(검색 프로그램에서 '기아 K5'처럼 브랜드와 모델명을 함께 검색 가능).</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="24" t="inlineStr">
+      <c r="A5" s="25" t="inlineStr">
         <is>
           <t>- 컬럼은 '기아_트랜스폰더_칩코드_DBnew.xlsx'와 같고, 칩코드 뒤에 '키종류'를 추가했습니다. 모델마다 연식별로 한 행씩, 2000년식부터 기록했습니다.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="24" t="inlineStr">
+      <c r="A6" s="25" t="inlineStr">
         <is>
           <t>- 연식은 실제 국내 판매 기준입니다. 원본 목록 연식과 국내 출시 시점이 다른 모델은 국내 기준으로 바꿨습니다(아래 목록). 단종 모델의 마지막 연식은 '2016(단종)' 형식입니다.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="24" t="inlineStr">
+      <c r="A7" s="25" t="inlineStr">
         <is>
           <t>- '키종류'는 그 연식에 나온 키 형태(막대키·폴딩키·스마트키·카드키)를 모두 적었습니다. 카드키는 PPE/PPC 차량의 NFC 키카드(Audi connect Key Card)입니다.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="24" t="inlineStr">
+      <c r="A8" s="25" t="inlineStr">
         <is>
           <t>- 키 부품번호는 국내 사양(433/434MHz)만 적었습니다. 미국형(315MHz, FCC IYZFBSB802·IYZ-AK01/AK2·NBG009272T 등 미국 딜러 품번)과 유럽 868MHz 사양은 뺐습니다.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="24" t="inlineStr">
+      <c r="A9" s="25" t="inlineStr">
         <is>
           <t>- '비고'에는 주황색·빨간색 칸의 이유만 적었습니다.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="24" t="inlineStr">
+      <c r="A10" s="25" t="inlineStr">
         <is>
           <t>- 칩코드는 세대별 방식입니다: ID48 Megamos(구형 폴딩키) / ID8E(A6 C6·Q7 4L) / ID46 Hitag2(A8 D3) / BCM2 PCF7945AC(2008~2018 B8·C7·D4·8R) / MQB Megamos AES(MQB48) / MQB-Evo Hitag Pro(MQB49, 8Y) / MLB·MLB evo 전용 키 / PPE·PPC·MEB 신형 키.</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="24" t="inlineStr">
+      <c r="A11" s="25" t="inlineStr">
         <is>
           <t>- BCM2·MLB·MLB evo 키는 일반 트랜스폰더(ID46 등)로 복제하는 방식이 아니라서 'XT27A/A66·XT27B·XT57B 호환' 칸을 비웠습니다.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="24" t="inlineStr">
+      <c r="A12" s="25" t="inlineStr">
         <is>
           <t>- 키블레이드(키웨이)는 비상키 블레이드입니다(HU66, Q2·Q3 F3·TT 8S·Q8은 HU162T 표기 병존). 키블레이드 부품번호는 MLB 비상키 4M0837216A만 찾았습니다.</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="24" t="inlineStr">
+      <c r="A13" s="25" t="inlineStr">
         <is>
           <t>- 출처 칸은 검색에서 근거로 쓴 페이지입니다. 원문은 이 환경에서 열 수 없어 검색 결과 요약을 근거로 했습니다. 부품 판매처는 대부분 미국·유럽 사이트입니다.</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="24" t="inlineStr"/>
+      <c r="A14" s="25" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="24" t="inlineStr">
+      <c r="A15" s="25" t="inlineStr">
         <is>
           <t>※ 색상</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="24" t="inlineStr">
+      <c r="A16" s="25" t="inlineStr">
         <is>
           <t>- 주황색: 추정이거나 자료가 서로 다른 값, 해당 연식 칩 자료가 없어 같은 세대 기준으로 채운 값, 또는 국내 미판매 모델(해외 사양 기준) — 실물 키로 재확인.</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="24" t="inlineStr">
+      <c r="A17" s="25" t="inlineStr">
         <is>
           <t>- 빨간색: 확인 불가 — PPE·PPC·MEB 신형 키(A5·S5 B10, Q5·SQ5 3세대, A6·S6 e-트론, Q6 e-트론, Q4 e-트론, 3세대 Q3)는 칩·이모빌라이저 자료가 없습니다.</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="24" t="inlineStr">
+      <c r="A18" s="25" t="inlineStr">
         <is>
           <t>- 전환 연식은 칩코드·이모빌라이저 칸에 전·후를 함께 적었습니다(예: TT 2015 = ID48[8J, 2015.10 이전], ID88[8S]). 후속 모델 칩이 확인 불가면 빨간색입니다.</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="24" t="inlineStr"/>
+      <c r="A19" s="25" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="24" t="inlineStr">
+      <c r="A20" s="25" t="inlineStr">
         <is>
           <t>※ 목록과 국내 판매 연식이 다른 모델</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="24" t="inlineStr">
+      <c r="A21" s="25" t="inlineStr">
         <is>
           <t>- A1: 2015.06 첫 출시, 2016 디젤게이트로 판매 중단 → 2015~2016만 기록(목록 2012-2018).</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="24" t="inlineStr">
+      <c r="A22" s="25" t="inlineStr">
         <is>
           <t>- A3 8P: 스포트백 2008.10 출시 → 2008~2012 / A3 8Y: 2022.07 출시 → 2022~ / S3 8Y: 2022.12 출시 → 2022~ / RS3: 8V 국내 미판매, 8Y 2023.07 출시 → 2023~.</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="24" t="inlineStr">
+      <c r="A23" s="25" t="inlineStr">
         <is>
           <t>- A5 B10: 2025.07 출시(목록 2024~) / A7 C8: 2020.03 / S7: 2020.07 / A8 D5: 2019.12 / S6 C8: 2020.07 / S8: D4는 2017까지, D5 S8 L은 2023.07 출시.</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="24" t="inlineStr">
+      <c r="A24" s="25" t="inlineStr">
         <is>
           <t>- RS6 아반트·RS7: C7 2014.08 출시, C8 2021.08 출시 → 2019~2020년식 없음.</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="24" t="inlineStr">
+      <c r="A25" s="25" t="inlineStr">
         <is>
           <t>- Q2: 2020.09 출시(2018 부산모터쇼 공개 후 연기) / Q3 F3: 2020.05 / Q5·SQ5 FY: 2020.05.13 / Q7 4L: 2006.07 판매 시작 / Q7 4M: 2016.03 / SQ7: 2024.01 첫 출시.</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="24" t="inlineStr">
+      <c r="A26" s="25" t="inlineStr">
         <is>
           <t>- Q8: 2020.04.01 첫 출시 / RS Q8: 2021.06 / e-트론 55: 2020.07.01 / SQ8 e-트론: 2024.06.10 / R8 2세대: 2017.11(1세대 국내 판매는 2016.02까지).</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="24" t="inlineStr">
+      <c r="A27" s="25" t="inlineStr">
         <is>
           <t>- 국내 정식 판매 이력이 없는 모델: SQ2, RS Q3, TT RS(2019 인증만). 목록 연식대로 남기고 주황색(해외 사양 기준)으로 표시했습니다.</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="24" t="inlineStr"/>
+      <c r="A28" s="25" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="24" t="inlineStr">
+      <c r="A29" s="25" t="inlineStr">
         <is>
           <t>※ 조사하며 확인된 주요 사항</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="24" t="inlineStr">
+      <c r="A30" s="25" t="inlineStr">
         <is>
           <t>- 모델마다 연식별로 검색했고 연식별 검색 기록은 research/audi/yearly.md에 있습니다.</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="24" t="inlineStr">
+      <c r="A31" s="25" t="inlineStr">
         <is>
           <t>- BCM2(2008~2018): 키 주파수는 BCM2 코드로 구분(5D1=433MHz, 5D2~5D4=315MHz, 5D7=868MHz). 2013년경부터 공장 잠김(locked) BCM2가 나와 올키로스트는 OBD만으로 안 되고 온라인 해제(Abrites VN020 등)나 벤치 읽기가 필요합니다.</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="24" t="inlineStr">
+      <c r="A32" s="25" t="inlineStr">
         <is>
           <t>- MQB(8V·Q2·Q3 F3·TT 8S)는 Megamos AES(ID88), 8Y(A3·S3·RS3 2021~)는 Hitag Pro MQB49(NCF295X)이며 GeKo 온라인 로그인이 필요합니다. 일부 판매처는 8Y를 AES ID88로 표기합니다.</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="24" t="inlineStr">
+      <c r="A33" s="25" t="inlineStr">
         <is>
           <t>- MLB(B9·Q5 FY·Q7 4M): 국내형 순정 스마트키 4M0959754BA(433MHz, 5M 칩, 2017-2021), 2016 Q7 4M0959754BC(434MHz). 중고 키는 VIN 잠금이라 재등록이 어렵습니다.</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="24" t="inlineStr">
+      <c r="A34" s="25" t="inlineStr">
         <is>
           <t>- MLB evo(C8·D5·Q8·e-트론·e-트론 GT): Q8 4N0959754BL(434MHz), RS6·RS7·RS Q8·RS e-트론 GT 4N0959754BC(433.92MHz). 미국 딜러 품번 4N0959754AM/K/BF는 뺐습니다.</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="24" t="inlineStr">
+      <c r="A35" s="25" t="inlineStr">
         <is>
           <t>- 구형 국내형 폴딩키: A3 8P·TT 8J 8P0837220D(434MHz), A1·Q3 8U 8X0837220D(434MHz), A4 B7 8E0837220E/Q/K(433MHz), A6 C6·Q7 4L 4F0837220M/T(434MHz), A8 D3 4E0837220M/D(433MHz), R8 1세대 420837220(433MHz).</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="24" t="inlineStr">
+      <c r="A36" s="25" t="inlineStr">
         <is>
           <t>- Q2 81A837220D(434MHz, Megamos AES), Q3 F3 81A837220AG(434MHz), TT 8S 8S0959754AK(434MHz, ID88), A3/S3 8V 8V0837220D(434MHz), A3/S3/RS3 8Y 8Y0959754AN(434MHz).</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="24" t="inlineStr">
+      <c r="A37" s="25" t="inlineStr">
         <is>
           <t>- PPE(A6 e-트론·Q6 e-트론)·PPC(A5·Q5 3세대)는 UWB/NFC 디지털 키가 표준이고 NFC 키카드가 제공됩니다. Q4 e-트론은 RSAD UWB(릴레이 공격 탐지) 키입니다.</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="24" t="n"/>
+      <c r="A38" s="25" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="24" t="inlineStr">
+      <c r="A39" s="25" t="inlineStr">
         <is>
           <t>※ 표기 규칙 (칩코드·부품번호·키웨이·이모빌라이저 칸 공통)</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="24" t="inlineStr">
+      <c r="A40" s="25" t="inlineStr">
         <is>
           <t>- 한 칸에 값이 여러 개면 ', '(쉼표)로만 구분합니다. '/', '·', '또는'은 쓰지 않고, 줄임(예: 4F0837220M/T, 5WK49145~49147)도 모두 풀어서 따로 적었습니다.</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="24" t="inlineStr">
+      <c r="A41" s="25" t="inlineStr">
         <is>
           <t>- ( ) 안에는 부품번호만 적습니다. 칩코드 'ID49(PCF7953)' = ID49 칩, 칩 부품번호 PCF7953. 이모빌라이저 'SKM(87570-36010)' = SKM 모듈, 품번 87570-36010. 칩 부품번호를 모르면 'ID46'처럼 ID만 적었습니다.</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="24" t="inlineStr">
+      <c r="A42" s="25" t="inlineStr">
         <is>
           <t>- [ ] 안에는 그 값이 적용되는 조건을 적습니다(키 종류·버튼 수·옵션·생산 시기·차종 코드). 예: ID46(PCF7936)[폴딩키], ID46(PCF7952A)[스마트키] → 폴딩키는 PCF7936, 스마트키는 PCF7952A.</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="24" t="inlineStr">
+      <c r="A43" s="25" t="inlineStr">
         <is>
           <t>- [추정] = 추정값, [일부 자료] = 일부 자료에만 나오는 값, [자료 상충] = 자료마다 달라 둘 중 무엇인지 미확정, [해외 공용 품번] = 해외 공용 품번(국내 순정 품번 미확인).</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="24" t="inlineStr">
+      <c r="A44" s="25" t="inlineStr">
         <is>
           <t>- 부품번호 칸에는 부품번호만 적습니다. 'FCC ' = 미국 FCC 인증번호(키 모델 식별용), 'KC ' = 한국 전파인증번호. 순정(제조사) 부품번호만 적고 애프터마켓 호환품 번호는 넣지 않았습니다. 설명·판매처·주파수(모두 국내 433/434MHz)는 적지 않았고, 부품번호가 없으면 공란입니다.</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="24" t="inlineStr">
+      <c r="A45" s="25" t="inlineStr">
         <is>
           <t>- Hitag2·Hitag Pro·Megamos·DST80 같은 칩 방식 이름은 ID 코드와 같은 뜻이라 칸에 따로 적지 않았습니다(아래 표).</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="24" t="n"/>
+      <c r="A46" s="25" t="n"/>
     </row>
     <row r="47">
-      <c r="A47" s="24" t="inlineStr">
+      <c r="A47" s="25" t="inlineStr">
         <is>
           <t>※ 칩 ID 코드 뜻</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="24" t="inlineStr">
+      <c r="A48" s="25" t="inlineStr">
         <is>
           <t>- ID13: Megamos 13(고정 코드)  |  ID44: Philips Crypto(PCF7935, BMW EWS 구형)  |  ID48: Megamos Crypto</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="24" t="inlineStr">
+      <c r="A49" s="25" t="inlineStr">
         <is>
           <t>- ID46: Philips Hitag2 계열(PCF7936·PCF7941·PCF7945·PCF7952 등). [Extended] = Hitag2 Extended, [Circle Plus] = GM Circle Plus</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="24" t="inlineStr">
+      <c r="A50" s="25" t="inlineStr">
         <is>
           <t>- ID47: NXP Hitag3(NCF2951·NCF2952·NCF2971·PCF7938 등)  |  ID49: NXP Hitag Pro(PCF7953P·NCF2951·NCF295X 등)  |  ID4A: NXP Hitag AES(NCF29A1M·PCF7953M·PCF7961M 등)</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="24" t="inlineStr">
+      <c r="A51" s="25" t="inlineStr">
         <is>
           <t>- ID60: Texas 4D60(40bit)  |  4D60x80: Texas 4D60 80bit(DST80 계열)  |  ID70: Texas 4D70  |  ID6E-MA: Texas DST80(현대·기아 표기)</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="24" t="inlineStr">
+      <c r="A52" s="25" t="inlineStr">
         <is>
           <t>- ID6A·ID8A: Texas Crypto AES(DST-AES)  |  ID75: Texas AES(판매처 표기)  |  ID88: Megamos AES(VW·아우디 MQB)  |  ID8E: 아우디 8E Crypto(Sokymat 8E)</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="24" t="inlineStr">
+      <c r="A53" s="25" t="inlineStr">
         <is>
           <t>- FBS3·FBS4: 벤츠 NEC 프로세서 키(ID 칩이 아님)  |  MLB 전용 칩·MLB evo 전용 칩: 아우디 MLB 플랫폼 전용 키 칩</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="24" t="inlineStr">
+      <c r="A54" s="25" t="inlineStr">
         <is>
           <t>- 확인 불가 = 자료로 확인하지 못함  |  해당 없음 = 이모빌라이저 미적용</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="24" t="n"/>
+      <c r="A55" s="25" t="n"/>
     </row>
     <row r="56">
-      <c r="A56" s="24" t="inlineStr">
+      <c r="A56" s="25" t="inlineStr">
         <is>
           <t>※ 재조사로 확인한 근거 (색을 지운 행)</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="24" t="inlineStr">
+      <c r="A57" s="25" t="inlineStr">
         <is>
           <t>- 아우디 A3 8V 2020·S3 2019·A5 B9 2020·A7 C7 2014·A8 D3 2008·Q2 2022·Q3 F3 2023·Q5 8R 2011·Q7 4L 2006·Q7 4M 2017·TT 8J 2014·TTS 2021·R8 42 2009: 같은 세대 안의 연식이라 키(부품번호)·칩이 앞뒤 확정 연식과 같음 — 연식별 판매처 표기 차이는 세대 구분 오류로 보고 색 지움</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="24" t="n"/>
+      <c r="A58" s="25" t="n"/>
     </row>
     <row r="59">
-      <c r="A59" s="24" t="inlineStr">
+      <c r="A59" s="25" t="inlineStr">
         <is>
           <t>※ 행 구분 규칙</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="24" t="inlineStr">
+      <c r="A60" s="25" t="inlineStr">
         <is>
           <t>- 연식 중간에 칩·이모빌라이저·키가 바뀐 해는 바뀌기 전·후를 따로 행으로 나눔. 세대가 바뀌면 세대별 모델명으로 1행씩, 같은 세대 안의 변경(부분변경·생산 시기·키 변경)은 같은 모델명으로 나누고 칸 안의 [생산 시기]·[세대] 표기로 구분</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="24" t="inlineStr">
+      <c r="A61" s="25" t="inlineStr">
         <is>
           <t>- 같은 연식·모델에 행이 2개인데 칸에 시기 표기가 없으면(예: 벤츠 FBS3 행과 FBS4 행) 전환 시점 자료가 없는 것 — 주황색, 비고의 방법(VIN 등)으로 확인</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="24" t="inlineStr">
+      <c r="A62" s="25" t="inlineStr">
         <is>
           <t>- A3 8Y 2026: 스마트키 8Y0959754 계열 적용 연식 2020~2026(go-parts) — 같은 세대 키 계속 사용 확인</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="24" t="inlineStr">
+      <c r="A63" s="25" t="inlineStr">
         <is>
           <t>- RS3 2026: 8Y0959754DD 적용(2022~2026) — 8Y 공용 키 확인</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="24" t="inlineStr">
+      <c r="A64" s="25" t="inlineStr">
         <is>
           <t>- Q2 2024~2026: 국내 2026년까지 판매, MQB 키 81A837220(ID88) 적용 연식 계속 — 추정 해제</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="24" t="inlineStr">
+      <c r="A65" s="25" t="inlineStr">
         <is>
           <t>- Q8 2026: 4N0959754AM 적용 2019~2026 — MLB evo 키 확인</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="24" t="inlineStr">
+      <c r="A66" s="25" t="inlineStr">
         <is>
           <t>- RS7 2026: 4N0959754BC 적용 2021~2026 — MLB evo 키 확인</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="24" t="inlineStr">
+      <c r="A67" s="25" t="inlineStr">
         <is>
           <t>- RS Q8 2026: 4N0959754BC 적용 2020~2026 — MLB evo 키 확인</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="24" t="inlineStr">
+      <c r="A68" s="25" t="inlineStr">
         <is>
           <t>- RS6 아반트 2026: 4N0959754BC(C8 공용) 적용 — MLB evo 키 확인</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="24" t="inlineStr">
+      <c r="A69" s="25" t="inlineStr">
         <is>
           <t>- Q7 4M 2022~2026·SQ7 2024~2026: 2023·2024 Q7/SQ7 키 4N0959754BF·AM(A8 D5·Q8과 같은 MLB evo 키) — 칩·이모빌라이저를 MLB evo로 정정</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="25" t="inlineStr">
+        <is>
+          <t>- 아우디 순정 부품번호(공란 행 보완): 4N0959754 = A6 C8·A7 C8·A8 D5·Q8 433MHz 스마트키(remkeys·autokeystore), 4N0959754AM·BF = Q7 4M·SQ7·Q8(Audi USA), 4N0959754AQ·BQ = e-tron·Q8 e-tron(Audi USA·auto-keys.eu 433MHz), 4M0959754CG = 2017~2024 A4·A5·S4·S5·Q5·SQ5·Q7 433MHz, 4H0959754EB·FK = R8 4S, 81A837220AG = Q3 F3 계열 폴딩키 — 한국 사양 번호 미확인이라 [해외 공용 품번]</t>
         </is>
       </c>
     </row>

--- a/아우디_models.xlsx
+++ b/아우디_models.xlsx
@@ -136,7 +136,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -200,6 +200,9 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
@@ -6387,12 +6390,12 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="D97" s="7" t="inlineStr"/>
-      <c r="E97" s="7" t="inlineStr"/>
-      <c r="F97" s="7" t="inlineStr"/>
-      <c r="G97" s="8" t="inlineStr">
-        <is>
-          <t>확인 불가</t>
+      <c r="D97" s="7" t="n"/>
+      <c r="E97" s="7" t="n"/>
+      <c r="F97" s="7" t="n"/>
+      <c r="G97" s="6" t="inlineStr">
+        <is>
+          <t>MLB evo 전용 칩[추정]</t>
         </is>
       </c>
       <c r="H97" s="11" t="inlineStr">
@@ -6401,23 +6404,27 @@
         </is>
       </c>
       <c r="I97" s="11" t="inlineStr"/>
-      <c r="J97" s="11" t="inlineStr"/>
+      <c r="J97" s="11" t="inlineStr">
+        <is>
+          <t>HU162T</t>
+        </is>
+      </c>
       <c r="K97" s="11" t="inlineStr"/>
       <c r="L97" s="11" t="inlineStr"/>
       <c r="M97" s="11" t="inlineStr"/>
-      <c r="N97" s="8" t="inlineStr">
+      <c r="N97" s="6" t="inlineStr">
         <is>
           <t>확인 불가</t>
         </is>
       </c>
       <c r="O97" s="11" t="inlineStr">
         <is>
-          <t>audi.com(new A5 family), wikipedia(A5), go-parts(2017-2025 B9 key guide)</t>
-        </is>
-      </c>
-      <c r="P97" s="8" t="inlineStr">
-        <is>
-          <t>신형 키(PPE·PPC·MEB) 칩·이모빌라이저 자료 없음</t>
+          <t>audi.com(new A5 family), wikipedia(A5), go-parts(2017-2025 B9 key guide), Audi USA 순정 부품(2025 Q6 e-tron·Q5·A5·SQ5 스마트키 4M0959754CG 공용 — 북미형이라 품번 뺌) — MLB evo 계열 키 기준 추정</t>
+        </is>
+      </c>
+      <c r="P97" s="6" t="inlineStr">
+        <is>
+          <t>2025년 이후 신형(PPE·PPC) 전용 칩 자료 없음 — MLB evo 공용 키 기준 추정</t>
         </is>
       </c>
     </row>
@@ -6437,12 +6444,12 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="D98" s="7" t="inlineStr"/>
-      <c r="E98" s="7" t="inlineStr"/>
-      <c r="F98" s="7" t="inlineStr"/>
-      <c r="G98" s="8" t="inlineStr">
-        <is>
-          <t>확인 불가</t>
+      <c r="D98" s="7" t="n"/>
+      <c r="E98" s="7" t="n"/>
+      <c r="F98" s="7" t="n"/>
+      <c r="G98" s="6" t="inlineStr">
+        <is>
+          <t>MLB evo 전용 칩[추정]</t>
         </is>
       </c>
       <c r="H98" s="11" t="inlineStr">
@@ -6451,23 +6458,27 @@
         </is>
       </c>
       <c r="I98" s="11" t="inlineStr"/>
-      <c r="J98" s="11" t="inlineStr"/>
+      <c r="J98" s="11" t="inlineStr">
+        <is>
+          <t>HU162T</t>
+        </is>
+      </c>
       <c r="K98" s="11" t="inlineStr"/>
       <c r="L98" s="11" t="inlineStr"/>
       <c r="M98" s="11" t="inlineStr"/>
-      <c r="N98" s="8" t="inlineStr">
+      <c r="N98" s="6" t="inlineStr">
         <is>
           <t>확인 불가</t>
         </is>
       </c>
       <c r="O98" s="11" t="inlineStr">
         <is>
-          <t>audiusa(Q5 digital key), mycarusermanual(Q5 2024-2026 key)</t>
-        </is>
-      </c>
-      <c r="P98" s="8" t="inlineStr">
-        <is>
-          <t>신형 키(PPE·PPC·MEB) 칩·이모빌라이저 자료 없음</t>
+          <t>audiusa(Q5 digital key), mycarusermanual(Q5 2024-2026 key), Audi USA 순정 부품(2025 Q6 e-tron·Q5·A5·SQ5 스마트키 4M0959754CG 공용 — 북미형이라 품번 뺌) — MLB evo 계열 키 기준 추정</t>
+        </is>
+      </c>
+      <c r="P98" s="6" t="inlineStr">
+        <is>
+          <t>2025년 이후 신형(PPE·PPC) 전용 칩 자료 없음 — MLB evo 공용 키 기준 추정</t>
         </is>
       </c>
     </row>
@@ -7158,9 +7169,9 @@
       <c r="D111" s="7" t="n"/>
       <c r="E111" s="7" t="n"/>
       <c r="F111" s="7" t="n"/>
-      <c r="G111" s="14" t="inlineStr">
-        <is>
-          <t>MLB 전용 칩[B9, 2025.07 이전]</t>
+      <c r="G111" s="6" t="inlineStr">
+        <is>
+          <t>MLB evo 전용 칩[추정]</t>
         </is>
       </c>
       <c r="H111" s="11" t="inlineStr">
@@ -7169,21 +7180,29 @@
         </is>
       </c>
       <c r="I111" s="11" t="n"/>
-      <c r="J111" s="11" t="n"/>
+      <c r="J111" s="11" t="inlineStr">
+        <is>
+          <t>HU162T</t>
+        </is>
+      </c>
       <c r="K111" s="11" t="n"/>
       <c r="L111" s="11" t="n"/>
       <c r="M111" s="11" t="n"/>
-      <c r="N111" s="14" t="inlineStr">
+      <c r="N111" s="6" t="inlineStr">
         <is>
           <t>MLB IMMO5[B9]</t>
         </is>
       </c>
       <c r="O111" s="11" t="inlineStr">
         <is>
-          <t>audi.co.kr(더 뉴 A5·S5 출시), parts.audiusa(2025 S5), go-parts</t>
-        </is>
-      </c>
-      <c r="P111" s="14" t="n"/>
+          <t>audi.co.kr(더 뉴 A5·S5 출시), parts.audiusa(2025 S5), go-parts, Audi USA 순정 부품(2025 Q6 e-tron·Q5·A5·SQ5 스마트키 4M0959754CG 공용 — 북미형이라 품번 뺌) — MLB evo 계열 키 기준 추정</t>
+        </is>
+      </c>
+      <c r="P111" s="6" t="inlineStr">
+        <is>
+          <t>2025년 이후 신형(PPE·PPC) 전용 칩 자료 없음 — MLB evo 공용 키 기준 추정</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="11" t="inlineStr">
@@ -7204,9 +7223,9 @@
       <c r="D112" s="7" t="n"/>
       <c r="E112" s="7" t="n"/>
       <c r="F112" s="7" t="n"/>
-      <c r="G112" s="8" t="inlineStr">
-        <is>
-          <t>확인 불가[B10]</t>
+      <c r="G112" s="6" t="inlineStr">
+        <is>
+          <t>MLB evo 전용 칩[추정]</t>
         </is>
       </c>
       <c r="H112" s="11" t="inlineStr">
@@ -7215,23 +7234,27 @@
         </is>
       </c>
       <c r="I112" s="11" t="n"/>
-      <c r="J112" s="11" t="n"/>
+      <c r="J112" s="11" t="inlineStr">
+        <is>
+          <t>HU162T</t>
+        </is>
+      </c>
       <c r="K112" s="11" t="n"/>
       <c r="L112" s="11" t="n"/>
       <c r="M112" s="11" t="n"/>
-      <c r="N112" s="8" t="inlineStr">
+      <c r="N112" s="6" t="inlineStr">
         <is>
           <t>확인 불가[B10]</t>
         </is>
       </c>
       <c r="O112" s="11" t="inlineStr">
         <is>
-          <t>audi.co.kr(더 뉴 A5·S5 출시), parts.audiusa(2025 S5), go-parts</t>
-        </is>
-      </c>
-      <c r="P112" s="8" t="inlineStr">
-        <is>
-          <t>B10(2025.07~) 신형 키 칩 자료 없음</t>
+          <t>audi.co.kr(더 뉴 A5·S5 출시), parts.audiusa(2025 S5), go-parts, Audi USA 순정 부품(2025 Q6 e-tron·Q5·A5·SQ5 스마트키 4M0959754CG 공용 — 북미형이라 품번 뺌) — MLB evo 계열 키 기준 추정</t>
+        </is>
+      </c>
+      <c r="P112" s="6" t="inlineStr">
+        <is>
+          <t>2025년 이후 신형(PPE·PPC) 전용 칩 자료 없음 — MLB evo 공용 키 기준 추정</t>
         </is>
       </c>
     </row>
@@ -7251,12 +7274,12 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="D113" s="7" t="inlineStr"/>
-      <c r="E113" s="7" t="inlineStr"/>
-      <c r="F113" s="7" t="inlineStr"/>
-      <c r="G113" s="8" t="inlineStr">
-        <is>
-          <t>확인 불가</t>
+      <c r="D113" s="7" t="n"/>
+      <c r="E113" s="7" t="n"/>
+      <c r="F113" s="7" t="n"/>
+      <c r="G113" s="6" t="inlineStr">
+        <is>
+          <t>MLB evo 전용 칩[추정]</t>
         </is>
       </c>
       <c r="H113" s="11" t="inlineStr">
@@ -7265,23 +7288,27 @@
         </is>
       </c>
       <c r="I113" s="11" t="inlineStr"/>
-      <c r="J113" s="11" t="inlineStr"/>
+      <c r="J113" s="11" t="inlineStr">
+        <is>
+          <t>HU162T</t>
+        </is>
+      </c>
       <c r="K113" s="11" t="inlineStr"/>
       <c r="L113" s="11" t="inlineStr"/>
       <c r="M113" s="11" t="inlineStr"/>
-      <c r="N113" s="8" t="inlineStr">
+      <c r="N113" s="6" t="inlineStr">
         <is>
           <t>확인 불가</t>
         </is>
       </c>
       <c r="O113" s="11" t="inlineStr">
         <is>
-          <t>parts.audirockville(2026 S5), carweek(2026 S5)</t>
-        </is>
-      </c>
-      <c r="P113" s="8" t="inlineStr">
-        <is>
-          <t>신형 키(PPE·PPC·MEB) 칩·이모빌라이저 자료 없음</t>
+          <t>parts.audirockville(2026 S5), carweek(2026 S5), Audi USA 순정 부품(2025 Q6 e-tron·Q5·A5·SQ5 스마트키 4M0959754CG 공용 — 북미형이라 품번 뺌) — MLB evo 계열 키 기준 추정</t>
+        </is>
+      </c>
+      <c r="P113" s="6" t="inlineStr">
+        <is>
+          <t>2025년 이후 신형(PPE·PPC) 전용 칩 자료 없음 — MLB evo 공용 키 기준 추정</t>
         </is>
       </c>
     </row>
@@ -8019,12 +8046,12 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="D127" s="7" t="inlineStr"/>
-      <c r="E127" s="7" t="inlineStr"/>
-      <c r="F127" s="7" t="inlineStr"/>
-      <c r="G127" s="8" t="inlineStr">
-        <is>
-          <t>확인 불가</t>
+      <c r="D127" s="7" t="n"/>
+      <c r="E127" s="7" t="n"/>
+      <c r="F127" s="7" t="n"/>
+      <c r="G127" s="6" t="inlineStr">
+        <is>
+          <t>MLB evo 전용 칩[추정]</t>
         </is>
       </c>
       <c r="H127" s="11" t="inlineStr">
@@ -8033,23 +8060,27 @@
         </is>
       </c>
       <c r="I127" s="11" t="inlineStr"/>
-      <c r="J127" s="11" t="inlineStr"/>
+      <c r="J127" s="11" t="inlineStr">
+        <is>
+          <t>HU162T</t>
+        </is>
+      </c>
       <c r="K127" s="11" t="inlineStr"/>
       <c r="L127" s="11" t="inlineStr"/>
       <c r="M127" s="11" t="inlineStr"/>
-      <c r="N127" s="8" t="inlineStr">
+      <c r="N127" s="6" t="inlineStr">
         <is>
           <t>확인 불가</t>
         </is>
       </c>
       <c r="O127" s="11" t="inlineStr">
         <is>
-          <t>motor1(new RS5), topgear.ph(2026 RS5)</t>
-        </is>
-      </c>
-      <c r="P127" s="8" t="inlineStr">
-        <is>
-          <t>B10 RS5(PHEV) 국내 출시·키 칩 자료 없음</t>
+          <t>motor1(new RS5), topgear.ph(2026 RS5), Audi USA 순정 부품(2025 Q6 e-tron·Q5·A5·SQ5 스마트키 4M0959754CG 공용 — 북미형이라 품번 뺌) — MLB evo 계열 키 기준 추정</t>
+        </is>
+      </c>
+      <c r="P127" s="6" t="inlineStr">
+        <is>
+          <t>2025년 이후 신형(PPE·PPC) 전용 칩 자료 없음 — MLB evo 공용 키 기준 추정</t>
         </is>
       </c>
     </row>
@@ -9009,7 +9040,11 @@
         </is>
       </c>
       <c r="I145" s="11" t="inlineStr"/>
-      <c r="J145" s="11" t="inlineStr"/>
+      <c r="J145" s="11" t="inlineStr">
+        <is>
+          <t>HU162T</t>
+        </is>
+      </c>
       <c r="K145" s="11" t="inlineStr"/>
       <c r="L145" s="11" t="inlineStr">
         <is>
@@ -9024,7 +9059,7 @@
       </c>
       <c r="O145" s="11" t="inlineStr">
         <is>
-          <t>seoul.co.kr·motorgraph(2019-10-23 출시), parts.audiusa(2019 A6 4N0959754KTKE)</t>
+          <t>seoul.co.kr·motorgraph(2019-10-23 출시), parts.audiusa(2019 A6 4N0959754KTKE), auto-keys.eu(Audi A8·A6·Q8 2018+ 스마트키 4N0959754AL·e-tron 4M0959754BF 비상키 HU162T), keyshop-online(Audi MLB 2016+ 비상키 HU162T)</t>
         </is>
       </c>
       <c r="P145" s="11" t="inlineStr"/>
@@ -9059,7 +9094,11 @@
         </is>
       </c>
       <c r="I146" s="11" t="inlineStr"/>
-      <c r="J146" s="11" t="inlineStr"/>
+      <c r="J146" s="11" t="inlineStr">
+        <is>
+          <t>HU162T</t>
+        </is>
+      </c>
       <c r="K146" s="11" t="inlineStr"/>
       <c r="L146" s="11" t="inlineStr">
         <is>
@@ -9074,7 +9113,7 @@
       </c>
       <c r="O146" s="11" t="inlineStr">
         <is>
-          <t>carandtruckremotes(2020 A6), cnautokeys(MLB 433MHz 5M 8W0959754DA)</t>
+          <t>carandtruckremotes(2020 A6), cnautokeys(MLB 433MHz 5M 8W0959754DA), auto-keys.eu(Audi A8·A6·Q8 2018+ 스마트키 4N0959754AL·e-tron 4M0959754BF 비상키 HU162T), keyshop-online(Audi MLB 2016+ 비상키 HU162T)</t>
         </is>
       </c>
       <c r="P146" s="11" t="inlineStr"/>
@@ -9109,7 +9148,11 @@
         </is>
       </c>
       <c r="I147" s="11" t="inlineStr"/>
-      <c r="J147" s="11" t="inlineStr"/>
+      <c r="J147" s="11" t="inlineStr">
+        <is>
+          <t>HU162T</t>
+        </is>
+      </c>
       <c r="K147" s="11" t="inlineStr"/>
       <c r="L147" s="11" t="inlineStr">
         <is>
@@ -9124,7 +9167,7 @@
       </c>
       <c r="O147" s="11" t="inlineStr">
         <is>
-          <t>parts.audiusa(2021 A6 4N0959754AMTKE), programyourremote(2021 A6)</t>
+          <t>parts.audiusa(2021 A6 4N0959754AMTKE), programyourremote(2021 A6), auto-keys.eu(Audi A8·A6·Q8 2018+ 스마트키 4N0959754AL·e-tron 4M0959754BF 비상키 HU162T), keyshop-online(Audi MLB 2016+ 비상키 HU162T)</t>
         </is>
       </c>
       <c r="P147" s="11" t="inlineStr"/>
@@ -9159,7 +9202,11 @@
         </is>
       </c>
       <c r="I148" s="11" t="inlineStr"/>
-      <c r="J148" s="11" t="inlineStr"/>
+      <c r="J148" s="11" t="inlineStr">
+        <is>
+          <t>HU162T</t>
+        </is>
+      </c>
       <c r="K148" s="11" t="inlineStr"/>
       <c r="L148" s="11" t="inlineStr">
         <is>
@@ -9174,7 +9221,7 @@
       </c>
       <c r="O148" s="11" t="inlineStr">
         <is>
-          <t>locksmithkeyless(2019-2022 IYZ-AK2), keyecu(KYDZ MLB)</t>
+          <t>locksmithkeyless(2019-2022 IYZ-AK2), keyecu(KYDZ MLB), auto-keys.eu(Audi A8·A6·Q8 2018+ 스마트키 4N0959754AL·e-tron 4M0959754BF 비상키 HU162T), keyshop-online(Audi MLB 2016+ 비상키 HU162T)</t>
         </is>
       </c>
       <c r="P148" s="11" t="inlineStr"/>
@@ -9209,7 +9256,11 @@
         </is>
       </c>
       <c r="I149" s="11" t="inlineStr"/>
-      <c r="J149" s="11" t="inlineStr"/>
+      <c r="J149" s="11" t="inlineStr">
+        <is>
+          <t>HU162T</t>
+        </is>
+      </c>
       <c r="K149" s="11" t="inlineStr"/>
       <c r="L149" s="11" t="inlineStr">
         <is>
@@ -9224,7 +9275,7 @@
       </c>
       <c r="O149" s="11" t="inlineStr">
         <is>
-          <t>parts.audiusa(2023 A6)</t>
+          <t>parts.audiusa(2023 A6), auto-keys.eu(Audi A8·A6·Q8 2018+ 스마트키 4N0959754AL·e-tron 4M0959754BF 비상키 HU162T), keyshop-online(Audi MLB 2016+ 비상키 HU162T)</t>
         </is>
       </c>
       <c r="P149" s="11" t="inlineStr"/>
@@ -9259,7 +9310,11 @@
         </is>
       </c>
       <c r="I150" s="11" t="inlineStr"/>
-      <c r="J150" s="11" t="inlineStr"/>
+      <c r="J150" s="11" t="inlineStr">
+        <is>
+          <t>HU162T</t>
+        </is>
+      </c>
       <c r="K150" s="11" t="inlineStr"/>
       <c r="L150" s="11" t="inlineStr">
         <is>
@@ -9274,7 +9329,7 @@
       </c>
       <c r="O150" s="11" t="inlineStr">
         <is>
-          <t>parts.audiusa(2024 A6 allroad), audiworld(A6 2024 key)</t>
+          <t>parts.audiusa(2024 A6 allroad), audiworld(A6 2024 key), auto-keys.eu(Audi A8·A6·Q8 2018+ 스마트키 4N0959754AL·e-tron 4M0959754BF 비상키 HU162T), keyshop-online(Audi MLB 2016+ 비상키 HU162T)</t>
         </is>
       </c>
       <c r="P150" s="14" t="n"/>
@@ -9295,12 +9350,12 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="D151" s="7" t="inlineStr"/>
-      <c r="E151" s="7" t="inlineStr"/>
-      <c r="F151" s="7" t="inlineStr"/>
-      <c r="G151" s="8" t="inlineStr">
-        <is>
-          <t>확인 불가</t>
+      <c r="D151" s="7" t="n"/>
+      <c r="E151" s="7" t="n"/>
+      <c r="F151" s="7" t="n"/>
+      <c r="G151" s="6" t="inlineStr">
+        <is>
+          <t>MLB evo 전용 칩[추정]</t>
         </is>
       </c>
       <c r="H151" s="11" t="inlineStr">
@@ -9309,23 +9364,27 @@
         </is>
       </c>
       <c r="I151" s="11" t="inlineStr"/>
-      <c r="J151" s="11" t="inlineStr"/>
+      <c r="J151" s="11" t="inlineStr">
+        <is>
+          <t>HU162T</t>
+        </is>
+      </c>
       <c r="K151" s="11" t="inlineStr"/>
       <c r="L151" s="11" t="inlineStr"/>
       <c r="M151" s="11" t="inlineStr"/>
-      <c r="N151" s="8" t="inlineStr">
+      <c r="N151" s="6" t="inlineStr">
         <is>
           <t>확인 불가</t>
         </is>
       </c>
       <c r="O151" s="11" t="inlineStr">
         <is>
-          <t>macrumors(A6 Avant e-tron Car Key), audiusa(A6 e-tron FAQ)</t>
-        </is>
-      </c>
-      <c r="P151" s="8" t="inlineStr">
-        <is>
-          <t>신형 키(PPE·PPC·MEB) 칩·이모빌라이저 자료 없음</t>
+          <t>macrumors(A6 Avant e-tron Car Key), audiusa(A6 e-tron FAQ), Audi USA 순정 부품(2025 Q6 e-tron·Q5·A5·SQ5 스마트키 4M0959754CG 공용 — 북미형이라 품번 뺌) — MLB evo 계열 키 기준 추정</t>
+        </is>
+      </c>
+      <c r="P151" s="6" t="inlineStr">
+        <is>
+          <t>2025년 이후 신형(PPE·PPC) 전용 칩 자료 없음 — MLB evo 공용 키 기준 추정</t>
         </is>
       </c>
     </row>
@@ -9345,12 +9404,12 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="D152" s="7" t="inlineStr"/>
-      <c r="E152" s="7" t="inlineStr"/>
-      <c r="F152" s="7" t="inlineStr"/>
-      <c r="G152" s="8" t="inlineStr">
-        <is>
-          <t>확인 불가</t>
+      <c r="D152" s="7" t="n"/>
+      <c r="E152" s="7" t="n"/>
+      <c r="F152" s="7" t="n"/>
+      <c r="G152" s="6" t="inlineStr">
+        <is>
+          <t>MLB evo 전용 칩[추정]</t>
         </is>
       </c>
       <c r="H152" s="11" t="inlineStr">
@@ -9359,23 +9418,27 @@
         </is>
       </c>
       <c r="I152" s="11" t="inlineStr"/>
-      <c r="J152" s="11" t="inlineStr"/>
+      <c r="J152" s="11" t="inlineStr">
+        <is>
+          <t>HU162T</t>
+        </is>
+      </c>
       <c r="K152" s="11" t="inlineStr"/>
       <c r="L152" s="11" t="inlineStr"/>
       <c r="M152" s="11" t="inlineStr"/>
-      <c r="N152" s="8" t="inlineStr">
+      <c r="N152" s="6" t="inlineStr">
         <is>
           <t>확인 불가</t>
         </is>
       </c>
       <c r="O152" s="11" t="inlineStr">
         <is>
-          <t>audiusa(A6 e-tron FAQ), parts.audinorthorlando(2025 Q6 e-tron CG)</t>
-        </is>
-      </c>
-      <c r="P152" s="8" t="inlineStr">
-        <is>
-          <t>신형 키(PPE·PPC·MEB) 칩·이모빌라이저 자료 없음</t>
+          <t>audiusa(A6 e-tron FAQ), parts.audinorthorlando(2025 Q6 e-tron CG), Audi USA 순정 부품(2025 Q6 e-tron·Q5·A5·SQ5 스마트키 4M0959754CG 공용 — 북미형이라 품번 뺌) — MLB evo 계열 키 기준 추정</t>
+        </is>
+      </c>
+      <c r="P152" s="6" t="inlineStr">
+        <is>
+          <t>2025년 이후 신형(PPE·PPC) 전용 칩 자료 없음 — MLB evo 공용 키 기준 추정</t>
         </is>
       </c>
     </row>
@@ -9733,7 +9796,11 @@
         </is>
       </c>
       <c r="I159" s="11" t="inlineStr"/>
-      <c r="J159" s="11" t="inlineStr"/>
+      <c r="J159" s="11" t="inlineStr">
+        <is>
+          <t>HU162T</t>
+        </is>
+      </c>
       <c r="K159" s="11" t="inlineStr"/>
       <c r="L159" s="11" t="inlineStr">
         <is>
@@ -9748,7 +9815,7 @@
       </c>
       <c r="O159" s="11" t="inlineStr">
         <is>
-          <t>audiworld(C8 S6 key fob), parts.audibethesda(2020 S6)</t>
+          <t>audiworld(C8 S6 key fob), parts.audibethesda(2020 S6), auto-keys.eu(Audi A8·A6·Q8 2018+ 스마트키 4N0959754AL·e-tron 4M0959754BF 비상키 HU162T), keyshop-online(Audi MLB 2016+ 비상키 HU162T)</t>
         </is>
       </c>
       <c r="P159" s="11" t="inlineStr"/>
@@ -9783,7 +9850,11 @@
         </is>
       </c>
       <c r="I160" s="11" t="inlineStr"/>
-      <c r="J160" s="11" t="inlineStr"/>
+      <c r="J160" s="11" t="inlineStr">
+        <is>
+          <t>HU162T</t>
+        </is>
+      </c>
       <c r="K160" s="11" t="inlineStr"/>
       <c r="L160" s="11" t="inlineStr">
         <is>
@@ -9798,7 +9869,7 @@
       </c>
       <c r="O160" s="11" t="inlineStr">
         <is>
-          <t>parts.audiusa(2021 A6/S6 4N0959754AMTKE)</t>
+          <t>parts.audiusa(2021 A6/S6 4N0959754AMTKE), auto-keys.eu(Audi A8·A6·Q8 2018+ 스마트키 4N0959754AL·e-tron 4M0959754BF 비상키 HU162T), keyshop-online(Audi MLB 2016+ 비상키 HU162T)</t>
         </is>
       </c>
       <c r="P160" s="11" t="inlineStr"/>
@@ -9833,7 +9904,11 @@
         </is>
       </c>
       <c r="I161" s="11" t="inlineStr"/>
-      <c r="J161" s="11" t="inlineStr"/>
+      <c r="J161" s="11" t="inlineStr">
+        <is>
+          <t>HU162T</t>
+        </is>
+      </c>
       <c r="K161" s="11" t="inlineStr"/>
       <c r="L161" s="11" t="inlineStr">
         <is>
@@ -9848,7 +9923,7 @@
       </c>
       <c r="O161" s="11" t="inlineStr">
         <is>
-          <t>locksmithkeyless(IYZ-AK2), go-parts</t>
+          <t>locksmithkeyless(IYZ-AK2), go-parts, auto-keys.eu(Audi A8·A6·Q8 2018+ 스마트키 4N0959754AL·e-tron 4M0959754BF 비상키 HU162T), keyshop-online(Audi MLB 2016+ 비상키 HU162T)</t>
         </is>
       </c>
       <c r="P161" s="14" t="n"/>
@@ -9883,7 +9958,11 @@
         </is>
       </c>
       <c r="I162" s="11" t="inlineStr"/>
-      <c r="J162" s="11" t="inlineStr"/>
+      <c r="J162" s="11" t="inlineStr">
+        <is>
+          <t>HU162T</t>
+        </is>
+      </c>
       <c r="K162" s="11" t="inlineStr"/>
       <c r="L162" s="11" t="inlineStr">
         <is>
@@ -9898,7 +9977,7 @@
       </c>
       <c r="O162" s="11" t="inlineStr">
         <is>
-          <t>carandtruckremotes(2023 A6), keylessentryremotefob(S6)</t>
+          <t>carandtruckremotes(2023 A6), keylessentryremotefob(S6), auto-keys.eu(Audi A8·A6·Q8 2018+ 스마트키 4N0959754AL·e-tron 4M0959754BF 비상키 HU162T), keyshop-online(Audi MLB 2016+ 비상키 HU162T)</t>
         </is>
       </c>
       <c r="P162" s="14" t="n"/>
@@ -9933,7 +10012,11 @@
         </is>
       </c>
       <c r="I163" s="11" t="inlineStr"/>
-      <c r="J163" s="11" t="inlineStr"/>
+      <c r="J163" s="11" t="inlineStr">
+        <is>
+          <t>HU162T</t>
+        </is>
+      </c>
       <c r="K163" s="11" t="inlineStr"/>
       <c r="L163" s="11" t="inlineStr">
         <is>
@@ -9948,7 +10031,7 @@
       </c>
       <c r="O163" s="11" t="inlineStr">
         <is>
-          <t>go-parts(2017-2026 key fob guide)</t>
+          <t>go-parts(2017-2026 key fob guide), auto-keys.eu(Audi A8·A6·Q8 2018+ 스마트키 4N0959754AL·e-tron 4M0959754BF 비상키 HU162T), keyshop-online(Audi MLB 2016+ 비상키 HU162T)</t>
         </is>
       </c>
       <c r="P163" s="14" t="n"/>
@@ -9969,12 +10052,12 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="D164" s="7" t="inlineStr"/>
-      <c r="E164" s="7" t="inlineStr"/>
-      <c r="F164" s="7" t="inlineStr"/>
-      <c r="G164" s="8" t="inlineStr">
-        <is>
-          <t>확인 불가</t>
+      <c r="D164" s="7" t="n"/>
+      <c r="E164" s="7" t="n"/>
+      <c r="F164" s="7" t="n"/>
+      <c r="G164" s="6" t="inlineStr">
+        <is>
+          <t>MLB evo 전용 칩[추정]</t>
         </is>
       </c>
       <c r="H164" s="11" t="inlineStr">
@@ -9983,7 +10066,11 @@
         </is>
       </c>
       <c r="I164" s="11" t="inlineStr"/>
-      <c r="J164" s="11" t="inlineStr"/>
+      <c r="J164" s="11" t="inlineStr">
+        <is>
+          <t>HU162T</t>
+        </is>
+      </c>
       <c r="K164" s="11" t="inlineStr"/>
       <c r="L164" s="11" t="inlineStr">
         <is>
@@ -9991,19 +10078,19 @@
         </is>
       </c>
       <c r="M164" s="11" t="inlineStr"/>
-      <c r="N164" s="8" t="inlineStr">
+      <c r="N164" s="6" t="inlineStr">
         <is>
           <t>확인 불가</t>
         </is>
       </c>
       <c r="O164" s="11" t="inlineStr">
         <is>
-          <t>top-rider(A6 e-트론 출시·S6 가격), audiusa(A6 e-tron FAQ)</t>
-        </is>
-      </c>
-      <c r="P164" s="8" t="inlineStr">
-        <is>
-          <t>신형 키(PPE·PPC·MEB) 칩·이모빌라이저 자료 없음</t>
+          <t>top-rider(A6 e-트론 출시·S6 가격), audiusa(A6 e-tron FAQ), Audi USA 순정 부품(2025 Q6 e-tron·Q5·A5·SQ5 스마트키 4M0959754CG 공용 — 북미형이라 품번 뺌) — MLB evo 계열 키 기준 추정</t>
+        </is>
+      </c>
+      <c r="P164" s="6" t="inlineStr">
+        <is>
+          <t>2025년 이후 신형(PPE·PPC) 전용 칩 자료 없음 — MLB evo 공용 키 기준 추정</t>
         </is>
       </c>
     </row>
@@ -10023,12 +10110,12 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="D165" s="7" t="inlineStr"/>
-      <c r="E165" s="7" t="inlineStr"/>
-      <c r="F165" s="7" t="inlineStr"/>
-      <c r="G165" s="8" t="inlineStr">
-        <is>
-          <t>확인 불가</t>
+      <c r="D165" s="7" t="n"/>
+      <c r="E165" s="7" t="n"/>
+      <c r="F165" s="7" t="n"/>
+      <c r="G165" s="6" t="inlineStr">
+        <is>
+          <t>MLB evo 전용 칩[추정]</t>
         </is>
       </c>
       <c r="H165" s="11" t="inlineStr">
@@ -10037,7 +10124,11 @@
         </is>
       </c>
       <c r="I165" s="11" t="inlineStr"/>
-      <c r="J165" s="11" t="inlineStr"/>
+      <c r="J165" s="11" t="inlineStr">
+        <is>
+          <t>HU162T</t>
+        </is>
+      </c>
       <c r="K165" s="11" t="inlineStr"/>
       <c r="L165" s="11" t="inlineStr">
         <is>
@@ -10045,19 +10136,19 @@
         </is>
       </c>
       <c r="M165" s="11" t="inlineStr"/>
-      <c r="N165" s="8" t="inlineStr">
+      <c r="N165" s="6" t="inlineStr">
         <is>
           <t>확인 불가</t>
         </is>
       </c>
       <c r="O165" s="11" t="inlineStr">
         <is>
-          <t>2025년식 기록 준용 — top-rider(A6 e-트론 출시·S6 가격), audiusa(A6 e-tron FAQ)</t>
-        </is>
-      </c>
-      <c r="P165" s="8" t="inlineStr">
-        <is>
-          <t>2026년식 개별 검색 자료 없음 — 2025년식 기준 추정, 신형 키 칩 자료 없음</t>
+          <t>2025년식 기록 준용 — top-rider(A6 e-트론 출시·S6 가격), audiusa(A6 e-tron FAQ), Audi USA 순정 부품(2025 Q6 e-tron·Q5·A5·SQ5 스마트키 4M0959754CG 공용 — 북미형이라 품번 뺌) — MLB evo 계열 키 기준 추정</t>
+        </is>
+      </c>
+      <c r="P165" s="6" t="inlineStr">
+        <is>
+          <t>2025년 이후 신형(PPE·PPC) 전용 칩 자료 없음 — MLB evo 공용 키 기준 추정</t>
         </is>
       </c>
     </row>
@@ -10361,7 +10452,11 @@
         </is>
       </c>
       <c r="I171" s="11" t="inlineStr"/>
-      <c r="J171" s="11" t="inlineStr"/>
+      <c r="J171" s="11" t="inlineStr">
+        <is>
+          <t>HU162T</t>
+        </is>
+      </c>
       <c r="K171" s="11" t="inlineStr"/>
       <c r="L171" s="11" t="inlineStr">
         <is>
@@ -10376,7 +10471,7 @@
       </c>
       <c r="O171" s="11" t="inlineStr">
         <is>
-          <t>carisyou(2021 RS6·RS7 출시), parts.audibethesda(4N0959754BC 433.92MHz)</t>
+          <t>carisyou(2021 RS6·RS7 출시), parts.audibethesda(4N0959754BC 433.92MHz), auto-keys.eu(Audi A8·A6·Q8 2018+ 스마트키 4N0959754AL·e-tron 4M0959754BF 비상키 HU162T), keyshop-online(Audi MLB 2016+ 비상키 HU162T)</t>
         </is>
       </c>
       <c r="P171" s="11" t="inlineStr"/>
@@ -10411,7 +10506,11 @@
         </is>
       </c>
       <c r="I172" s="11" t="inlineStr"/>
-      <c r="J172" s="11" t="inlineStr"/>
+      <c r="J172" s="11" t="inlineStr">
+        <is>
+          <t>HU162T</t>
+        </is>
+      </c>
       <c r="K172" s="11" t="inlineStr"/>
       <c r="L172" s="11" t="inlineStr">
         <is>
@@ -10426,7 +10525,7 @@
       </c>
       <c r="O172" s="11" t="inlineStr">
         <is>
-          <t>parts.audiusa(2022 e-tron GT/RS6 4N0959754BCTKE)</t>
+          <t>parts.audiusa(2022 e-tron GT/RS6 4N0959754BCTKE), auto-keys.eu(Audi A8·A6·Q8 2018+ 스마트키 4N0959754AL·e-tron 4M0959754BF 비상키 HU162T), keyshop-online(Audi MLB 2016+ 비상키 HU162T)</t>
         </is>
       </c>
       <c r="P172" s="11" t="inlineStr"/>
@@ -10461,7 +10560,11 @@
         </is>
       </c>
       <c r="I173" s="11" t="inlineStr"/>
-      <c r="J173" s="11" t="inlineStr"/>
+      <c r="J173" s="11" t="inlineStr">
+        <is>
+          <t>HU162T</t>
+        </is>
+      </c>
       <c r="K173" s="11" t="inlineStr"/>
       <c r="L173" s="11" t="inlineStr">
         <is>
@@ -10476,7 +10579,7 @@
       </c>
       <c r="O173" s="11" t="inlineStr">
         <is>
-          <t>rs246(RS6 performance missing convenience key), programyourremote(2023 RS6)</t>
+          <t>rs246(RS6 performance missing convenience key), programyourremote(2023 RS6), auto-keys.eu(Audi A8·A6·Q8 2018+ 스마트키 4N0959754AL·e-tron 4M0959754BF 비상키 HU162T), keyshop-online(Audi MLB 2016+ 비상키 HU162T)</t>
         </is>
       </c>
       <c r="P173" s="11" t="inlineStr"/>
@@ -10511,7 +10614,11 @@
         </is>
       </c>
       <c r="I174" s="11" t="inlineStr"/>
-      <c r="J174" s="11" t="inlineStr"/>
+      <c r="J174" s="11" t="inlineStr">
+        <is>
+          <t>HU162T</t>
+        </is>
+      </c>
       <c r="K174" s="11" t="inlineStr"/>
       <c r="L174" s="11" t="inlineStr">
         <is>
@@ -10526,7 +10633,7 @@
       </c>
       <c r="O174" s="11" t="inlineStr">
         <is>
-          <t>top-rider(RS6 퍼포먼스 1억7550만원), parts.audiusa(RS6)</t>
+          <t>top-rider(RS6 퍼포먼스 1억7550만원), parts.audiusa(RS6), auto-keys.eu(Audi A8·A6·Q8 2018+ 스마트키 4N0959754AL·e-tron 4M0959754BF 비상키 HU162T), keyshop-online(Audi MLB 2016+ 비상키 HU162T)</t>
         </is>
       </c>
       <c r="P174" s="11" t="inlineStr"/>
@@ -10561,7 +10668,11 @@
         </is>
       </c>
       <c r="I175" s="11" t="inlineStr"/>
-      <c r="J175" s="11" t="inlineStr"/>
+      <c r="J175" s="11" t="inlineStr">
+        <is>
+          <t>HU162T</t>
+        </is>
+      </c>
       <c r="K175" s="11" t="inlineStr"/>
       <c r="L175" s="11" t="inlineStr">
         <is>
@@ -10576,7 +10687,7 @@
       </c>
       <c r="O175" s="11" t="inlineStr">
         <is>
-          <t>ebay(RS logo 4N0959754BC), motorgraph(RS6 아반트 GT)</t>
+          <t>ebay(RS logo 4N0959754BC), motorgraph(RS6 아반트 GT), auto-keys.eu(Audi A8·A6·Q8 2018+ 스마트키 4N0959754AL·e-tron 4M0959754BF 비상키 HU162T), keyshop-online(Audi MLB 2016+ 비상키 HU162T)</t>
         </is>
       </c>
       <c r="P175" s="11" t="inlineStr"/>
@@ -10611,7 +10722,11 @@
         </is>
       </c>
       <c r="I176" s="11" t="inlineStr"/>
-      <c r="J176" s="11" t="inlineStr"/>
+      <c r="J176" s="11" t="inlineStr">
+        <is>
+          <t>HU162T</t>
+        </is>
+      </c>
       <c r="K176" s="11" t="inlineStr"/>
       <c r="L176" s="11" t="inlineStr">
         <is>
@@ -10626,7 +10741,7 @@
       </c>
       <c r="O176" s="11" t="inlineStr">
         <is>
-          <t>audiusa(2026 RS6 Avant), parts.audiusa(RS6)</t>
+          <t>audiusa(2026 RS6 Avant), parts.audiusa(RS6), auto-keys.eu(Audi A8·A6·Q8 2018+ 스마트키 4N0959754AL·e-tron 4M0959754BF 비상키 HU162T), keyshop-online(Audi MLB 2016+ 비상키 HU162T)</t>
         </is>
       </c>
       <c r="P176" s="14" t="n"/>
@@ -11093,7 +11208,11 @@
         </is>
       </c>
       <c r="I185" s="11" t="inlineStr"/>
-      <c r="J185" s="11" t="inlineStr"/>
+      <c r="J185" s="11" t="inlineStr">
+        <is>
+          <t>HU162T</t>
+        </is>
+      </c>
       <c r="K185" s="11" t="inlineStr"/>
       <c r="L185" s="11" t="inlineStr">
         <is>
@@ -11108,7 +11227,7 @@
       </c>
       <c r="O185" s="11" t="inlineStr">
         <is>
-          <t>top-rider, obdii365(KYDZ MLB A7 2019-), locksmithkeyless(IYZ-AK2)</t>
+          <t>top-rider, obdii365(KYDZ MLB A7 2019-), locksmithkeyless(IYZ-AK2), auto-keys.eu(Audi A8·A6·Q8 2018+ 스마트키 4N0959754AL·e-tron 4M0959754BF 비상키 HU162T), keyshop-online(Audi MLB 2016+ 비상키 HU162T)</t>
         </is>
       </c>
       <c r="P185" s="11" t="inlineStr"/>
@@ -11143,7 +11262,11 @@
         </is>
       </c>
       <c r="I186" s="11" t="inlineStr"/>
-      <c r="J186" s="11" t="inlineStr"/>
+      <c r="J186" s="11" t="inlineStr">
+        <is>
+          <t>HU162T</t>
+        </is>
+      </c>
       <c r="K186" s="11" t="inlineStr"/>
       <c r="L186" s="11" t="inlineStr">
         <is>
@@ -11158,7 +11281,7 @@
       </c>
       <c r="O186" s="11" t="inlineStr">
         <is>
-          <t>parts.audiusa(4N0959754AMTKE)</t>
+          <t>parts.audiusa(4N0959754AMTKE), auto-keys.eu(Audi A8·A6·Q8 2018+ 스마트키 4N0959754AL·e-tron 4M0959754BF 비상키 HU162T), keyshop-online(Audi MLB 2016+ 비상키 HU162T)</t>
         </is>
       </c>
       <c r="P186" s="11" t="inlineStr"/>
@@ -11193,7 +11316,11 @@
         </is>
       </c>
       <c r="I187" s="11" t="inlineStr"/>
-      <c r="J187" s="11" t="inlineStr"/>
+      <c r="J187" s="11" t="inlineStr">
+        <is>
+          <t>HU162T</t>
+        </is>
+      </c>
       <c r="K187" s="11" t="inlineStr"/>
       <c r="L187" s="11" t="inlineStr">
         <is>
@@ -11208,7 +11335,7 @@
       </c>
       <c r="O187" s="11" t="inlineStr">
         <is>
-          <t>parts.audiusa(4N0959754AMTKE), parts.audibethesda(2022 A8 AM)</t>
+          <t>parts.audiusa(4N0959754AMTKE), parts.audibethesda(2022 A8 AM), auto-keys.eu(Audi A8·A6·Q8 2018+ 스마트키 4N0959754AL·e-tron 4M0959754BF 비상키 HU162T), keyshop-online(Audi MLB 2016+ 비상키 HU162T)</t>
         </is>
       </c>
       <c r="P187" s="14" t="n"/>
@@ -11243,7 +11370,11 @@
         </is>
       </c>
       <c r="I188" s="11" t="inlineStr"/>
-      <c r="J188" s="11" t="inlineStr"/>
+      <c r="J188" s="11" t="inlineStr">
+        <is>
+          <t>HU162T</t>
+        </is>
+      </c>
       <c r="K188" s="11" t="inlineStr"/>
       <c r="L188" s="11" t="inlineStr">
         <is>
@@ -11258,7 +11389,7 @@
       </c>
       <c r="O188" s="11" t="inlineStr">
         <is>
-          <t>parts.audiusa, go-parts(2017-2026 guide)</t>
+          <t>parts.audiusa, go-parts(2017-2026 guide), auto-keys.eu(Audi A8·A6·Q8 2018+ 스마트키 4N0959754AL·e-tron 4M0959754BF 비상키 HU162T), keyshop-online(Audi MLB 2016+ 비상키 HU162T)</t>
         </is>
       </c>
       <c r="P188" s="14" t="n"/>
@@ -11293,7 +11424,11 @@
         </is>
       </c>
       <c r="I189" s="11" t="inlineStr"/>
-      <c r="J189" s="11" t="inlineStr"/>
+      <c r="J189" s="11" t="inlineStr">
+        <is>
+          <t>HU162T</t>
+        </is>
+      </c>
       <c r="K189" s="11" t="inlineStr"/>
       <c r="L189" s="11" t="inlineStr">
         <is>
@@ -11308,7 +11443,7 @@
       </c>
       <c r="O189" s="11" t="inlineStr">
         <is>
-          <t>audi.co.kr(A7 TFSI e 2024), programyourremote(2024 A7)</t>
+          <t>audi.co.kr(A7 TFSI e 2024), programyourremote(2024 A7), auto-keys.eu(Audi A8·A6·Q8 2018+ 스마트키 4N0959754AL·e-tron 4M0959754BF 비상키 HU162T), keyshop-online(Audi MLB 2016+ 비상키 HU162T)</t>
         </is>
       </c>
       <c r="P189" s="14" t="n"/>
@@ -11343,7 +11478,11 @@
         </is>
       </c>
       <c r="I190" s="11" t="inlineStr"/>
-      <c r="J190" s="11" t="inlineStr"/>
+      <c r="J190" s="11" t="inlineStr">
+        <is>
+          <t>HU162T</t>
+        </is>
+      </c>
       <c r="K190" s="11" t="inlineStr"/>
       <c r="L190" s="11" t="inlineStr">
         <is>
@@ -11358,7 +11497,7 @@
       </c>
       <c r="O190" s="11" t="inlineStr">
         <is>
-          <t>parts.audiusa(2025 RS7 4H0959754DBTKE)</t>
+          <t>parts.audiusa(2025 RS7 4H0959754DBTKE), auto-keys.eu(Audi A8·A6·Q8 2018+ 스마트키 4N0959754AL·e-tron 4M0959754BF 비상키 HU162T), keyshop-online(Audi MLB 2016+ 비상키 HU162T)</t>
         </is>
       </c>
       <c r="P190" s="14" t="n"/>
@@ -11393,7 +11532,11 @@
         </is>
       </c>
       <c r="I191" s="11" t="inlineStr"/>
-      <c r="J191" s="11" t="inlineStr"/>
+      <c r="J191" s="11" t="inlineStr">
+        <is>
+          <t>HU162T</t>
+        </is>
+      </c>
       <c r="K191" s="11" t="inlineStr"/>
       <c r="L191" s="11" t="inlineStr">
         <is>
@@ -11408,7 +11551,7 @@
       </c>
       <c r="O191" s="11" t="inlineStr">
         <is>
-          <t>ebay(A7 IYZ AK2 433MHz), audi-mediacenter(A7 Sportback digital key)</t>
+          <t>ebay(A7 IYZ AK2 433MHz), audi-mediacenter(A7 Sportback digital key), auto-keys.eu(Audi A8·A6·Q8 2018+ 스마트키 4N0959754AL·e-tron 4M0959754BF 비상키 HU162T), keyshop-online(Audi MLB 2016+ 비상키 HU162T)</t>
         </is>
       </c>
       <c r="P191" s="11" t="inlineStr"/>
@@ -11443,7 +11586,11 @@
         </is>
       </c>
       <c r="I192" s="11" t="inlineStr"/>
-      <c r="J192" s="11" t="inlineStr"/>
+      <c r="J192" s="11" t="inlineStr">
+        <is>
+          <t>HU162T</t>
+        </is>
+      </c>
       <c r="K192" s="11" t="inlineStr"/>
       <c r="L192" s="11" t="inlineStr">
         <is>
@@ -11458,7 +11605,7 @@
       </c>
       <c r="O192" s="11" t="inlineStr">
         <is>
-          <t>namu.wiki(A7), parts.audiusa(2020 S7 4N0959754BFTKE)</t>
+          <t>namu.wiki(A7), parts.audiusa(2020 S7 4N0959754BFTKE), auto-keys.eu(Audi A8·A6·Q8 2018+ 스마트키 4N0959754AL·e-tron 4M0959754BF 비상키 HU162T), keyshop-online(Audi MLB 2016+ 비상키 HU162T)</t>
         </is>
       </c>
       <c r="P192" s="11" t="inlineStr"/>
@@ -11493,7 +11640,11 @@
         </is>
       </c>
       <c r="I193" s="11" t="inlineStr"/>
-      <c r="J193" s="11" t="inlineStr"/>
+      <c r="J193" s="11" t="inlineStr">
+        <is>
+          <t>HU162T</t>
+        </is>
+      </c>
       <c r="K193" s="11" t="inlineStr"/>
       <c r="L193" s="11" t="inlineStr">
         <is>
@@ -11508,7 +11659,7 @@
       </c>
       <c r="O193" s="11" t="inlineStr">
         <is>
-          <t>parts.audiusa(A7 4N0959754AMTKE), ebay(S7 key)</t>
+          <t>parts.audiusa(A7 4N0959754AMTKE), ebay(S7 key), auto-keys.eu(Audi A8·A6·Q8 2018+ 스마트키 4N0959754AL·e-tron 4M0959754BF 비상키 HU162T), keyshop-online(Audi MLB 2016+ 비상키 HU162T)</t>
         </is>
       </c>
       <c r="P193" s="14" t="n"/>
@@ -11543,7 +11694,11 @@
         </is>
       </c>
       <c r="I194" s="11" t="inlineStr"/>
-      <c r="J194" s="11" t="inlineStr"/>
+      <c r="J194" s="11" t="inlineStr">
+        <is>
+          <t>HU162T</t>
+        </is>
+      </c>
       <c r="K194" s="11" t="inlineStr"/>
       <c r="L194" s="11" t="inlineStr">
         <is>
@@ -11558,7 +11713,7 @@
       </c>
       <c r="O194" s="11" t="inlineStr">
         <is>
-          <t>parts.audiusa(A7 AM/K), fcpeuro(S7 keys)</t>
+          <t>parts.audiusa(A7 AM/K), fcpeuro(S7 keys), auto-keys.eu(Audi A8·A6·Q8 2018+ 스마트키 4N0959754AL·e-tron 4M0959754BF 비상키 HU162T), keyshop-online(Audi MLB 2016+ 비상키 HU162T)</t>
         </is>
       </c>
       <c r="P194" s="14" t="n"/>
@@ -11593,7 +11748,11 @@
         </is>
       </c>
       <c r="I195" s="11" t="inlineStr"/>
-      <c r="J195" s="11" t="inlineStr"/>
+      <c r="J195" s="11" t="inlineStr">
+        <is>
+          <t>HU162T</t>
+        </is>
+      </c>
       <c r="K195" s="11" t="inlineStr"/>
       <c r="L195" s="11" t="inlineStr">
         <is>
@@ -11608,7 +11767,7 @@
       </c>
       <c r="O195" s="11" t="inlineStr">
         <is>
-          <t>programyourremote(S7), keylessentryremotefob(S7)</t>
+          <t>programyourremote(S7), keylessentryremotefob(S7), auto-keys.eu(Audi A8·A6·Q8 2018+ 스마트키 4N0959754AL·e-tron 4M0959754BF 비상키 HU162T), keyshop-online(Audi MLB 2016+ 비상키 HU162T)</t>
         </is>
       </c>
       <c r="P195" s="14" t="n"/>
@@ -11643,7 +11802,11 @@
         </is>
       </c>
       <c r="I196" s="11" t="inlineStr"/>
-      <c r="J196" s="11" t="inlineStr"/>
+      <c r="J196" s="11" t="inlineStr">
+        <is>
+          <t>HU162T</t>
+        </is>
+      </c>
       <c r="K196" s="11" t="inlineStr"/>
       <c r="L196" s="11" t="inlineStr">
         <is>
@@ -11658,7 +11821,7 @@
       </c>
       <c r="O196" s="11" t="inlineStr">
         <is>
-          <t>audi.co.kr(S7 TDI 2024), programyourremote(2024 A7)</t>
+          <t>audi.co.kr(S7 TDI 2024), programyourremote(2024 A7), auto-keys.eu(Audi A8·A6·Q8 2018+ 스마트키 4N0959754AL·e-tron 4M0959754BF 비상키 HU162T), keyshop-online(Audi MLB 2016+ 비상키 HU162T)</t>
         </is>
       </c>
       <c r="P196" s="14" t="n"/>
@@ -11693,7 +11856,11 @@
         </is>
       </c>
       <c r="I197" s="11" t="inlineStr"/>
-      <c r="J197" s="11" t="inlineStr"/>
+      <c r="J197" s="11" t="inlineStr">
+        <is>
+          <t>HU162T</t>
+        </is>
+      </c>
       <c r="K197" s="11" t="inlineStr"/>
       <c r="L197" s="11" t="inlineStr">
         <is>
@@ -11708,7 +11875,7 @@
       </c>
       <c r="O197" s="11" t="inlineStr">
         <is>
-          <t>parts.audiusa(A7 AM), keylessentryremotefob(S7)</t>
+          <t>parts.audiusa(A7 AM), keylessentryremotefob(S7), auto-keys.eu(Audi A8·A6·Q8 2018+ 스마트키 4N0959754AL·e-tron 4M0959754BF 비상키 HU162T), keyshop-online(Audi MLB 2016+ 비상키 HU162T)</t>
         </is>
       </c>
       <c r="P197" s="14" t="n"/>
@@ -11743,7 +11910,11 @@
         </is>
       </c>
       <c r="I198" s="11" t="inlineStr"/>
-      <c r="J198" s="11" t="inlineStr"/>
+      <c r="J198" s="11" t="inlineStr">
+        <is>
+          <t>HU162T</t>
+        </is>
+      </c>
       <c r="K198" s="11" t="inlineStr"/>
       <c r="L198" s="11" t="inlineStr">
         <is>
@@ -11758,7 +11929,7 @@
       </c>
       <c r="O198" s="11" t="inlineStr">
         <is>
-          <t>autoevolution(A7/S7 discontinued 2026), carbuzz</t>
+          <t>autoevolution(A7/S7 discontinued 2026), carbuzz, auto-keys.eu(Audi A8·A6·Q8 2018+ 스마트키 4N0959754AL·e-tron 4M0959754BF 비상키 HU162T), keyshop-online(Audi MLB 2016+ 비상키 HU162T)</t>
         </is>
       </c>
       <c r="P198" s="6" t="inlineStr">
@@ -12067,7 +12238,11 @@
         </is>
       </c>
       <c r="I204" s="11" t="inlineStr"/>
-      <c r="J204" s="11" t="inlineStr"/>
+      <c r="J204" s="11" t="inlineStr">
+        <is>
+          <t>HU162T</t>
+        </is>
+      </c>
       <c r="K204" s="11" t="inlineStr"/>
       <c r="L204" s="11" t="inlineStr">
         <is>
@@ -12082,7 +12257,7 @@
       </c>
       <c r="O204" s="11" t="inlineStr">
         <is>
-          <t>carisyou(RS6·RS7 출시), parts.audiusa(4N0959754BCTKE), audizine(2021 RS7 key)</t>
+          <t>carisyou(RS6·RS7 출시), parts.audiusa(4N0959754BCTKE), audizine(2021 RS7 key), auto-keys.eu(Audi A8·A6·Q8 2018+ 스마트키 4N0959754AL·e-tron 4M0959754BF 비상키 HU162T), keyshop-online(Audi MLB 2016+ 비상키 HU162T)</t>
         </is>
       </c>
       <c r="P204" s="11" t="inlineStr"/>
@@ -12117,7 +12292,11 @@
         </is>
       </c>
       <c r="I205" s="11" t="inlineStr"/>
-      <c r="J205" s="11" t="inlineStr"/>
+      <c r="J205" s="11" t="inlineStr">
+        <is>
+          <t>HU162T</t>
+        </is>
+      </c>
       <c r="K205" s="11" t="inlineStr"/>
       <c r="L205" s="11" t="inlineStr">
         <is>
@@ -12132,7 +12311,7 @@
       </c>
       <c r="O205" s="11" t="inlineStr">
         <is>
-          <t>parts.audiusa, parts.audinorthoc(2022 RS7 vehicle key)</t>
+          <t>parts.audiusa, parts.audinorthoc(2022 RS7 vehicle key), auto-keys.eu(Audi A8·A6·Q8 2018+ 스마트키 4N0959754AL·e-tron 4M0959754BF 비상키 HU162T), keyshop-online(Audi MLB 2016+ 비상키 HU162T)</t>
         </is>
       </c>
       <c r="P205" s="11" t="inlineStr"/>
@@ -12167,7 +12346,11 @@
         </is>
       </c>
       <c r="I206" s="11" t="inlineStr"/>
-      <c r="J206" s="11" t="inlineStr"/>
+      <c r="J206" s="11" t="inlineStr">
+        <is>
+          <t>HU162T</t>
+        </is>
+      </c>
       <c r="K206" s="11" t="inlineStr"/>
       <c r="L206" s="11" t="inlineStr">
         <is>
@@ -12182,7 +12365,7 @@
       </c>
       <c r="O206" s="11" t="inlineStr">
         <is>
-          <t>parts.audiusa, keylessentryremotefob(RS7 w/ &amp; w/o comfort access)</t>
+          <t>parts.audiusa, keylessentryremotefob(RS7 w/ &amp; w/o comfort access), auto-keys.eu(Audi A8·A6·Q8 2018+ 스마트키 4N0959754AL·e-tron 4M0959754BF 비상키 HU162T), keyshop-online(Audi MLB 2016+ 비상키 HU162T)</t>
         </is>
       </c>
       <c r="P206" s="11" t="inlineStr"/>
@@ -12217,7 +12400,11 @@
         </is>
       </c>
       <c r="I207" s="11" t="inlineStr"/>
-      <c r="J207" s="11" t="inlineStr"/>
+      <c r="J207" s="11" t="inlineStr">
+        <is>
+          <t>HU162T</t>
+        </is>
+      </c>
       <c r="K207" s="11" t="inlineStr"/>
       <c r="L207" s="11" t="inlineStr">
         <is>
@@ -12232,7 +12419,7 @@
       </c>
       <c r="O207" s="11" t="inlineStr">
         <is>
-          <t>parts.audiusa(RS7 4N0959754BC), parts.audibethesda(2024 RSQ8 BC)</t>
+          <t>parts.audiusa(RS7 4N0959754BC), parts.audibethesda(2024 RSQ8 BC), auto-keys.eu(Audi A8·A6·Q8 2018+ 스마트키 4N0959754AL·e-tron 4M0959754BF 비상키 HU162T), keyshop-online(Audi MLB 2016+ 비상키 HU162T)</t>
         </is>
       </c>
       <c r="P207" s="11" t="inlineStr"/>
@@ -12267,7 +12454,11 @@
         </is>
       </c>
       <c r="I208" s="11" t="inlineStr"/>
-      <c r="J208" s="11" t="inlineStr"/>
+      <c r="J208" s="11" t="inlineStr">
+        <is>
+          <t>HU162T</t>
+        </is>
+      </c>
       <c r="K208" s="11" t="inlineStr"/>
       <c r="L208" s="11" t="inlineStr">
         <is>
@@ -12282,7 +12473,7 @@
       </c>
       <c r="O208" s="11" t="inlineStr">
         <is>
-          <t>parts.audiusa(2025 RS7)</t>
+          <t>parts.audiusa(2025 RS7), auto-keys.eu(Audi A8·A6·Q8 2018+ 스마트키 4N0959754AL·e-tron 4M0959754BF 비상키 HU162T), keyshop-online(Audi MLB 2016+ 비상키 HU162T)</t>
         </is>
       </c>
       <c r="P208" s="14" t="n"/>
@@ -12317,7 +12508,11 @@
         </is>
       </c>
       <c r="I209" s="11" t="inlineStr"/>
-      <c r="J209" s="11" t="inlineStr"/>
+      <c r="J209" s="11" t="inlineStr">
+        <is>
+          <t>HU162T</t>
+        </is>
+      </c>
       <c r="K209" s="11" t="inlineStr"/>
       <c r="L209" s="11" t="inlineStr">
         <is>
@@ -12332,7 +12527,7 @@
       </c>
       <c r="O209" s="11" t="inlineStr">
         <is>
-          <t>audiusa(2026 RS7), carbuzz(2026 RS7)</t>
+          <t>audiusa(2026 RS7), carbuzz(2026 RS7), auto-keys.eu(Audi A8·A6·Q8 2018+ 스마트키 4N0959754AL·e-tron 4M0959754BF 비상키 HU162T), keyshop-online(Audi MLB 2016+ 비상키 HU162T)</t>
         </is>
       </c>
       <c r="P209" s="14" t="n"/>
@@ -13261,7 +13456,11 @@
         </is>
       </c>
       <c r="I225" s="11" t="inlineStr"/>
-      <c r="J225" s="11" t="inlineStr"/>
+      <c r="J225" s="11" t="inlineStr">
+        <is>
+          <t>HU162T</t>
+        </is>
+      </c>
       <c r="K225" s="11" t="inlineStr"/>
       <c r="L225" s="11" t="inlineStr">
         <is>
@@ -13276,7 +13475,7 @@
       </c>
       <c r="O225" s="11" t="inlineStr">
         <is>
-          <t>hankookilbo(A8 국내 출시), parts.audiusa(2019 Q8 4N0959754AMTKE)</t>
+          <t>hankookilbo(A8 국내 출시), parts.audiusa(2019 Q8 4N0959754AMTKE), auto-keys.eu(Audi A8·A6·Q8 2018+ 스마트키 4N0959754AL·e-tron 4M0959754BF 비상키 HU162T), keyshop-online(Audi MLB 2016+ 비상키 HU162T)</t>
         </is>
       </c>
       <c r="P225" s="11" t="inlineStr"/>
@@ -13311,7 +13510,11 @@
         </is>
       </c>
       <c r="I226" s="11" t="inlineStr"/>
-      <c r="J226" s="11" t="inlineStr"/>
+      <c r="J226" s="11" t="inlineStr">
+        <is>
+          <t>HU162T</t>
+        </is>
+      </c>
       <c r="K226" s="11" t="inlineStr"/>
       <c r="L226" s="11" t="inlineStr">
         <is>
@@ -13326,7 +13529,7 @@
       </c>
       <c r="O226" s="11" t="inlineStr">
         <is>
-          <t>programyourremote(2020 A8), obdii365(KYDZ MLB), xhorsevvdi(VVDI MLB 2020 Q8)</t>
+          <t>programyourremote(2020 A8), obdii365(KYDZ MLB), xhorsevvdi(VVDI MLB 2020 Q8), auto-keys.eu(Audi A8·A6·Q8 2018+ 스마트키 4N0959754AL·e-tron 4M0959754BF 비상키 HU162T), keyshop-online(Audi MLB 2016+ 비상키 HU162T)</t>
         </is>
       </c>
       <c r="P226" s="11" t="inlineStr"/>
@@ -13361,7 +13564,11 @@
         </is>
       </c>
       <c r="I227" s="11" t="inlineStr"/>
-      <c r="J227" s="11" t="inlineStr"/>
+      <c r="J227" s="11" t="inlineStr">
+        <is>
+          <t>HU162T</t>
+        </is>
+      </c>
       <c r="K227" s="11" t="inlineStr"/>
       <c r="L227" s="11" t="inlineStr">
         <is>
@@ -13376,7 +13583,7 @@
       </c>
       <c r="O227" s="11" t="inlineStr">
         <is>
-          <t>parts.audiusa(Q8/A8 4N0959754AMTKE), keyless2go(2021 A8)</t>
+          <t>parts.audiusa(Q8/A8 4N0959754AMTKE), keyless2go(2021 A8), auto-keys.eu(Audi A8·A6·Q8 2018+ 스마트키 4N0959754AL·e-tron 4M0959754BF 비상키 HU162T), keyshop-online(Audi MLB 2016+ 비상키 HU162T)</t>
         </is>
       </c>
       <c r="P227" s="11" t="inlineStr"/>
@@ -13411,7 +13618,11 @@
         </is>
       </c>
       <c r="I228" s="11" t="inlineStr"/>
-      <c r="J228" s="11" t="inlineStr"/>
+      <c r="J228" s="11" t="inlineStr">
+        <is>
+          <t>HU162T</t>
+        </is>
+      </c>
       <c r="K228" s="11" t="inlineStr"/>
       <c r="L228" s="11" t="inlineStr">
         <is>
@@ -13426,7 +13637,7 @@
       </c>
       <c r="O228" s="11" t="inlineStr">
         <is>
-          <t>parts.audibethesda(2022 A8 AM), parts.audiusa(2022 A8 CG)</t>
+          <t>parts.audibethesda(2022 A8 AM), parts.audiusa(2022 A8 CG), auto-keys.eu(Audi A8·A6·Q8 2018+ 스마트키 4N0959754AL·e-tron 4M0959754BF 비상키 HU162T), keyshop-online(Audi MLB 2016+ 비상키 HU162T)</t>
         </is>
       </c>
       <c r="P228" s="11" t="inlineStr"/>
@@ -13461,7 +13672,11 @@
         </is>
       </c>
       <c r="I229" s="11" t="inlineStr"/>
-      <c r="J229" s="11" t="inlineStr"/>
+      <c r="J229" s="11" t="inlineStr">
+        <is>
+          <t>HU162T</t>
+        </is>
+      </c>
       <c r="K229" s="11" t="inlineStr"/>
       <c r="L229" s="11" t="inlineStr">
         <is>
@@ -13476,7 +13691,7 @@
       </c>
       <c r="O229" s="11" t="inlineStr">
         <is>
-          <t>go-parts(2017-2026 guide), keylessentryremotefob(A8)</t>
+          <t>go-parts(2017-2026 guide), keylessentryremotefob(A8), auto-keys.eu(Audi A8·A6·Q8 2018+ 스마트키 4N0959754AL·e-tron 4M0959754BF 비상키 HU162T), keyshop-online(Audi MLB 2016+ 비상키 HU162T)</t>
         </is>
       </c>
       <c r="P229" s="14" t="n"/>
@@ -13511,7 +13726,11 @@
         </is>
       </c>
       <c r="I230" s="11" t="inlineStr"/>
-      <c r="J230" s="11" t="inlineStr"/>
+      <c r="J230" s="11" t="inlineStr">
+        <is>
+          <t>HU162T</t>
+        </is>
+      </c>
       <c r="K230" s="11" t="inlineStr"/>
       <c r="L230" s="11" t="inlineStr">
         <is>
@@ -13526,7 +13745,7 @@
       </c>
       <c r="O230" s="11" t="inlineStr">
         <is>
-          <t>keyless2go(2024 A8), programyourremote(2024 A8)</t>
+          <t>keyless2go(2024 A8), programyourremote(2024 A8), auto-keys.eu(Audi A8·A6·Q8 2018+ 스마트키 4N0959754AL·e-tron 4M0959754BF 비상키 HU162T), keyshop-online(Audi MLB 2016+ 비상키 HU162T)</t>
         </is>
       </c>
       <c r="P230" s="14" t="n"/>
@@ -13561,7 +13780,11 @@
         </is>
       </c>
       <c r="I231" s="11" t="inlineStr"/>
-      <c r="J231" s="11" t="inlineStr"/>
+      <c r="J231" s="11" t="inlineStr">
+        <is>
+          <t>HU162T</t>
+        </is>
+      </c>
       <c r="K231" s="11" t="inlineStr"/>
       <c r="L231" s="11" t="inlineStr">
         <is>
@@ -13576,7 +13799,7 @@
       </c>
       <c r="O231" s="11" t="inlineStr">
         <is>
-          <t>go-parts(2018-2026 A8), youtube(2025 Audi dead key fob)</t>
+          <t>go-parts(2018-2026 A8), youtube(2025 Audi dead key fob), auto-keys.eu(Audi A8·A6·Q8 2018+ 스마트키 4N0959754AL·e-tron 4M0959754BF 비상키 HU162T), keyshop-online(Audi MLB 2016+ 비상키 HU162T)</t>
         </is>
       </c>
       <c r="P231" s="14" t="n"/>
@@ -13611,7 +13834,11 @@
         </is>
       </c>
       <c r="I232" s="11" t="inlineStr"/>
-      <c r="J232" s="11" t="inlineStr"/>
+      <c r="J232" s="11" t="inlineStr">
+        <is>
+          <t>HU162T</t>
+        </is>
+      </c>
       <c r="K232" s="11" t="inlineStr"/>
       <c r="L232" s="11" t="inlineStr">
         <is>
@@ -13626,7 +13853,7 @@
       </c>
       <c r="O232" s="11" t="inlineStr">
         <is>
-          <t>autoblog(2026 A8), audi-me(A8 L 2026)</t>
+          <t>autoblog(2026 A8), audi-me(A8 L 2026), auto-keys.eu(Audi A8·A6·Q8 2018+ 스마트키 4N0959754AL·e-tron 4M0959754BF 비상키 HU162T), keyshop-online(Audi MLB 2016+ 비상키 HU162T)</t>
         </is>
       </c>
       <c r="P232" s="6" t="inlineStr">
@@ -13935,7 +14162,11 @@
         </is>
       </c>
       <c r="I238" s="11" t="inlineStr"/>
-      <c r="J238" s="11" t="inlineStr"/>
+      <c r="J238" s="11" t="inlineStr">
+        <is>
+          <t>HU162T</t>
+        </is>
+      </c>
       <c r="K238" s="11" t="inlineStr"/>
       <c r="L238" s="11" t="inlineStr">
         <is>
@@ -13950,7 +14181,7 @@
       </c>
       <c r="O238" s="11" t="inlineStr">
         <is>
-          <t>top-rider, autoview(S8 L TFSI 출시)</t>
+          <t>top-rider, autoview(S8 L TFSI 출시), auto-keys.eu(Audi A8·A6·Q8 2018+ 스마트키 4N0959754AL·e-tron 4M0959754BF 비상키 HU162T), keyshop-online(Audi MLB 2016+ 비상키 HU162T)</t>
         </is>
       </c>
       <c r="P238" s="14" t="n"/>
@@ -13985,7 +14216,11 @@
         </is>
       </c>
       <c r="I239" s="11" t="inlineStr"/>
-      <c r="J239" s="11" t="inlineStr"/>
+      <c r="J239" s="11" t="inlineStr">
+        <is>
+          <t>HU162T</t>
+        </is>
+      </c>
       <c r="K239" s="11" t="inlineStr"/>
       <c r="L239" s="11" t="inlineStr">
         <is>
@@ -14000,7 +14235,7 @@
       </c>
       <c r="O239" s="11" t="inlineStr">
         <is>
-          <t>audi.co.kr(S8 L 2024), parts.audivirginiabeach(4N0959754BF)</t>
+          <t>audi.co.kr(S8 L 2024), parts.audivirginiabeach(4N0959754BF), auto-keys.eu(Audi A8·A6·Q8 2018+ 스마트키 4N0959754AL·e-tron 4M0959754BF 비상키 HU162T), keyshop-online(Audi MLB 2016+ 비상키 HU162T)</t>
         </is>
       </c>
       <c r="P239" s="14" t="n"/>
@@ -14035,7 +14270,11 @@
         </is>
       </c>
       <c r="I240" s="11" t="inlineStr"/>
-      <c r="J240" s="11" t="inlineStr"/>
+      <c r="J240" s="11" t="inlineStr">
+        <is>
+          <t>HU162T</t>
+        </is>
+      </c>
       <c r="K240" s="11" t="inlineStr"/>
       <c r="L240" s="11" t="inlineStr">
         <is>
@@ -14050,7 +14289,7 @@
       </c>
       <c r="O240" s="11" t="inlineStr">
         <is>
-          <t>parts.audiusa(2025 SQ8 4N0959754BFTKE), go-parts</t>
+          <t>parts.audiusa(2025 SQ8 4N0959754BFTKE), go-parts, auto-keys.eu(Audi A8·A6·Q8 2018+ 스마트키 4N0959754AL·e-tron 4M0959754BF 비상키 HU162T), keyshop-online(Audi MLB 2016+ 비상키 HU162T)</t>
         </is>
       </c>
       <c r="P240" s="14" t="n"/>
@@ -14085,7 +14324,11 @@
         </is>
       </c>
       <c r="I241" s="11" t="inlineStr"/>
-      <c r="J241" s="11" t="inlineStr"/>
+      <c r="J241" s="11" t="inlineStr">
+        <is>
+          <t>HU162T</t>
+        </is>
+      </c>
       <c r="K241" s="11" t="inlineStr"/>
       <c r="L241" s="11" t="inlineStr">
         <is>
@@ -14100,7 +14343,7 @@
       </c>
       <c r="O241" s="11" t="inlineStr">
         <is>
-          <t>cars.com(2026 S8), kbb(2026 S8 specs)</t>
+          <t>cars.com(2026 S8), kbb(2026 S8 specs), auto-keys.eu(Audi A8·A6·Q8 2018+ 스마트키 4N0959754AL·e-tron 4M0959754BF 비상키 HU162T), keyshop-online(Audi MLB 2016+ 비상키 HU162T)</t>
         </is>
       </c>
       <c r="P241" s="6" t="inlineStr">
@@ -16633,7 +16876,11 @@
         </is>
       </c>
       <c r="I279" s="11" t="inlineStr"/>
-      <c r="J279" s="11" t="inlineStr"/>
+      <c r="J279" s="11" t="inlineStr">
+        <is>
+          <t>HU66</t>
+        </is>
+      </c>
       <c r="K279" s="11" t="inlineStr"/>
       <c r="L279" s="11" t="inlineStr"/>
       <c r="M279" s="11" t="inlineStr"/>
@@ -16644,7 +16891,7 @@
       </c>
       <c r="O279" s="11" t="inlineStr">
         <is>
-          <t>namu.wiki(Q4 e-트론), dealsite(Q4 e-트론 출시), e-tronforum(Q4 key type)</t>
+          <t>namu.wiki(Q4 e-트론), dealsite(Q4 e-트론 출시), e-tronforum(Q4 key type), MEB 플랫폼 키(폭스바겐 ID.4와 공용) — 비상키 HU66</t>
         </is>
       </c>
       <c r="P279" s="6" t="inlineStr">
@@ -16695,7 +16942,11 @@
         </is>
       </c>
       <c r="I280" s="11" t="inlineStr"/>
-      <c r="J280" s="11" t="inlineStr"/>
+      <c r="J280" s="11" t="inlineStr">
+        <is>
+          <t>HU66</t>
+        </is>
+      </c>
       <c r="K280" s="11" t="inlineStr"/>
       <c r="L280" s="11" t="inlineStr"/>
       <c r="M280" s="11" t="inlineStr"/>
@@ -16706,7 +16957,7 @@
       </c>
       <c r="O280" s="11" t="inlineStr">
         <is>
-          <t>parts.audiusa(4N0959754AQTKE), ebay(Q4 key cover 89A071208Y9T)</t>
+          <t>parts.audiusa(4N0959754AQTKE), ebay(Q4 key cover 89A071208Y9T), MEB 플랫폼 키(폭스바겐 ID.4와 공용) — 비상키 HU66</t>
         </is>
       </c>
       <c r="P280" s="6" t="inlineStr">
@@ -16757,7 +17008,11 @@
         </is>
       </c>
       <c r="I281" s="11" t="inlineStr"/>
-      <c r="J281" s="11" t="inlineStr"/>
+      <c r="J281" s="11" t="inlineStr">
+        <is>
+          <t>HU66</t>
+        </is>
+      </c>
       <c r="K281" s="11" t="inlineStr"/>
       <c r="L281" s="11" t="inlineStr"/>
       <c r="M281" s="11" t="inlineStr"/>
@@ -16768,7 +17023,7 @@
       </c>
       <c r="O281" s="11" t="inlineStr">
         <is>
-          <t>electrichasgoneaudi(Q4 locking systems), autouserguide(2024 Q4 keys)</t>
+          <t>electrichasgoneaudi(Q4 locking systems), autouserguide(2024 Q4 keys), MEB 플랫폼 키(폭스바겐 ID.4와 공용) — 비상키 HU66</t>
         </is>
       </c>
       <c r="P281" s="6" t="inlineStr">
@@ -16819,7 +17074,11 @@
         </is>
       </c>
       <c r="I282" s="11" t="inlineStr"/>
-      <c r="J282" s="11" t="inlineStr"/>
+      <c r="J282" s="11" t="inlineStr">
+        <is>
+          <t>HU66</t>
+        </is>
+      </c>
       <c r="K282" s="11" t="inlineStr"/>
       <c r="L282" s="11" t="inlineStr"/>
       <c r="M282" s="11" t="inlineStr"/>
@@ -16830,7 +17089,7 @@
       </c>
       <c r="O282" s="11" t="inlineStr">
         <is>
-          <t>ebay(2025 Q4 8Y0959754CJ), e-tronforum(Q4 keyless entry)</t>
+          <t>ebay(2025 Q4 8Y0959754CJ), e-tronforum(Q4 keyless entry), MEB 플랫폼 키(폭스바겐 ID.4와 공용) — 비상키 HU66</t>
         </is>
       </c>
       <c r="P282" s="6" t="inlineStr">
@@ -16881,7 +17140,11 @@
         </is>
       </c>
       <c r="I283" s="11" t="inlineStr"/>
-      <c r="J283" s="11" t="inlineStr"/>
+      <c r="J283" s="11" t="inlineStr">
+        <is>
+          <t>HU66</t>
+        </is>
+      </c>
       <c r="K283" s="11" t="inlineStr"/>
       <c r="L283" s="11" t="inlineStr"/>
       <c r="M283" s="11" t="inlineStr"/>
@@ -16892,7 +17155,7 @@
       </c>
       <c r="O283" s="11" t="inlineStr">
         <is>
-          <t>electrichasgoneaudi(Q4 locking), autoview(Q4 2027 F/L)</t>
+          <t>electrichasgoneaudi(Q4 locking), autoview(Q4 2027 F/L), MEB 플랫폼 키(폭스바겐 ID.4와 공용) — 비상키 HU66</t>
         </is>
       </c>
       <c r="P283" s="6" t="inlineStr">
@@ -17731,12 +17994,12 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="D299" s="7" t="inlineStr"/>
-      <c r="E299" s="7" t="inlineStr"/>
-      <c r="F299" s="7" t="inlineStr"/>
-      <c r="G299" s="8" t="inlineStr">
-        <is>
-          <t>확인 불가</t>
+      <c r="D299" s="7" t="n"/>
+      <c r="E299" s="7" t="n"/>
+      <c r="F299" s="7" t="n"/>
+      <c r="G299" s="6" t="inlineStr">
+        <is>
+          <t>MLB evo 전용 칩[추정]</t>
         </is>
       </c>
       <c r="H299" s="11" t="inlineStr">
@@ -17745,23 +18008,27 @@
         </is>
       </c>
       <c r="I299" s="11" t="inlineStr"/>
-      <c r="J299" s="11" t="inlineStr"/>
+      <c r="J299" s="11" t="inlineStr">
+        <is>
+          <t>HU162T</t>
+        </is>
+      </c>
       <c r="K299" s="11" t="inlineStr"/>
       <c r="L299" s="11" t="inlineStr"/>
       <c r="M299" s="11" t="inlineStr"/>
-      <c r="N299" s="8" t="inlineStr">
+      <c r="N299" s="6" t="inlineStr">
         <is>
           <t>확인 불가</t>
         </is>
       </c>
       <c r="O299" s="11" t="inlineStr">
         <is>
-          <t>audi.co.kr(더 뉴 Q5 2025-07-01), danawa(신형 Q5)</t>
-        </is>
-      </c>
-      <c r="P299" s="8" t="inlineStr">
-        <is>
-          <t>신형 키(PPE·PPC·MEB) 칩·이모빌라이저 자료 없음</t>
+          <t>audi.co.kr(더 뉴 Q5 2025-07-01), danawa(신형 Q5), Audi USA 순정 부품(2025 Q6 e-tron·Q5·A5·SQ5 스마트키 4M0959754CG 공용 — 북미형이라 품번 뺌) — MLB evo 계열 키 기준 추정</t>
+        </is>
+      </c>
+      <c r="P299" s="6" t="inlineStr">
+        <is>
+          <t>2025년 이후 신형(PPE·PPC) 전용 칩 자료 없음 — MLB evo 공용 키 기준 추정</t>
         </is>
       </c>
     </row>
@@ -17781,12 +18048,12 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="D300" s="7" t="inlineStr"/>
-      <c r="E300" s="7" t="inlineStr"/>
-      <c r="F300" s="7" t="inlineStr"/>
-      <c r="G300" s="8" t="inlineStr">
-        <is>
-          <t>확인 불가</t>
+      <c r="D300" s="7" t="n"/>
+      <c r="E300" s="7" t="n"/>
+      <c r="F300" s="7" t="n"/>
+      <c r="G300" s="6" t="inlineStr">
+        <is>
+          <t>MLB evo 전용 칩[추정]</t>
         </is>
       </c>
       <c r="H300" s="11" t="inlineStr">
@@ -17795,23 +18062,27 @@
         </is>
       </c>
       <c r="I300" s="11" t="inlineStr"/>
-      <c r="J300" s="11" t="inlineStr"/>
+      <c r="J300" s="11" t="inlineStr">
+        <is>
+          <t>HU162T</t>
+        </is>
+      </c>
       <c r="K300" s="11" t="inlineStr"/>
       <c r="L300" s="11" t="inlineStr"/>
       <c r="M300" s="11" t="inlineStr"/>
-      <c r="N300" s="8" t="inlineStr">
+      <c r="N300" s="6" t="inlineStr">
         <is>
           <t>확인 불가</t>
         </is>
       </c>
       <c r="O300" s="11" t="inlineStr">
         <is>
-          <t>audiusa(new Q5 FAQ), mycarusermanual(Q5 3rd gen keys)</t>
-        </is>
-      </c>
-      <c r="P300" s="8" t="inlineStr">
-        <is>
-          <t>신형 키(PPE·PPC·MEB) 칩·이모빌라이저 자료 없음</t>
+          <t>audiusa(new Q5 FAQ), mycarusermanual(Q5 3rd gen keys), Audi USA 순정 부품(2025 Q6 e-tron·Q5·A5·SQ5 스마트키 4M0959754CG 공용 — 북미형이라 품번 뺌) — MLB evo 계열 키 기준 추정</t>
+        </is>
+      </c>
+      <c r="P300" s="6" t="inlineStr">
+        <is>
+          <t>2025년 이후 신형(PPE·PPC) 전용 칩 자료 없음 — MLB evo 공용 키 기준 추정</t>
         </is>
       </c>
     </row>
@@ -18328,9 +18599,9 @@
       <c r="D310" s="7" t="n"/>
       <c r="E310" s="7" t="n"/>
       <c r="F310" s="7" t="n"/>
-      <c r="G310" s="14" t="inlineStr">
-        <is>
-          <t>MLB 전용 칩[FY]</t>
+      <c r="G310" s="6" t="inlineStr">
+        <is>
+          <t>MLB evo 전용 칩[추정]</t>
         </is>
       </c>
       <c r="H310" s="11" t="inlineStr">
@@ -18341,23 +18612,27 @@
       <c r="I310" s="11" t="n"/>
       <c r="J310" s="11" t="inlineStr">
         <is>
-          <t>HU66</t>
+          <t>HU162T</t>
         </is>
       </c>
       <c r="K310" s="11" t="n"/>
       <c r="L310" s="11" t="n"/>
       <c r="M310" s="11" t="n"/>
-      <c r="N310" s="14" t="inlineStr">
+      <c r="N310" s="6" t="inlineStr">
         <is>
           <t>MLB IMMO5[FY]</t>
         </is>
       </c>
       <c r="O310" s="11" t="inlineStr">
         <is>
-          <t>top-rider(신형 SQ5 국내 출시 예고), autoview(3세대 SQ5)</t>
-        </is>
-      </c>
-      <c r="P310" s="14" t="n"/>
+          <t>top-rider(신형 SQ5 국내 출시 예고), autoview(3세대 SQ5), Audi USA 순정 부품(2025 Q6 e-tron·Q5·A5·SQ5 스마트키 4M0959754CG 공용 — 북미형이라 품번 뺌) — MLB evo 계열 키 기준 추정</t>
+        </is>
+      </c>
+      <c r="P310" s="6" t="inlineStr">
+        <is>
+          <t>2025년 이후 신형(PPE·PPC) 전용 칩 자료 없음 — MLB evo 공용 키 기준 추정</t>
+        </is>
+      </c>
     </row>
     <row r="311">
       <c r="A311" s="11" t="inlineStr">
@@ -18378,9 +18653,9 @@
       <c r="D311" s="7" t="n"/>
       <c r="E311" s="7" t="n"/>
       <c r="F311" s="7" t="n"/>
-      <c r="G311" s="8" t="inlineStr">
-        <is>
-          <t>확인 불가[3세대, 2025년 4분기~]</t>
+      <c r="G311" s="6" t="inlineStr">
+        <is>
+          <t>MLB evo 전용 칩[추정]</t>
         </is>
       </c>
       <c r="H311" s="11" t="inlineStr">
@@ -18389,23 +18664,27 @@
         </is>
       </c>
       <c r="I311" s="11" t="n"/>
-      <c r="J311" s="11" t="n"/>
+      <c r="J311" s="11" t="inlineStr">
+        <is>
+          <t>HU162T</t>
+        </is>
+      </c>
       <c r="K311" s="11" t="n"/>
       <c r="L311" s="11" t="n"/>
       <c r="M311" s="11" t="n"/>
-      <c r="N311" s="8" t="inlineStr">
+      <c r="N311" s="6" t="inlineStr">
         <is>
           <t>확인 불가[3세대]</t>
         </is>
       </c>
       <c r="O311" s="11" t="inlineStr">
         <is>
-          <t>top-rider(신형 SQ5 국내 출시 예고), autoview(3세대 SQ5)</t>
-        </is>
-      </c>
-      <c r="P311" s="8" t="inlineStr">
-        <is>
-          <t>3세대 SQ5 신형 키 칩 자료 없음</t>
+          <t>top-rider(신형 SQ5 국내 출시 예고), autoview(3세대 SQ5), Audi USA 순정 부품(2025 Q6 e-tron·Q5·A5·SQ5 스마트키 4M0959754CG 공용 — 북미형이라 품번 뺌) — MLB evo 계열 키 기준 추정</t>
+        </is>
+      </c>
+      <c r="P311" s="6" t="inlineStr">
+        <is>
+          <t>2025년 이후 신형(PPE·PPC) 전용 칩 자료 없음 — MLB evo 공용 키 기준 추정</t>
         </is>
       </c>
     </row>
@@ -18425,12 +18704,12 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="D312" s="7" t="inlineStr"/>
-      <c r="E312" s="7" t="inlineStr"/>
-      <c r="F312" s="7" t="inlineStr"/>
-      <c r="G312" s="8" t="inlineStr">
-        <is>
-          <t>확인 불가</t>
+      <c r="D312" s="7" t="n"/>
+      <c r="E312" s="7" t="n"/>
+      <c r="F312" s="7" t="n"/>
+      <c r="G312" s="6" t="inlineStr">
+        <is>
+          <t>MLB evo 전용 칩[추정]</t>
         </is>
       </c>
       <c r="H312" s="11" t="inlineStr">
@@ -18439,23 +18718,27 @@
         </is>
       </c>
       <c r="I312" s="11" t="inlineStr"/>
-      <c r="J312" s="11" t="inlineStr"/>
+      <c r="J312" s="11" t="inlineStr">
+        <is>
+          <t>HU162T</t>
+        </is>
+      </c>
       <c r="K312" s="11" t="inlineStr"/>
       <c r="L312" s="11" t="inlineStr"/>
       <c r="M312" s="11" t="inlineStr"/>
-      <c r="N312" s="8" t="inlineStr">
+      <c r="N312" s="6" t="inlineStr">
         <is>
           <t>확인 불가</t>
         </is>
       </c>
       <c r="O312" s="11" t="inlineStr">
         <is>
-          <t>audiusa(2026 SQ5), media.audiusa(2026 A5/Q5)</t>
-        </is>
-      </c>
-      <c r="P312" s="8" t="inlineStr">
-        <is>
-          <t>신형 키(PPE·PPC·MEB) 칩·이모빌라이저 자료 없음</t>
+          <t>audiusa(2026 SQ5), media.audiusa(2026 A5/Q5), Audi USA 순정 부품(2025 Q6 e-tron·Q5·A5·SQ5 스마트키 4M0959754CG 공용 — 북미형이라 품번 뺌) — MLB evo 계열 키 기준 추정</t>
+        </is>
+      </c>
+      <c r="P312" s="6" t="inlineStr">
+        <is>
+          <t>2025년 이후 신형(PPE·PPC) 전용 칩 자료 없음 — MLB evo 공용 키 기준 추정</t>
         </is>
       </c>
     </row>
@@ -18475,12 +18758,12 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="D313" s="7" t="inlineStr"/>
-      <c r="E313" s="7" t="inlineStr"/>
-      <c r="F313" s="7" t="inlineStr"/>
-      <c r="G313" s="8" t="inlineStr">
-        <is>
-          <t>확인 불가</t>
+      <c r="D313" s="7" t="n"/>
+      <c r="E313" s="7" t="n"/>
+      <c r="F313" s="7" t="n"/>
+      <c r="G313" s="6" t="inlineStr">
+        <is>
+          <t>MLB evo 전용 칩[추정]</t>
         </is>
       </c>
       <c r="H313" s="11" t="inlineStr">
@@ -18489,23 +18772,27 @@
         </is>
       </c>
       <c r="I313" s="11" t="inlineStr"/>
-      <c r="J313" s="11" t="inlineStr"/>
+      <c r="J313" s="11" t="inlineStr">
+        <is>
+          <t>HU162T</t>
+        </is>
+      </c>
       <c r="K313" s="11" t="inlineStr"/>
       <c r="L313" s="11" t="inlineStr"/>
       <c r="M313" s="11" t="inlineStr"/>
-      <c r="N313" s="8" t="inlineStr">
+      <c r="N313" s="6" t="inlineStr">
         <is>
           <t>확인 불가</t>
         </is>
       </c>
       <c r="O313" s="11" t="inlineStr">
         <is>
-          <t>continental(Q6 e-tron access system 2025-06-25), audiusa(Q6 FAQ)</t>
-        </is>
-      </c>
-      <c r="P313" s="8" t="inlineStr">
-        <is>
-          <t>신형 키(PPE·PPC·MEB) 칩·이모빌라이저 자료 없음</t>
+          <t>continental(Q6 e-tron access system 2025-06-25), audiusa(Q6 FAQ), Audi USA 순정 부품(2025 Q6 e-tron·Q5·A5·SQ5 스마트키 4M0959754CG 공용 — 북미형이라 품번 뺌) — MLB evo 계열 키 기준 추정</t>
+        </is>
+      </c>
+      <c r="P313" s="6" t="inlineStr">
+        <is>
+          <t>2025년 이후 신형(PPE·PPC) 전용 칩 자료 없음 — MLB evo 공용 키 기준 추정</t>
         </is>
       </c>
     </row>
@@ -18525,12 +18812,12 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="D314" s="7" t="inlineStr"/>
-      <c r="E314" s="7" t="inlineStr"/>
-      <c r="F314" s="7" t="inlineStr"/>
-      <c r="G314" s="8" t="inlineStr">
-        <is>
-          <t>확인 불가</t>
+      <c r="D314" s="7" t="n"/>
+      <c r="E314" s="7" t="n"/>
+      <c r="F314" s="7" t="n"/>
+      <c r="G314" s="6" t="inlineStr">
+        <is>
+          <t>MLB evo 전용 칩[추정]</t>
         </is>
       </c>
       <c r="H314" s="11" t="inlineStr">
@@ -18539,23 +18826,27 @@
         </is>
       </c>
       <c r="I314" s="11" t="inlineStr"/>
-      <c r="J314" s="11" t="inlineStr"/>
+      <c r="J314" s="11" t="inlineStr">
+        <is>
+          <t>HU162T</t>
+        </is>
+      </c>
       <c r="K314" s="11" t="inlineStr"/>
       <c r="L314" s="11" t="inlineStr"/>
       <c r="M314" s="11" t="inlineStr"/>
-      <c r="N314" s="8" t="inlineStr">
+      <c r="N314" s="6" t="inlineStr">
         <is>
           <t>확인 불가</t>
         </is>
       </c>
       <c r="O314" s="11" t="inlineStr">
         <is>
-          <t>audiusa(Q6 FAQ), parts.audiusa(2026 Q6 e-tron parts)</t>
-        </is>
-      </c>
-      <c r="P314" s="8" t="inlineStr">
-        <is>
-          <t>신형 키(PPE·PPC·MEB) 칩·이모빌라이저 자료 없음</t>
+          <t>audiusa(Q6 FAQ), parts.audiusa(2026 Q6 e-tron parts), Audi USA 순정 부품(2025 Q6 e-tron·Q5·A5·SQ5 스마트키 4M0959754CG 공용 — 북미형이라 품번 뺌) — MLB evo 계열 키 기준 추정</t>
+        </is>
+      </c>
+      <c r="P314" s="6" t="inlineStr">
+        <is>
+          <t>2025년 이후 신형(PPE·PPC) 전용 칩 자료 없음 — MLB evo 공용 키 기준 추정</t>
         </is>
       </c>
     </row>
@@ -20283,7 +20574,11 @@
         </is>
       </c>
       <c r="I346" s="11" t="inlineStr"/>
-      <c r="J346" s="11" t="inlineStr"/>
+      <c r="J346" s="11" t="inlineStr">
+        <is>
+          <t>HU162T</t>
+        </is>
+      </c>
       <c r="K346" s="11" t="inlineStr"/>
       <c r="L346" s="11" t="inlineStr">
         <is>
@@ -20298,7 +20593,7 @@
       </c>
       <c r="O346" s="11" t="inlineStr">
         <is>
-          <t>hankookilbo(SQ8 TDI 출시), parts.audiusa(SQ8 4N0959754BFTKE)</t>
+          <t>hankookilbo(SQ8 TDI 출시), parts.audiusa(SQ8 4N0959754BFTKE), auto-keys.eu(Audi A8·A6·Q8 2018+ 스마트키 4N0959754AL·e-tron 4M0959754BF 비상키 HU162T), keyshop-online(Audi MLB 2016+ 비상키 HU162T)</t>
         </is>
       </c>
       <c r="P346" s="11" t="inlineStr"/>
@@ -20333,7 +20628,11 @@
         </is>
       </c>
       <c r="I347" s="11" t="inlineStr"/>
-      <c r="J347" s="11" t="inlineStr"/>
+      <c r="J347" s="11" t="inlineStr">
+        <is>
+          <t>HU162T</t>
+        </is>
+      </c>
       <c r="K347" s="11" t="inlineStr"/>
       <c r="L347" s="11" t="inlineStr">
         <is>
@@ -20348,7 +20647,7 @@
       </c>
       <c r="O347" s="11" t="inlineStr">
         <is>
-          <t>parts.audiusa(2021 SQ8), programyourremote(2021 SQ8)</t>
+          <t>parts.audiusa(2021 SQ8), programyourremote(2021 SQ8), auto-keys.eu(Audi A8·A6·Q8 2018+ 스마트키 4N0959754AL·e-tron 4M0959754BF 비상키 HU162T), keyshop-online(Audi MLB 2016+ 비상키 HU162T)</t>
         </is>
       </c>
       <c r="P347" s="11" t="inlineStr"/>
@@ -20383,7 +20682,11 @@
         </is>
       </c>
       <c r="I348" s="11" t="inlineStr"/>
-      <c r="J348" s="11" t="inlineStr"/>
+      <c r="J348" s="11" t="inlineStr">
+        <is>
+          <t>HU162T</t>
+        </is>
+      </c>
       <c r="K348" s="11" t="inlineStr"/>
       <c r="L348" s="11" t="inlineStr">
         <is>
@@ -20398,7 +20701,7 @@
       </c>
       <c r="O348" s="11" t="inlineStr">
         <is>
-          <t>parts.audiusa(2022 SQ8)</t>
+          <t>parts.audiusa(2022 SQ8), auto-keys.eu(Audi A8·A6·Q8 2018+ 스마트키 4N0959754AL·e-tron 4M0959754BF 비상키 HU162T), keyshop-online(Audi MLB 2016+ 비상키 HU162T)</t>
         </is>
       </c>
       <c r="P348" s="14" t="n"/>
@@ -20433,7 +20736,11 @@
         </is>
       </c>
       <c r="I349" s="11" t="inlineStr"/>
-      <c r="J349" s="11" t="inlineStr"/>
+      <c r="J349" s="11" t="inlineStr">
+        <is>
+          <t>HU162T</t>
+        </is>
+      </c>
       <c r="K349" s="11" t="inlineStr"/>
       <c r="L349" s="11" t="inlineStr">
         <is>
@@ -20448,7 +20755,7 @@
       </c>
       <c r="O349" s="11" t="inlineStr">
         <is>
-          <t>parts.audiusa(2023 SQ8), carandtruckremotes(2023 SQ8)</t>
+          <t>parts.audiusa(2023 SQ8), carandtruckremotes(2023 SQ8), auto-keys.eu(Audi A8·A6·Q8 2018+ 스마트키 4N0959754AL·e-tron 4M0959754BF 비상키 HU162T), keyshop-online(Audi MLB 2016+ 비상키 HU162T)</t>
         </is>
       </c>
       <c r="P349" s="14" t="n"/>
@@ -20483,7 +20790,11 @@
         </is>
       </c>
       <c r="I350" s="11" t="inlineStr"/>
-      <c r="J350" s="11" t="inlineStr"/>
+      <c r="J350" s="11" t="inlineStr">
+        <is>
+          <t>HU162T</t>
+        </is>
+      </c>
       <c r="K350" s="11" t="inlineStr"/>
       <c r="L350" s="11" t="inlineStr">
         <is>
@@ -20498,7 +20809,7 @@
       </c>
       <c r="O350" s="11" t="inlineStr">
         <is>
-          <t>parts.audivirginiabeach(SQ8 BF), wikipedia(Q8)</t>
+          <t>parts.audivirginiabeach(SQ8 BF), wikipedia(Q8), auto-keys.eu(Audi A8·A6·Q8 2018+ 스마트키 4N0959754AL·e-tron 4M0959754BF 비상키 HU162T), keyshop-online(Audi MLB 2016+ 비상키 HU162T)</t>
         </is>
       </c>
       <c r="P350" s="14" t="n"/>
@@ -20533,7 +20844,11 @@
         </is>
       </c>
       <c r="I351" s="11" t="inlineStr"/>
-      <c r="J351" s="11" t="inlineStr"/>
+      <c r="J351" s="11" t="inlineStr">
+        <is>
+          <t>HU162T</t>
+        </is>
+      </c>
       <c r="K351" s="11" t="inlineStr"/>
       <c r="L351" s="11" t="inlineStr">
         <is>
@@ -20548,7 +20863,7 @@
       </c>
       <c r="O351" s="11" t="inlineStr">
         <is>
-          <t>parts.audiusa(2025 SQ8)</t>
+          <t>parts.audiusa(2025 SQ8), auto-keys.eu(Audi A8·A6·Q8 2018+ 스마트키 4N0959754AL·e-tron 4M0959754BF 비상키 HU162T), keyshop-online(Audi MLB 2016+ 비상키 HU162T)</t>
         </is>
       </c>
       <c r="P351" s="14" t="n"/>
@@ -20583,7 +20898,11 @@
         </is>
       </c>
       <c r="I352" s="11" t="inlineStr"/>
-      <c r="J352" s="11" t="inlineStr"/>
+      <c r="J352" s="11" t="inlineStr">
+        <is>
+          <t>HU162T</t>
+        </is>
+      </c>
       <c r="K352" s="11" t="inlineStr"/>
       <c r="L352" s="11" t="inlineStr">
         <is>
@@ -20598,7 +20917,7 @@
       </c>
       <c r="O352" s="11" t="inlineStr">
         <is>
-          <t>kbb(2026 SQ8 specs), audiusa(2026 SQ8)</t>
+          <t>kbb(2026 SQ8 specs), audiusa(2026 SQ8), auto-keys.eu(Audi A8·A6·Q8 2018+ 스마트키 4N0959754AL·e-tron 4M0959754BF 비상키 HU162T), keyshop-online(Audi MLB 2016+ 비상키 HU162T)</t>
         </is>
       </c>
       <c r="P352" s="6" t="inlineStr">
@@ -20637,7 +20956,11 @@
         </is>
       </c>
       <c r="I353" s="11" t="inlineStr"/>
-      <c r="J353" s="11" t="inlineStr"/>
+      <c r="J353" s="11" t="inlineStr">
+        <is>
+          <t>HU162T</t>
+        </is>
+      </c>
       <c r="K353" s="11" t="inlineStr"/>
       <c r="L353" s="11" t="inlineStr">
         <is>
@@ -20652,7 +20975,7 @@
       </c>
       <c r="O353" s="11" t="inlineStr">
         <is>
-          <t>parts.audibethesda(4N0959754BC 433.92MHz), ebay(2021 RSQ8 key), ajunews(RS Q8 출시 2021-06-11)</t>
+          <t>parts.audibethesda(4N0959754BC 433.92MHz), ebay(2021 RSQ8 key), ajunews(RS Q8 출시 2021-06-11), auto-keys.eu(Audi A8·A6·Q8 2018+ 스마트키 4N0959754AL·e-tron 4M0959754BF 비상키 HU162T), keyshop-online(Audi MLB 2016+ 비상키 HU162T)</t>
         </is>
       </c>
       <c r="P353" s="11" t="inlineStr"/>
@@ -20687,7 +21010,11 @@
         </is>
       </c>
       <c r="I354" s="11" t="inlineStr"/>
-      <c r="J354" s="11" t="inlineStr"/>
+      <c r="J354" s="11" t="inlineStr">
+        <is>
+          <t>HU162T</t>
+        </is>
+      </c>
       <c r="K354" s="11" t="inlineStr"/>
       <c r="L354" s="11" t="inlineStr">
         <is>
@@ -20702,7 +21029,7 @@
       </c>
       <c r="O354" s="11" t="inlineStr">
         <is>
-          <t>parts.audiusa(2022 e-tron GT/RSQ8 BC)</t>
+          <t>parts.audiusa(2022 e-tron GT/RSQ8 BC), auto-keys.eu(Audi A8·A6·Q8 2018+ 스마트키 4N0959754AL·e-tron 4M0959754BF 비상키 HU162T), keyshop-online(Audi MLB 2016+ 비상키 HU162T)</t>
         </is>
       </c>
       <c r="P354" s="11" t="inlineStr"/>
@@ -20737,7 +21064,11 @@
         </is>
       </c>
       <c r="I355" s="11" t="inlineStr"/>
-      <c r="J355" s="11" t="inlineStr"/>
+      <c r="J355" s="11" t="inlineStr">
+        <is>
+          <t>HU162T</t>
+        </is>
+      </c>
       <c r="K355" s="11" t="inlineStr"/>
       <c r="L355" s="11" t="inlineStr">
         <is>
@@ -20752,7 +21083,7 @@
       </c>
       <c r="O355" s="11" t="inlineStr">
         <is>
-          <t>parts.audiusa(2023 RSQ8)</t>
+          <t>parts.audiusa(2023 RSQ8), auto-keys.eu(Audi A8·A6·Q8 2018+ 스마트키 4N0959754AL·e-tron 4M0959754BF 비상키 HU162T), keyshop-online(Audi MLB 2016+ 비상키 HU162T)</t>
         </is>
       </c>
       <c r="P355" s="11" t="inlineStr"/>
@@ -20787,7 +21118,11 @@
         </is>
       </c>
       <c r="I356" s="11" t="inlineStr"/>
-      <c r="J356" s="11" t="inlineStr"/>
+      <c r="J356" s="11" t="inlineStr">
+        <is>
+          <t>HU162T</t>
+        </is>
+      </c>
       <c r="K356" s="11" t="inlineStr"/>
       <c r="L356" s="11" t="inlineStr">
         <is>
@@ -20802,7 +21137,7 @@
       </c>
       <c r="O356" s="11" t="inlineStr">
         <is>
-          <t>parts.audibethesda(2024 RSQ8 BC)</t>
+          <t>parts.audibethesda(2024 RSQ8 BC), auto-keys.eu(Audi A8·A6·Q8 2018+ 스마트키 4N0959754AL·e-tron 4M0959754BF 비상키 HU162T), keyshop-online(Audi MLB 2016+ 비상키 HU162T)</t>
         </is>
       </c>
       <c r="P356" s="11" t="inlineStr"/>
@@ -20837,7 +21172,11 @@
         </is>
       </c>
       <c r="I357" s="11" t="inlineStr"/>
-      <c r="J357" s="11" t="inlineStr"/>
+      <c r="J357" s="11" t="inlineStr">
+        <is>
+          <t>HU162T</t>
+        </is>
+      </c>
       <c r="K357" s="11" t="inlineStr"/>
       <c r="L357" s="11" t="inlineStr">
         <is>
@@ -20852,7 +21191,7 @@
       </c>
       <c r="O357" s="11" t="inlineStr">
         <is>
-          <t>audi.co.kr(RS Q8 퍼포먼스 2025-02-24), parts.audiusa(RSQ8 BC)</t>
+          <t>audi.co.kr(RS Q8 퍼포먼스 2025-02-24), parts.audiusa(RSQ8 BC), auto-keys.eu(Audi A8·A6·Q8 2018+ 스마트키 4N0959754AL·e-tron 4M0959754BF 비상키 HU162T), keyshop-online(Audi MLB 2016+ 비상키 HU162T)</t>
         </is>
       </c>
       <c r="P357" s="11" t="inlineStr"/>
@@ -20887,7 +21226,11 @@
         </is>
       </c>
       <c r="I358" s="11" t="inlineStr"/>
-      <c r="J358" s="11" t="inlineStr"/>
+      <c r="J358" s="11" t="inlineStr">
+        <is>
+          <t>HU162T</t>
+        </is>
+      </c>
       <c r="K358" s="11" t="inlineStr"/>
       <c r="L358" s="11" t="inlineStr">
         <is>
@@ -20902,7 +21245,7 @@
       </c>
       <c r="O358" s="11" t="inlineStr">
         <is>
-          <t>audiusa(2026 RS Q8 performance), kbb(2026 RS Q8)</t>
+          <t>audiusa(2026 RS Q8 performance), kbb(2026 RS Q8), auto-keys.eu(Audi A8·A6·Q8 2018+ 스마트키 4N0959754AL·e-tron 4M0959754BF 비상키 HU162T), keyshop-online(Audi MLB 2016+ 비상키 HU162T)</t>
         </is>
       </c>
       <c r="P358" s="14" t="n"/>
@@ -20937,7 +21280,11 @@
         </is>
       </c>
       <c r="I359" s="11" t="inlineStr"/>
-      <c r="J359" s="11" t="inlineStr"/>
+      <c r="J359" s="11" t="inlineStr">
+        <is>
+          <t>HU162T</t>
+        </is>
+      </c>
       <c r="K359" s="11" t="inlineStr"/>
       <c r="L359" s="11" t="inlineStr">
         <is>
@@ -20952,7 +21299,7 @@
       </c>
       <c r="O359" s="11" t="inlineStr">
         <is>
-          <t>2021년식 기록 준용 — motorgraph(e-트론 국내 출시), parts.audiusa(e-tron 4N0959754AQTKE), hubspot(2021 e-tron mechanical key tipsheet)</t>
+          <t>2021년식 기록 준용 — motorgraph(e-트론 국내 출시), parts.audiusa(e-tron 4N0959754AQTKE), hubspot(2021 e-tron mechanical key tipsheet), auto-keys.eu(Audi A8·A6·Q8 2018+ 스마트키 4N0959754AL·e-tron 4M0959754BF 비상키 HU162T), keyshop-online(Audi MLB 2016+ 비상키 HU162T)</t>
         </is>
       </c>
       <c r="P359" s="14" t="n"/>
@@ -20987,7 +21334,11 @@
         </is>
       </c>
       <c r="I360" s="11" t="inlineStr"/>
-      <c r="J360" s="11" t="inlineStr"/>
+      <c r="J360" s="11" t="inlineStr">
+        <is>
+          <t>HU162T</t>
+        </is>
+      </c>
       <c r="K360" s="11" t="inlineStr"/>
       <c r="L360" s="11" t="inlineStr">
         <is>
@@ -21002,7 +21353,7 @@
       </c>
       <c r="O360" s="11" t="inlineStr">
         <is>
-          <t>motorgraph(e-트론 국내 출시), parts.audiusa(e-tron 4N0959754AQTKE), hubspot(2021 e-tron mechanical key tipsheet)</t>
+          <t>motorgraph(e-트론 국내 출시), parts.audiusa(e-tron 4N0959754AQTKE), hubspot(2021 e-tron mechanical key tipsheet), auto-keys.eu(Audi A8·A6·Q8 2018+ 스마트키 4N0959754AL·e-tron 4M0959754BF 비상키 HU162T), keyshop-online(Audi MLB 2016+ 비상키 HU162T)</t>
         </is>
       </c>
       <c r="P360" s="11" t="inlineStr"/>
@@ -21037,7 +21388,11 @@
         </is>
       </c>
       <c r="I361" s="11" t="inlineStr"/>
-      <c r="J361" s="11" t="inlineStr"/>
+      <c r="J361" s="11" t="inlineStr">
+        <is>
+          <t>HU162T</t>
+        </is>
+      </c>
       <c r="K361" s="11" t="inlineStr"/>
       <c r="L361" s="11" t="inlineStr">
         <is>
@@ -21052,7 +21407,7 @@
       </c>
       <c r="O361" s="11" t="inlineStr">
         <is>
-          <t>parts.audiusa(2022 e-tron Sportback AQ/BF)</t>
+          <t>parts.audiusa(2022 e-tron Sportback AQ/BF), auto-keys.eu(Audi A8·A6·Q8 2018+ 스마트키 4N0959754AL·e-tron 4M0959754BF 비상키 HU162T), keyshop-online(Audi MLB 2016+ 비상키 HU162T)</t>
         </is>
       </c>
       <c r="P361" s="11" t="inlineStr"/>
@@ -21087,7 +21442,11 @@
         </is>
       </c>
       <c r="I362" s="11" t="inlineStr"/>
-      <c r="J362" s="11" t="inlineStr"/>
+      <c r="J362" s="11" t="inlineStr">
+        <is>
+          <t>HU162T</t>
+        </is>
+      </c>
       <c r="K362" s="11" t="inlineStr"/>
       <c r="L362" s="11" t="inlineStr">
         <is>
@@ -21102,7 +21461,7 @@
       </c>
       <c r="O362" s="11" t="inlineStr">
         <is>
-          <t>top-rider(Q8 e-트론 출시 예고 2023-01), parts.audiusa(e-tron AQ)</t>
+          <t>top-rider(Q8 e-트론 출시 예고 2023-01), parts.audiusa(e-tron AQ), auto-keys.eu(Audi A8·A6·Q8 2018+ 스마트키 4N0959754AL·e-tron 4M0959754BF 비상키 HU162T), keyshop-online(Audi MLB 2016+ 비상키 HU162T)</t>
         </is>
       </c>
       <c r="P362" s="11" t="inlineStr"/>
@@ -21137,7 +21496,11 @@
         </is>
       </c>
       <c r="I363" s="11" t="inlineStr"/>
-      <c r="J363" s="11" t="inlineStr"/>
+      <c r="J363" s="11" t="inlineStr">
+        <is>
+          <t>HU162T</t>
+        </is>
+      </c>
       <c r="K363" s="11" t="inlineStr"/>
       <c r="L363" s="11" t="inlineStr">
         <is>
@@ -21152,7 +21515,7 @@
       </c>
       <c r="O363" s="11" t="inlineStr">
         <is>
-          <t>autocast(Q8 e-트론 출시), go-parts(2019-2025 e-tron/Q8 key)</t>
+          <t>autocast(Q8 e-트론 출시), go-parts(2019-2025 e-tron/Q8 key), auto-keys.eu(Audi A8·A6·Q8 2018+ 스마트키 4N0959754AL·e-tron 4M0959754BF 비상키 HU162T), keyshop-online(Audi MLB 2016+ 비상키 HU162T)</t>
         </is>
       </c>
       <c r="P363" s="11" t="inlineStr"/>
@@ -21187,7 +21550,11 @@
         </is>
       </c>
       <c r="I364" s="11" t="inlineStr"/>
-      <c r="J364" s="11" t="inlineStr"/>
+      <c r="J364" s="11" t="inlineStr">
+        <is>
+          <t>HU162T</t>
+        </is>
+      </c>
       <c r="K364" s="11" t="inlineStr"/>
       <c r="L364" s="11" t="inlineStr">
         <is>
@@ -21202,7 +21569,7 @@
       </c>
       <c r="O364" s="11" t="inlineStr">
         <is>
-          <t>motor1(Q8 e-tron discontinued Feb 2025), greencarreports</t>
+          <t>motor1(Q8 e-tron discontinued Feb 2025), greencarreports, auto-keys.eu(Audi A8·A6·Q8 2018+ 스마트키 4N0959754AL·e-tron 4M0959754BF 비상키 HU162T), keyshop-online(Audi MLB 2016+ 비상키 HU162T)</t>
         </is>
       </c>
       <c r="P364" s="14" t="n"/>
@@ -21237,7 +21604,11 @@
         </is>
       </c>
       <c r="I365" s="11" t="inlineStr"/>
-      <c r="J365" s="11" t="inlineStr"/>
+      <c r="J365" s="11" t="inlineStr">
+        <is>
+          <t>HU162T</t>
+        </is>
+      </c>
       <c r="K365" s="11" t="inlineStr"/>
       <c r="L365" s="11" t="inlineStr">
         <is>
@@ -21252,7 +21623,7 @@
       </c>
       <c r="O365" s="11" t="inlineStr">
         <is>
-          <t>drive.com.au(Q8 e-tron remaining stock), topelectricsuv(final unsold Q8 e-trons)</t>
+          <t>drive.com.au(Q8 e-tron remaining stock), topelectricsuv(final unsold Q8 e-trons), auto-keys.eu(Audi A8·A6·Q8 2018+ 스마트키 4N0959754AL·e-tron 4M0959754BF 비상키 HU162T), keyshop-online(Audi MLB 2016+ 비상키 HU162T)</t>
         </is>
       </c>
       <c r="P365" s="6" t="inlineStr">
@@ -21291,7 +21662,11 @@
         </is>
       </c>
       <c r="I366" s="11" t="inlineStr"/>
-      <c r="J366" s="11" t="inlineStr"/>
+      <c r="J366" s="11" t="inlineStr">
+        <is>
+          <t>HU162T</t>
+        </is>
+      </c>
       <c r="K366" s="11" t="inlineStr"/>
       <c r="L366" s="11" t="inlineStr">
         <is>
@@ -21306,7 +21681,7 @@
       </c>
       <c r="O366" s="11" t="inlineStr">
         <is>
-          <t>edaily(더 뉴 Q8 e-트론 국내 출격), autouserguide(2024 Q8 e-tron keys)</t>
+          <t>edaily(더 뉴 Q8 e-트론 국내 출격), autouserguide(2024 Q8 e-tron keys), auto-keys.eu(Audi A8·A6·Q8 2018+ 스마트키 4N0959754AL·e-tron 4M0959754BF 비상키 HU162T), keyshop-online(Audi MLB 2016+ 비상키 HU162T)</t>
         </is>
       </c>
       <c r="P366" s="11" t="inlineStr"/>
@@ -21341,7 +21716,11 @@
         </is>
       </c>
       <c r="I367" s="11" t="inlineStr"/>
-      <c r="J367" s="11" t="inlineStr"/>
+      <c r="J367" s="11" t="inlineStr">
+        <is>
+          <t>HU162T</t>
+        </is>
+      </c>
       <c r="K367" s="11" t="inlineStr"/>
       <c r="L367" s="11" t="inlineStr">
         <is>
@@ -21356,7 +21735,7 @@
       </c>
       <c r="O367" s="11" t="inlineStr">
         <is>
-          <t>parts.audiusa(2025 SQ8 e-tron BF), go-parts(2019-2025 e-tron key)</t>
+          <t>parts.audiusa(2025 SQ8 e-tron BF), go-parts(2019-2025 e-tron key), auto-keys.eu(Audi A8·A6·Q8 2018+ 스마트키 4N0959754AL·e-tron 4M0959754BF 비상키 HU162T), keyshop-online(Audi MLB 2016+ 비상키 HU162T)</t>
         </is>
       </c>
       <c r="P367" s="11" t="inlineStr"/>
@@ -21391,7 +21770,11 @@
         </is>
       </c>
       <c r="I368" s="11" t="inlineStr"/>
-      <c r="J368" s="11" t="inlineStr"/>
+      <c r="J368" s="11" t="inlineStr">
+        <is>
+          <t>HU162T</t>
+        </is>
+      </c>
       <c r="K368" s="11" t="inlineStr"/>
       <c r="L368" s="11" t="inlineStr">
         <is>
@@ -21406,7 +21789,7 @@
       </c>
       <c r="O368" s="11" t="inlineStr">
         <is>
-          <t>2025년식 기록 준용 — parts.audiusa(2025 SQ8 e-tron BF), go-parts(2019-2025 e-tron key)</t>
+          <t>2025년식 기록 준용 — parts.audiusa(2025 SQ8 e-tron BF), go-parts(2019-2025 e-tron key), auto-keys.eu(Audi A8·A6·Q8 2018+ 스마트키 4N0959754AL·e-tron 4M0959754BF 비상키 HU162T), keyshop-online(Audi MLB 2016+ 비상키 HU162T)</t>
         </is>
       </c>
       <c r="P368" s="6" t="inlineStr">
@@ -24323,7 +24706,11 @@
         </is>
       </c>
       <c r="I412" s="11" t="inlineStr"/>
-      <c r="J412" s="11" t="inlineStr"/>
+      <c r="J412" s="11" t="inlineStr">
+        <is>
+          <t>HU66, HU162T</t>
+        </is>
+      </c>
       <c r="K412" s="11" t="inlineStr"/>
       <c r="L412" s="11" t="inlineStr">
         <is>
@@ -24338,7 +24725,7 @@
       </c>
       <c r="O412" s="11" t="inlineStr">
         <is>
-          <t>carisyou(R8 2세대 출시), audiusaparts(R8 4H0959754EB 315MHz)</t>
+          <t>carisyou(R8 2세대 출시), audiusaparts(R8 4H0959754EB 315MHz), auto-keys.eu(Audi R8 2021+ 순정 스마트키 4H0959754FK 비상키 HU162T), key4·Keymall(R8 HU66 비상키)</t>
         </is>
       </c>
       <c r="P412" s="6" t="inlineStr">
@@ -24389,7 +24776,11 @@
         </is>
       </c>
       <c r="I413" s="11" t="inlineStr"/>
-      <c r="J413" s="11" t="inlineStr"/>
+      <c r="J413" s="11" t="inlineStr">
+        <is>
+          <t>HU66, HU162T</t>
+        </is>
+      </c>
       <c r="K413" s="11" t="inlineStr"/>
       <c r="L413" s="11" t="inlineStr">
         <is>
@@ -24404,7 +24795,7 @@
       </c>
       <c r="O413" s="11" t="inlineStr">
         <is>
-          <t>ebay(2017 R8 4H0959754EB), go-parts(2017-2023 R8 key)</t>
+          <t>ebay(2017 R8 4H0959754EB), go-parts(2017-2023 R8 key), auto-keys.eu(Audi R8 2021+ 순정 스마트키 4H0959754FK 비상키 HU162T), key4·Keymall(R8 HU66 비상키)</t>
         </is>
       </c>
       <c r="P413" s="6" t="inlineStr">
@@ -24455,7 +24846,11 @@
         </is>
       </c>
       <c r="I414" s="11" t="inlineStr"/>
-      <c r="J414" s="11" t="inlineStr"/>
+      <c r="J414" s="11" t="inlineStr">
+        <is>
+          <t>HU66, HU162T</t>
+        </is>
+      </c>
       <c r="K414" s="11" t="inlineStr"/>
       <c r="L414" s="11" t="inlineStr">
         <is>
@@ -24470,7 +24865,7 @@
       </c>
       <c r="O414" s="11" t="inlineStr">
         <is>
-          <t>go-parts(R8 key guide), wikipedia(R8 Type 4S)</t>
+          <t>go-parts(R8 key guide), wikipedia(R8 Type 4S), auto-keys.eu(Audi R8 2021+ 순정 스마트키 4H0959754FK 비상키 HU162T), key4·Keymall(R8 HU66 비상키)</t>
         </is>
       </c>
       <c r="P414" s="6" t="inlineStr">
@@ -24521,7 +24916,11 @@
         </is>
       </c>
       <c r="I415" s="11" t="inlineStr"/>
-      <c r="J415" s="11" t="inlineStr"/>
+      <c r="J415" s="11" t="inlineStr">
+        <is>
+          <t>HU66, HU162T</t>
+        </is>
+      </c>
       <c r="K415" s="11" t="inlineStr"/>
       <c r="L415" s="11" t="inlineStr">
         <is>
@@ -24536,7 +24935,7 @@
       </c>
       <c r="O415" s="11" t="inlineStr">
         <is>
-          <t>parts.audiusa(2020 R8 8S0959754ACTKE)</t>
+          <t>parts.audiusa(2020 R8 8S0959754ACTKE), auto-keys.eu(Audi R8 2021+ 순정 스마트키 4H0959754FK 비상키 HU162T), key4·Keymall(R8 HU66 비상키)</t>
         </is>
       </c>
       <c r="P415" s="6" t="inlineStr">
@@ -24587,7 +24986,11 @@
         </is>
       </c>
       <c r="I416" s="11" t="inlineStr"/>
-      <c r="J416" s="11" t="inlineStr"/>
+      <c r="J416" s="11" t="inlineStr">
+        <is>
+          <t>HU66, HU162T</t>
+        </is>
+      </c>
       <c r="K416" s="11" t="inlineStr"/>
       <c r="L416" s="11" t="inlineStr">
         <is>
@@ -24602,7 +25005,7 @@
       </c>
       <c r="O416" s="11" t="inlineStr">
         <is>
-          <t>motorgraph(R8 V10 퍼포먼스 출시), ebay(R8 V10 plus RWS key fob)</t>
+          <t>motorgraph(R8 V10 퍼포먼스 출시), ebay(R8 V10 plus RWS key fob), auto-keys.eu(Audi R8 2021+ 순정 스마트키 4H0959754FK 비상키 HU162T), key4·Keymall(R8 HU66 비상키)</t>
         </is>
       </c>
       <c r="P416" s="6" t="inlineStr">
@@ -24653,7 +25056,11 @@
         </is>
       </c>
       <c r="I417" s="11" t="inlineStr"/>
-      <c r="J417" s="11" t="inlineStr"/>
+      <c r="J417" s="11" t="inlineStr">
+        <is>
+          <t>HU66, HU162T</t>
+        </is>
+      </c>
       <c r="K417" s="11" t="inlineStr"/>
       <c r="L417" s="11" t="inlineStr">
         <is>
@@ -24668,7 +25075,7 @@
       </c>
       <c r="O417" s="11" t="inlineStr">
         <is>
-          <t>parts.audiusa(2022 R8)</t>
+          <t>parts.audiusa(2022 R8), auto-keys.eu(Audi R8 2021+ 순정 스마트키 4H0959754FK 비상키 HU162T), key4·Keymall(R8 HU66 비상키)</t>
         </is>
       </c>
       <c r="P417" s="6" t="inlineStr">
@@ -24719,7 +25126,11 @@
         </is>
       </c>
       <c r="I418" s="11" t="inlineStr"/>
-      <c r="J418" s="11" t="inlineStr"/>
+      <c r="J418" s="11" t="inlineStr">
+        <is>
+          <t>HU66, HU162T</t>
+        </is>
+      </c>
       <c r="K418" s="11" t="inlineStr"/>
       <c r="L418" s="11" t="inlineStr">
         <is>
@@ -24734,7 +25145,7 @@
       </c>
       <c r="O418" s="11" t="inlineStr">
         <is>
-          <t>ebay(2017-2023 R8 5-button), go-parts(R8 key guide)</t>
+          <t>ebay(2017-2023 R8 5-button), go-parts(R8 key guide), auto-keys.eu(Audi R8 2021+ 순정 스마트키 4H0959754FK 비상키 HU162T), key4·Keymall(R8 HU66 비상키)</t>
         </is>
       </c>
       <c r="P418" s="6" t="inlineStr">
@@ -24785,7 +25196,11 @@
         </is>
       </c>
       <c r="I419" s="11" t="inlineStr"/>
-      <c r="J419" s="11" t="inlineStr"/>
+      <c r="J419" s="11" t="inlineStr">
+        <is>
+          <t>HU66, HU162T</t>
+        </is>
+      </c>
       <c r="K419" s="11" t="inlineStr"/>
       <c r="L419" s="11" t="inlineStr">
         <is>
@@ -24800,7 +25215,7 @@
       </c>
       <c r="O419" s="11" t="inlineStr">
         <is>
-          <t>wikipedia(R8 Type 4S), carandtruckremotes(2024 R8)</t>
+          <t>wikipedia(R8 Type 4S), carandtruckremotes(2024 R8), auto-keys.eu(Audi R8 2021+ 순정 스마트키 4H0959754FK 비상키 HU162T), key4·Keymall(R8 HU66 비상키)</t>
         </is>
       </c>
       <c r="P419" s="6" t="inlineStr">
@@ -24839,7 +25254,11 @@
         </is>
       </c>
       <c r="I420" s="11" t="inlineStr"/>
-      <c r="J420" s="11" t="inlineStr"/>
+      <c r="J420" s="11" t="inlineStr">
+        <is>
+          <t>HU162T</t>
+        </is>
+      </c>
       <c r="K420" s="11" t="inlineStr"/>
       <c r="L420" s="11" t="inlineStr">
         <is>
@@ -24854,7 +25273,7 @@
       </c>
       <c r="O420" s="11" t="inlineStr">
         <is>
-          <t>namu.wiki(e-트론 GT), wikipedia(e-tron GT J1)</t>
+          <t>namu.wiki(e-트론 GT), wikipedia(e-tron GT J1), auto-keys.eu(Audi A8·A6·Q8 2018+ 스마트키 4N0959754AL·e-tron 4M0959754BF 비상키 HU162T), keyshop-online(Audi MLB 2016+ 비상키 HU162T)</t>
         </is>
       </c>
       <c r="P420" s="11" t="inlineStr"/>
@@ -24889,7 +25308,11 @@
         </is>
       </c>
       <c r="I421" s="11" t="inlineStr"/>
-      <c r="J421" s="11" t="inlineStr"/>
+      <c r="J421" s="11" t="inlineStr">
+        <is>
+          <t>HU162T</t>
+        </is>
+      </c>
       <c r="K421" s="11" t="inlineStr"/>
       <c r="L421" s="11" t="inlineStr">
         <is>
@@ -24904,7 +25327,7 @@
       </c>
       <c r="O421" s="11" t="inlineStr">
         <is>
-          <t>parts.audiusa(2022 e-tron GT AQ/BC)</t>
+          <t>parts.audiusa(2022 e-tron GT AQ/BC), auto-keys.eu(Audi A8·A6·Q8 2018+ 스마트키 4N0959754AL·e-tron 4M0959754BF 비상키 HU162T), keyshop-online(Audi MLB 2016+ 비상키 HU162T)</t>
         </is>
       </c>
       <c r="P421" s="11" t="inlineStr"/>
@@ -24939,7 +25362,11 @@
         </is>
       </c>
       <c r="I422" s="11" t="inlineStr"/>
-      <c r="J422" s="11" t="inlineStr"/>
+      <c r="J422" s="11" t="inlineStr">
+        <is>
+          <t>HU162T</t>
+        </is>
+      </c>
       <c r="K422" s="11" t="inlineStr"/>
       <c r="L422" s="11" t="inlineStr">
         <is>
@@ -24954,7 +25381,7 @@
       </c>
       <c r="O422" s="11" t="inlineStr">
         <is>
-          <t>parts.audiusa(2023 e-tron GT AQ), go-parts(2019-2025 e-tron GT key)</t>
+          <t>parts.audiusa(2023 e-tron GT AQ), go-parts(2019-2025 e-tron GT key), auto-keys.eu(Audi A8·A6·Q8 2018+ 스마트키 4N0959754AL·e-tron 4M0959754BF 비상키 HU162T), keyshop-online(Audi MLB 2016+ 비상키 HU162T)</t>
         </is>
       </c>
       <c r="P422" s="11" t="inlineStr"/>
@@ -24989,7 +25416,11 @@
         </is>
       </c>
       <c r="I423" s="11" t="inlineStr"/>
-      <c r="J423" s="11" t="inlineStr"/>
+      <c r="J423" s="11" t="inlineStr">
+        <is>
+          <t>HU162T</t>
+        </is>
+      </c>
       <c r="K423" s="11" t="inlineStr"/>
       <c r="L423" s="11" t="inlineStr">
         <is>
@@ -25004,7 +25435,7 @@
       </c>
       <c r="O423" s="11" t="inlineStr">
         <is>
-          <t>parts.audivirginiabeach(2024 e-tron GT AQ), go-parts(e-tron GT key)</t>
+          <t>parts.audivirginiabeach(2024 e-tron GT AQ), go-parts(e-tron GT key), auto-keys.eu(Audi A8·A6·Q8 2018+ 스마트키 4N0959754AL·e-tron 4M0959754BF 비상키 HU162T), keyshop-online(Audi MLB 2016+ 비상키 HU162T)</t>
         </is>
       </c>
       <c r="P423" s="11" t="inlineStr"/>
@@ -25039,7 +25470,11 @@
         </is>
       </c>
       <c r="I424" s="11" t="inlineStr"/>
-      <c r="J424" s="11" t="inlineStr"/>
+      <c r="J424" s="11" t="inlineStr">
+        <is>
+          <t>HU162T</t>
+        </is>
+      </c>
       <c r="K424" s="11" t="inlineStr"/>
       <c r="L424" s="11" t="inlineStr">
         <is>
@@ -25054,7 +25489,7 @@
       </c>
       <c r="O424" s="11" t="inlineStr">
         <is>
-          <t>newsis(S e-트론 GT 부분변경 출시), parts.audiusa(2025 e-tron GT vehicle key)</t>
+          <t>newsis(S e-트론 GT 부분변경 출시), parts.audiusa(2025 e-tron GT vehicle key), auto-keys.eu(Audi A8·A6·Q8 2018+ 스마트키 4N0959754AL·e-tron 4M0959754BF 비상키 HU162T), keyshop-online(Audi MLB 2016+ 비상키 HU162T)</t>
         </is>
       </c>
       <c r="P424" s="14" t="n"/>
@@ -25089,7 +25524,11 @@
         </is>
       </c>
       <c r="I425" s="11" t="inlineStr"/>
-      <c r="J425" s="11" t="inlineStr"/>
+      <c r="J425" s="11" t="inlineStr">
+        <is>
+          <t>HU162T</t>
+        </is>
+      </c>
       <c r="K425" s="11" t="inlineStr"/>
       <c r="L425" s="11" t="inlineStr">
         <is>
@@ -25104,7 +25543,7 @@
       </c>
       <c r="O425" s="11" t="inlineStr">
         <is>
-          <t>parts.audiwest(e-tron GT 8V4915798BS02), go-parts</t>
+          <t>parts.audiwest(e-tron GT 8V4915798BS02), go-parts, auto-keys.eu(Audi A8·A6·Q8 2018+ 스마트키 4N0959754AL·e-tron 4M0959754BF 비상키 HU162T), keyshop-online(Audi MLB 2016+ 비상키 HU162T)</t>
         </is>
       </c>
       <c r="P425" s="6" t="inlineStr">
@@ -25143,7 +25582,11 @@
         </is>
       </c>
       <c r="I426" s="11" t="inlineStr"/>
-      <c r="J426" s="11" t="inlineStr"/>
+      <c r="J426" s="11" t="inlineStr">
+        <is>
+          <t>HU162T</t>
+        </is>
+      </c>
       <c r="K426" s="11" t="inlineStr"/>
       <c r="L426" s="11" t="inlineStr">
         <is>
@@ -25158,7 +25601,7 @@
       </c>
       <c r="O426" s="11" t="inlineStr">
         <is>
-          <t>namu.wiki(e-트론 GT), parts.audiusa(RS e-tron GT BC)</t>
+          <t>namu.wiki(e-트론 GT), parts.audiusa(RS e-tron GT BC), auto-keys.eu(Audi A8·A6·Q8 2018+ 스마트키 4N0959754AL·e-tron 4M0959754BF 비상키 HU162T), keyshop-online(Audi MLB 2016+ 비상키 HU162T)</t>
         </is>
       </c>
       <c r="P426" s="11" t="inlineStr"/>
@@ -25193,7 +25636,11 @@
         </is>
       </c>
       <c r="I427" s="11" t="inlineStr"/>
-      <c r="J427" s="11" t="inlineStr"/>
+      <c r="J427" s="11" t="inlineStr">
+        <is>
+          <t>HU162T</t>
+        </is>
+      </c>
       <c r="K427" s="11" t="inlineStr"/>
       <c r="L427" s="11" t="inlineStr">
         <is>
@@ -25208,7 +25655,7 @@
       </c>
       <c r="O427" s="11" t="inlineStr">
         <is>
-          <t>ebay.com.au(2022 RS e-tron GT 2701A AK2), parts.audiusa</t>
+          <t>ebay.com.au(2022 RS e-tron GT 2701A AK2), parts.audiusa, auto-keys.eu(Audi A8·A6·Q8 2018+ 스마트키 4N0959754AL·e-tron 4M0959754BF 비상키 HU162T), keyshop-online(Audi MLB 2016+ 비상키 HU162T)</t>
         </is>
       </c>
       <c r="P427" s="11" t="inlineStr"/>
@@ -25243,7 +25690,11 @@
         </is>
       </c>
       <c r="I428" s="11" t="inlineStr"/>
-      <c r="J428" s="11" t="inlineStr"/>
+      <c r="J428" s="11" t="inlineStr">
+        <is>
+          <t>HU162T</t>
+        </is>
+      </c>
       <c r="K428" s="11" t="inlineStr"/>
       <c r="L428" s="11" t="inlineStr">
         <is>
@@ -25258,7 +25709,7 @@
       </c>
       <c r="O428" s="11" t="inlineStr">
         <is>
-          <t>truecar(2023 RS e-tron GT), audiusa(2023 e-tron GT key setup)</t>
+          <t>truecar(2023 RS e-tron GT), audiusa(2023 e-tron GT key setup), auto-keys.eu(Audi A8·A6·Q8 2018+ 스마트키 4N0959754AL·e-tron 4M0959754BF 비상키 HU162T), keyshop-online(Audi MLB 2016+ 비상키 HU162T)</t>
         </is>
       </c>
       <c r="P428" s="14" t="n"/>
@@ -25293,7 +25744,11 @@
         </is>
       </c>
       <c r="I429" s="11" t="inlineStr"/>
-      <c r="J429" s="11" t="inlineStr"/>
+      <c r="J429" s="11" t="inlineStr">
+        <is>
+          <t>HU162T</t>
+        </is>
+      </c>
       <c r="K429" s="11" t="inlineStr"/>
       <c r="L429" s="11" t="inlineStr">
         <is>
@@ -25308,7 +25763,7 @@
       </c>
       <c r="O429" s="11" t="inlineStr">
         <is>
-          <t>parts.audiusa(2025 RS e-tron GT BC), parts.audipaloalto(e-tron GT BC)</t>
+          <t>parts.audiusa(2025 RS e-tron GT BC), parts.audipaloalto(e-tron GT BC), auto-keys.eu(Audi A8·A6·Q8 2018+ 스마트키 4N0959754AL·e-tron 4M0959754BF 비상키 HU162T), keyshop-online(Audi MLB 2016+ 비상키 HU162T)</t>
         </is>
       </c>
       <c r="P429" s="14" t="n"/>
@@ -25343,7 +25798,11 @@
         </is>
       </c>
       <c r="I430" s="11" t="inlineStr"/>
-      <c r="J430" s="11" t="inlineStr"/>
+      <c r="J430" s="11" t="inlineStr">
+        <is>
+          <t>HU162T</t>
+        </is>
+      </c>
       <c r="K430" s="11" t="inlineStr"/>
       <c r="L430" s="11" t="inlineStr">
         <is>
@@ -25358,7 +25817,7 @@
       </c>
       <c r="O430" s="11" t="inlineStr">
         <is>
-          <t>newsis(RS e-트론 GT 퍼포먼스 출시), parts.audiusa(2025 RS e-tron GT BC)</t>
+          <t>newsis(RS e-트론 GT 퍼포먼스 출시), parts.audiusa(2025 RS e-tron GT BC), auto-keys.eu(Audi A8·A6·Q8 2018+ 스마트키 4N0959754AL·e-tron 4M0959754BF 비상키 HU162T), keyshop-online(Audi MLB 2016+ 비상키 HU162T)</t>
         </is>
       </c>
       <c r="P430" s="14" t="n"/>
@@ -25393,7 +25852,11 @@
         </is>
       </c>
       <c r="I431" s="11" t="inlineStr"/>
-      <c r="J431" s="11" t="inlineStr"/>
+      <c r="J431" s="11" t="inlineStr">
+        <is>
+          <t>HU162T</t>
+        </is>
+      </c>
       <c r="K431" s="11" t="inlineStr"/>
       <c r="L431" s="11" t="inlineStr">
         <is>
@@ -25408,7 +25871,7 @@
       </c>
       <c r="O431" s="11" t="inlineStr">
         <is>
-          <t>audiusa(2026 RS e-tron GT performance), kbb(2026 RS e-tron GT)</t>
+          <t>audiusa(2026 RS e-tron GT performance), kbb(2026 RS e-tron GT), auto-keys.eu(Audi A8·A6·Q8 2018+ 스마트키 4N0959754AL·e-tron 4M0959754BF 비상키 HU162T), keyshop-online(Audi MLB 2016+ 비상키 HU162T)</t>
         </is>
       </c>
       <c r="P431" s="6" t="inlineStr">
@@ -25429,7 +25892,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A70"/>
+  <dimension ref="A1:A71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="150" customWidth="1" min="1" max="1"/>
@@ -25893,6 +26356,13 @@
         </is>
       </c>
     </row>
+    <row r="71">
+      <c r="A71" s="26" t="inlineStr">
+        <is>
+          <t>- 6차 세대별 보완: MLB evo(A6·A7·A8·Q8·e-트론 등 2018~) 비상키 HU162T(auto-keys·keyshop), R8 4S HU66·HU162T, Q4 e-트론 MEB HU66. 2025년 이후 신형(A5 B10·Q5 GU·Q6 e-트론·A6 e-트론)은 Audi 순정 공용 키 4M0959754CG 기준 MLB evo 계열로 추정(주황)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
